--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN3"/>
+  <dimension ref="A1:AN2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -629,282 +629,136 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4406</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>新昕纖</t>
+          <t>億泰</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>10</v>
+        <v>18.79999923706055</v>
       </c>
       <c r="G2" t="n">
-        <v>10.02700004577637</v>
+        <v>19.23249988555908</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>38.74853767215826</v>
+        <v>41.78723051602822</v>
       </c>
       <c r="J2" t="n">
-        <v>33.69818633041162</v>
+        <v>33.30550904357997</v>
       </c>
       <c r="K2" t="n">
-        <v>49.35789437444871</v>
+        <v>40.71368745382341</v>
       </c>
       <c r="L2" t="n">
-        <v>54800</v>
+        <v>594927.2</v>
       </c>
       <c r="M2" t="n">
-        <v>28850</v>
+        <v>344849.2</v>
       </c>
       <c r="N2" t="n">
-        <v>35450</v>
+        <v>385720.475</v>
       </c>
       <c r="O2" t="n">
-        <v>1.89948006932409</v>
+        <v>1.725180745670861</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.005521283981343217</v>
+        <v>-0.2522845087345402</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.003822729009781798</v>
+        <v>-0.2333507626246235</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.009344012991125014</v>
+        <v>-0.01893374610991677</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.01167934474599521</v>
+        <v>-0.01618484084401525</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.01451802404534919</v>
+        <v>-0.0173019603056076</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>-49.036</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>0.722</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>-48.314</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>390.024</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>-0.5949999999999999</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>389.429</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>698.576</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>0.7059999999999996</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>699.2819999999999</v>
       </c>
       <c r="AN2" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>80</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1616</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>億泰</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>18.79999923706055</v>
-      </c>
-      <c r="G3" t="n">
-        <v>19.23249988555908</v>
-      </c>
-      <c r="H3" t="b">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>41.78723051632754</v>
-      </c>
-      <c r="J3" t="n">
-        <v>33.30550904920057</v>
-      </c>
-      <c r="K3" t="n">
-        <v>42.02824549427734</v>
-      </c>
-      <c r="L3" t="n">
-        <v>595393.2</v>
-      </c>
-      <c r="M3" t="n">
-        <v>344965.7</v>
-      </c>
-      <c r="N3" t="n">
-        <v>385778.725</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.725948985652776</v>
-      </c>
-      <c r="P3" t="n">
-        <v>-0.2477411726811241</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>-0.2266987258114353</v>
-      </c>
-      <c r="R3" t="n">
-        <v>-0.02104244686968873</v>
-      </c>
-      <c r="S3" t="n">
-        <v>-0.01845864791455323</v>
-      </c>
-      <c r="T3" t="n">
-        <v>-0.01975343893701209</v>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB3" t="n">
-        <v>-2.964</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>-1.058</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>-4.022</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>376.06</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>-1.516</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>374.544</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>715.5960000000001</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1.871</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>717.4669999999999</v>
-      </c>
-      <c r="AN3" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN2"/>
+  <dimension ref="A1:AN10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -629,138 +629,1306 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>8401</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>白紗科</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>22.70000076293945</v>
+      </c>
+      <c r="G2" t="n">
+        <v>22.83999986648559</v>
+      </c>
+      <c r="H2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>42.07934109863474</v>
+      </c>
+      <c r="J2" t="n">
+        <v>34.19276193753539</v>
+      </c>
+      <c r="K2" t="n">
+        <v>42.83725713600048</v>
+      </c>
+      <c r="L2" t="n">
+        <v>54007</v>
+      </c>
+      <c r="M2" t="n">
+        <v>31379.55</v>
+      </c>
+      <c r="N2" t="n">
+        <v>31288.25</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.721089053220967</v>
+      </c>
+      <c r="P2" t="n">
+        <v>-0.06731632637356455</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>-0.04742212255354807</v>
+      </c>
+      <c r="R2" t="n">
+        <v>-0.01989420382001648</v>
+      </c>
+      <c r="S2" t="n">
+        <v>-0.02575487877083031</v>
+      </c>
+      <c r="T2" t="n">
+        <v>-0.02724281547297571</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>80</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>1616</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>億泰</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>18.79999923706055</v>
-      </c>
-      <c r="G2" t="n">
-        <v>19.23249988555908</v>
-      </c>
-      <c r="H2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>41.78723051602822</v>
-      </c>
-      <c r="J2" t="n">
-        <v>33.30550904357997</v>
-      </c>
-      <c r="K2" t="n">
-        <v>40.71368745382341</v>
-      </c>
-      <c r="L2" t="n">
-        <v>594927.2</v>
-      </c>
-      <c r="M2" t="n">
-        <v>344849.2</v>
-      </c>
-      <c r="N2" t="n">
-        <v>385720.475</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.725180745670861</v>
-      </c>
-      <c r="P2" t="n">
-        <v>-0.2522845087345402</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>-0.2333507626246235</v>
-      </c>
-      <c r="R2" t="n">
+      <c r="F3" t="n">
+        <v>18.35000038146973</v>
+      </c>
+      <c r="G3" t="n">
+        <v>19.17249984741211</v>
+      </c>
+      <c r="H3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>38.94728849149878</v>
+      </c>
+      <c r="J3" t="n">
+        <v>36.72689991480502</v>
+      </c>
+      <c r="K3" t="n">
+        <v>35.64704537487061</v>
+      </c>
+      <c r="L3" t="n">
+        <v>578344.2</v>
+      </c>
+      <c r="M3" t="n">
+        <v>345469.7</v>
+      </c>
+      <c r="N3" t="n">
+        <v>367276.475</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.674080823875437</v>
+      </c>
+      <c r="P3" t="n">
+        <v>-0.3152365068020657</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-0.2583406705081664</v>
+      </c>
+      <c r="R3" t="n">
+        <v>-0.05689583629389927</v>
+      </c>
+      <c r="S3" t="n">
+        <v>-0.04306379524027276</v>
+      </c>
+      <c r="T3" t="n">
         <v>-0.01893374610991677</v>
       </c>
-      <c r="S2" t="n">
-        <v>-0.01618484084401525</v>
-      </c>
-      <c r="T2" t="n">
-        <v>-0.0173019603056076</v>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB2" t="n">
-        <v>-49.036</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0.722</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>-48.314</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>390.024</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-0.5949999999999999</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>389.429</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>698.576</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0.7059999999999996</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>699.2819999999999</v>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>-24.57</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>-24.57</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>354.302</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>-0.4769999999999999</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>353.825</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>752.0060000000001</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.3339999999999992</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>752.34</v>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>70</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1441</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>大東</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>8.609999656677246</v>
+      </c>
+      <c r="G4" t="n">
+        <v>8.844499921798706</v>
+      </c>
+      <c r="H4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>32.77095137096235</v>
+      </c>
+      <c r="J4" t="n">
+        <v>30.89585221755802</v>
+      </c>
+      <c r="K4" t="n">
+        <v>37.83745191169973</v>
+      </c>
+      <c r="L4" t="n">
+        <v>49229</v>
+      </c>
+      <c r="M4" t="n">
+        <v>21139.2</v>
+      </c>
+      <c r="N4" t="n">
+        <v>17459.975</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.328801468362095</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-0.08077522527042369</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-0.06440407400421262</v>
+      </c>
+      <c r="R4" t="n">
+        <v>-0.01637115126621107</v>
+      </c>
+      <c r="S4" t="n">
+        <v>-0.01126207756300962</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-0.01554618882503493</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>-14.97</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>-14.97</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>-9.409999999999997</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>-8.409999999999997</v>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>70</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2035</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>唐榮公司</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>26.89999961853027</v>
+      </c>
+      <c r="G5" t="n">
+        <v>26.98000001907349</v>
+      </c>
+      <c r="H5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>49.21733687559828</v>
+      </c>
+      <c r="J5" t="n">
+        <v>47.60871879792085</v>
+      </c>
+      <c r="K5" t="n">
+        <v>47.83740380717153</v>
+      </c>
+      <c r="L5" t="n">
+        <v>8900.4</v>
+      </c>
+      <c r="M5" t="n">
+        <v>4527.15</v>
+      </c>
+      <c r="N5" t="n">
+        <v>4371.475</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.966005102547961</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-0.06173592214328849</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-0.09958961854682309</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.0378536964035346</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.04144755281917308</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.03002840241648751</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>70</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>3346</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>麗清</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>19.29999923706055</v>
+      </c>
+      <c r="G6" t="n">
+        <v>19.60999994277954</v>
+      </c>
+      <c r="H6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>44.73112456571825</v>
+      </c>
+      <c r="J6" t="n">
+        <v>37.99095337286886</v>
+      </c>
+      <c r="K6" t="n">
+        <v>44.34632401496682</v>
+      </c>
+      <c r="L6" t="n">
+        <v>656345.6</v>
+      </c>
+      <c r="M6" t="n">
+        <v>343879.85</v>
+      </c>
+      <c r="N6" t="n">
+        <v>345745.025</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.908648035062246</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-0.4173971035858699</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-0.5184136045501052</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.1010165009642353</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.1046405307816412</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.09939678937226193</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-367.055</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.703000000000001</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-365.352</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>-882.895</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>3.817000000000001</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>-879.0779999999999</v>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>70</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1813</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>寶利徠</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="G7" t="n">
+        <v>11.475</v>
+      </c>
+      <c r="H7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>43.32011404443771</v>
+      </c>
+      <c r="J7" t="n">
+        <v>37.02570263424967</v>
+      </c>
+      <c r="K7" t="n">
+        <v>37.26563125359729</v>
+      </c>
+      <c r="L7" t="n">
+        <v>24891.4</v>
+      </c>
+      <c r="M7" t="n">
+        <v>15019.9</v>
+      </c>
+      <c r="N7" t="n">
+        <v>14731.1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.657228077417293</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-0.0734608769618923</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-0.06134059694198695</v>
+      </c>
+      <c r="R7" t="n">
+        <v>-0.01212028001990535</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-0.005040175021427222</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-0.002656351311715079</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>70</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2608</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>嘉里大榮</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>28.60000038146973</v>
+      </c>
+      <c r="G8" t="n">
+        <v>28.61499996185303</v>
+      </c>
+      <c r="H8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>32.38510259863372</v>
+      </c>
+      <c r="J8" t="n">
+        <v>30.99057606056034</v>
+      </c>
+      <c r="K8" t="n">
+        <v>47.82558606939766</v>
+      </c>
+      <c r="L8" t="n">
+        <v>394708.6</v>
+      </c>
+      <c r="M8" t="n">
+        <v>242058.7</v>
+      </c>
+      <c r="N8" t="n">
+        <v>262455</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.630631743457269</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-0.0390910268463287</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-0.07441211820317017</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.03532109135684147</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.04404443177368969</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.04021651876430968</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>-88</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>5.959</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>-82.041</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>-172.227</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>27.213</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>-145.014</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>-687.8420000000001</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>15.352</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>-672.49</v>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>70</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>5212</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>凌網</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>46.34999847412109</v>
+      </c>
+      <c r="G9" t="n">
+        <v>46.59750003814698</v>
+      </c>
+      <c r="H9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>47.64762642686387</v>
+      </c>
+      <c r="J9" t="n">
+        <v>44.32919797250486</v>
+      </c>
+      <c r="K9" t="n">
+        <v>44.93952246294608</v>
+      </c>
+      <c r="L9" t="n">
+        <v>14717.8</v>
+      </c>
+      <c r="M9" t="n">
+        <v>9080.25</v>
+      </c>
+      <c r="N9" t="n">
+        <v>7490.7</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.620858456540293</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-0.1065821190914278</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-0.1232930226543603</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.01671090356293253</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.03534973315428425</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.01816647589076786</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>70</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>8171</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>天宇</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>19.79999923706055</v>
+      </c>
+      <c r="G10" t="n">
+        <v>19.80249996185303</v>
+      </c>
+      <c r="H10" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>47.34680897278013</v>
+      </c>
+      <c r="J10" t="n">
+        <v>47.06915737543887</v>
+      </c>
+      <c r="K10" t="n">
+        <v>47.90412596045189</v>
+      </c>
+      <c r="L10" t="n">
+        <v>205420.2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>129896.9</v>
+      </c>
+      <c r="N10" t="n">
+        <v>106662.425</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.581409564046563</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-0.03303016645965329</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-0.05413263120931249</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.0211024647496592</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.02652463747027661</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.03382116332097197</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN10"/>
+  <dimension ref="A1:AN8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,67 +625,67 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8401</t>
+          <t>4930</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>白紗科</t>
+          <t>燦星網</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>22.70000076293945</v>
+        <v>16.10000038146973</v>
       </c>
       <c r="G2" t="n">
-        <v>22.83999986648559</v>
+        <v>16.09750013351441</v>
       </c>
       <c r="H2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>42.07934109863474</v>
+        <v>39.757641097281</v>
       </c>
       <c r="J2" t="n">
-        <v>34.19276193753539</v>
+        <v>39.5653735526485</v>
       </c>
       <c r="K2" t="n">
-        <v>42.83725713600048</v>
+        <v>48.95453942892726</v>
       </c>
       <c r="L2" t="n">
-        <v>54007</v>
+        <v>81670.8</v>
       </c>
       <c r="M2" t="n">
-        <v>31379.55</v>
+        <v>32720.75</v>
       </c>
       <c r="N2" t="n">
-        <v>31288.25</v>
+        <v>58465.35</v>
       </c>
       <c r="O2" t="n">
-        <v>1.721089053220967</v>
+        <v>2.495994132163841</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.06731632637356455</v>
+        <v>-0.08801242887535565</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.04742212255354807</v>
+        <v>-0.08417019948365545</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.01989420382001648</v>
+        <v>-0.003842229391700203</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.02575487877083031</v>
+        <v>-0.01865661834749327</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.02724281547297571</v>
+        <v>-0.01915789471663962</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -732,10 +732,10 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
@@ -744,23 +744,23 @@
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>23.709</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>22.709</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
@@ -771,16 +771,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>1441</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>億泰</t>
+          <t>大東</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -789,49 +789,49 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>18.35000038146973</v>
+        <v>8.720000267028809</v>
       </c>
       <c r="G3" t="n">
-        <v>19.17249984741211</v>
+        <v>8.840499925613404</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>38.94728849149878</v>
+        <v>42.83500320322867</v>
       </c>
       <c r="J3" t="n">
-        <v>36.72689991480502</v>
+        <v>34.87556923249954</v>
       </c>
       <c r="K3" t="n">
-        <v>35.64704537487061</v>
+        <v>44.29068228982177</v>
       </c>
       <c r="L3" t="n">
-        <v>578344.2</v>
+        <v>47668.4</v>
       </c>
       <c r="M3" t="n">
-        <v>345469.7</v>
+        <v>21749.45</v>
       </c>
       <c r="N3" t="n">
-        <v>367276.475</v>
+        <v>17031.5</v>
       </c>
       <c r="O3" t="n">
-        <v>1.674080823875437</v>
+        <v>2.191705997163147</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.3152365068020657</v>
+        <v>-0.07785466714476996</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2583406705081664</v>
+        <v>-0.06654456174527329</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.05689583629389927</v>
+        <v>-0.01131010539949667</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.04306379524027276</v>
+        <v>-0.0165890448942871</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.01893374610991677</v>
+        <v>-0.01149705012827114</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>-24.57</v>
+        <v>-6</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -878,35 +878,35 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>-24.57</v>
+        <v>-6</v>
       </c>
       <c r="AF3" t="n">
-        <v>354.302</v>
+        <v>-25.97</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0.4769999999999999</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>353.825</v>
+        <v>-25.97</v>
       </c>
       <c r="AJ3" t="n">
-        <v>752.0060000000001</v>
+        <v>-11.41</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.3339999999999992</v>
+        <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>752.34</v>
+        <v>-10.41</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1441</t>
+          <t>3346</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>大東</t>
+          <t>麗清</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,49 +935,49 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>8.609999656677246</v>
+        <v>19.75</v>
       </c>
       <c r="G4" t="n">
-        <v>8.844499921798706</v>
+        <v>19.60249996185303</v>
       </c>
       <c r="H4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>32.77095137096235</v>
+        <v>49.95963639245484</v>
       </c>
       <c r="J4" t="n">
-        <v>30.89585221755802</v>
+        <v>41.98051439225708</v>
       </c>
       <c r="K4" t="n">
-        <v>37.83745191169973</v>
+        <v>48.74302681866537</v>
       </c>
       <c r="L4" t="n">
-        <v>49229</v>
+        <v>678310.6</v>
       </c>
       <c r="M4" t="n">
-        <v>21139.2</v>
+        <v>340421.1</v>
       </c>
       <c r="N4" t="n">
-        <v>17459.975</v>
+        <v>341490.65</v>
       </c>
       <c r="O4" t="n">
-        <v>2.328801468362095</v>
+        <v>1.992563328183829</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.08077522527042369</v>
+        <v>-0.3576237721918716</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.06440407400421262</v>
+        <v>-0.483507468666879</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.01637115126621107</v>
+        <v>0.1258836964750074</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.01126207756300962</v>
+        <v>0.09992702688669475</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.01554618882503493</v>
+        <v>0.1034656615528102</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>-3</v>
+        <v>54.042</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1024,35 +1024,35 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-3</v>
+        <v>54.042</v>
       </c>
       <c r="AF4" t="n">
-        <v>-14.97</v>
+        <v>-300.123</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.674000000000001</v>
       </c>
       <c r="AI4" t="n">
-        <v>-14.97</v>
+        <v>-298.449</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-9.409999999999997</v>
+        <v>-831.8530000000001</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>1</v>
+        <v>3.147000000000001</v>
       </c>
       <c r="AM4" t="n">
-        <v>-8.409999999999997</v>
+        <v>-828.7059999999999</v>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2035</t>
+          <t>7547</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>唐榮公司</t>
+          <t>碩網</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1081,49 +1081,49 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>26.89999961853027</v>
+        <v>50.20000076293945</v>
       </c>
       <c r="G5" t="n">
-        <v>26.98000001907349</v>
+        <v>50.66999950408935</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>49.21733687559828</v>
+        <v>42.31673194004082</v>
       </c>
       <c r="J5" t="n">
-        <v>47.60871879792085</v>
+        <v>33.44627033046578</v>
       </c>
       <c r="K5" t="n">
-        <v>47.83740380717153</v>
+        <v>46.70427731132254</v>
       </c>
       <c r="L5" t="n">
-        <v>8900.4</v>
+        <v>29658.6</v>
       </c>
       <c r="M5" t="n">
-        <v>4527.15</v>
+        <v>16317.4</v>
       </c>
       <c r="N5" t="n">
-        <v>4371.475</v>
+        <v>19059.475</v>
       </c>
       <c r="O5" t="n">
-        <v>1.966005102547961</v>
+        <v>1.817605746013458</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.06173592214328849</v>
+        <v>-0.6986777455452682</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.09958961854682309</v>
+        <v>-0.735866658166582</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0378536964035346</v>
+        <v>0.03718891262131385</v>
       </c>
       <c r="S5" t="n">
-        <v>0.04144755281917308</v>
+        <v>-0.01718704951946504</v>
       </c>
       <c r="T5" t="n">
-        <v>0.03002840241648751</v>
+        <v>-0.1629380206734168</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
@@ -1213,63 +1213,63 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3346</t>
+          <t>4953</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>麗清</t>
+          <t>緯致</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>19.29999923706055</v>
+        <v>121</v>
       </c>
       <c r="G6" t="n">
-        <v>19.60999994277954</v>
+        <v>121.1</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>44.73112456571825</v>
+        <v>41.35391703787671</v>
       </c>
       <c r="J6" t="n">
-        <v>37.99095337286886</v>
+        <v>31.72541155025957</v>
       </c>
       <c r="K6" t="n">
-        <v>44.34632401496682</v>
+        <v>47.15788545709405</v>
       </c>
       <c r="L6" t="n">
-        <v>656345.6</v>
+        <v>367634.4</v>
       </c>
       <c r="M6" t="n">
-        <v>343879.85</v>
+        <v>212079</v>
       </c>
       <c r="N6" t="n">
-        <v>345745.025</v>
+        <v>254893.175</v>
       </c>
       <c r="O6" t="n">
-        <v>1.908648035062246</v>
+        <v>1.733478562233885</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.4173971035858699</v>
+        <v>-1.173998670369386</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.5184136045501052</v>
+        <v>-1.299501446332937</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1010165009642353</v>
+        <v>0.1255027759635514</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1046405307816412</v>
+        <v>-0.005459447640173476</v>
       </c>
       <c r="T6" t="n">
-        <v>0.09939678937226193</v>
+        <v>-0.1945889012733262</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1319,32 +1319,32 @@
         <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>-367.055</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.703000000000001</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>-365.352</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-882.895</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>3.817000000000001</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>-879.0779999999999</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
@@ -1376,46 +1376,46 @@
         <v>11.25</v>
       </c>
       <c r="G7" t="n">
-        <v>11.475</v>
+        <v>11.46750001907349</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>43.32011404443771</v>
+        <v>39.99116359294389</v>
       </c>
       <c r="J7" t="n">
-        <v>37.02570263424967</v>
+        <v>38.01418961529213</v>
       </c>
       <c r="K7" t="n">
-        <v>37.26563125359729</v>
+        <v>36.6382687600792</v>
       </c>
       <c r="L7" t="n">
-        <v>24891.4</v>
+        <v>24326.6</v>
       </c>
       <c r="M7" t="n">
-        <v>15019.9</v>
+        <v>15278.95</v>
       </c>
       <c r="N7" t="n">
-        <v>14731.1</v>
+        <v>14735.625</v>
       </c>
       <c r="O7" t="n">
-        <v>1.657228077417293</v>
+        <v>1.592164383023702</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.0734608769618923</v>
+        <v>-0.08085514768273505</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.06134059694198695</v>
+        <v>-0.06563609630193987</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.01212028001990535</v>
+        <v>-0.01521905138079518</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.005040175021427222</v>
+        <v>-0.011964643410467</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.002656351311715079</v>
+        <v>-0.004872339304104148</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2608</t>
+          <t>6645</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>嘉里大榮</t>
+          <t>金萬林-創</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1519,49 +1519,49 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>28.60000038146973</v>
+        <v>12.64999961853027</v>
       </c>
       <c r="G8" t="n">
-        <v>28.61499996185303</v>
+        <v>12.63499989509583</v>
       </c>
       <c r="H8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>32.38510259863372</v>
+        <v>39.13213431878399</v>
       </c>
       <c r="J8" t="n">
-        <v>30.99057606056034</v>
+        <v>36.72072401999707</v>
       </c>
       <c r="K8" t="n">
-        <v>47.82558606939766</v>
+        <v>47.06731149353106</v>
       </c>
       <c r="L8" t="n">
-        <v>394708.6</v>
+        <v>44131.8</v>
       </c>
       <c r="M8" t="n">
-        <v>242058.7</v>
+        <v>28116.7</v>
       </c>
       <c r="N8" t="n">
-        <v>262455</v>
+        <v>27329.575</v>
       </c>
       <c r="O8" t="n">
-        <v>1.630631743457269</v>
+        <v>1.569593871258007</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.0390910268463287</v>
+        <v>-0.1825177100290745</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.07441211820317017</v>
+        <v>-0.2700284224956727</v>
       </c>
       <c r="R8" t="n">
-        <v>0.03532109135684147</v>
+        <v>0.08751071246659825</v>
       </c>
       <c r="S8" t="n">
-        <v>0.04404443177368969</v>
+        <v>0.09319885509086956</v>
       </c>
       <c r="T8" t="n">
-        <v>0.04021651876430968</v>
+        <v>0.09872512167908232</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -1599,336 +1599,44 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>-88</v>
+        <v>-6</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>5.959</v>
+        <v>-17</v>
       </c>
       <c r="AE8" t="n">
-        <v>-82.041</v>
+        <v>-23</v>
       </c>
       <c r="AF8" t="n">
-        <v>-172.227</v>
+        <v>-7</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>27.213</v>
+        <v>-36.286</v>
       </c>
       <c r="AI8" t="n">
-        <v>-145.014</v>
+        <v>-43.286</v>
       </c>
       <c r="AJ8" t="n">
-        <v>-687.8420000000001</v>
+        <v>20.528</v>
       </c>
       <c r="AK8" t="n">
         <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>15.352</v>
+        <v>-48.195</v>
       </c>
       <c r="AM8" t="n">
-        <v>-672.49</v>
+        <v>-27.667</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>70</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>5212</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>凌網</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>46.34999847412109</v>
-      </c>
-      <c r="G9" t="n">
-        <v>46.59750003814698</v>
-      </c>
-      <c r="H9" t="b">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>47.64762642686387</v>
-      </c>
-      <c r="J9" t="n">
-        <v>44.32919797250486</v>
-      </c>
-      <c r="K9" t="n">
-        <v>44.93952246294608</v>
-      </c>
-      <c r="L9" t="n">
-        <v>14717.8</v>
-      </c>
-      <c r="M9" t="n">
-        <v>9080.25</v>
-      </c>
-      <c r="N9" t="n">
-        <v>7490.7</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.620858456540293</v>
-      </c>
-      <c r="P9" t="n">
-        <v>-0.1065821190914278</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>-0.1232930226543603</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.01671090356293253</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.03534973315428425</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0.01816647589076786</v>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>70</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>8171</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>天宇</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>19.79999923706055</v>
-      </c>
-      <c r="G10" t="n">
-        <v>19.80249996185303</v>
-      </c>
-      <c r="H10" t="b">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>47.34680897278013</v>
-      </c>
-      <c r="J10" t="n">
-        <v>47.06915737543887</v>
-      </c>
-      <c r="K10" t="n">
-        <v>47.90412596045189</v>
-      </c>
-      <c r="L10" t="n">
-        <v>205420.2</v>
-      </c>
-      <c r="M10" t="n">
-        <v>129896.9</v>
-      </c>
-      <c r="N10" t="n">
-        <v>106662.425</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.581409564046563</v>
-      </c>
-      <c r="P10" t="n">
-        <v>-0.03303016645965329</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>-0.05413263120931249</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.0211024647496592</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.02652463747027661</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0.03382116332097197</v>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN8"/>
+  <dimension ref="A1:AN9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,67 +625,67 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4930</t>
+          <t>8923</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>燦星網</t>
+          <t>時報</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>16.10000038146973</v>
+        <v>18.5</v>
       </c>
       <c r="G2" t="n">
-        <v>16.09750013351441</v>
+        <v>18.56750011444092</v>
       </c>
       <c r="H2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>39.757641097281</v>
+        <v>45.99591622757954</v>
       </c>
       <c r="J2" t="n">
-        <v>39.5653735526485</v>
+        <v>35.22650233995557</v>
       </c>
       <c r="K2" t="n">
-        <v>48.95453942892726</v>
+        <v>48.77631556349957</v>
       </c>
       <c r="L2" t="n">
-        <v>81670.8</v>
+        <v>19000</v>
       </c>
       <c r="M2" t="n">
-        <v>32720.75</v>
+        <v>6400.35</v>
       </c>
       <c r="N2" t="n">
-        <v>58465.35</v>
+        <v>9158</v>
       </c>
       <c r="O2" t="n">
-        <v>2.495994132163841</v>
+        <v>2.968587655362597</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.08801242887535565</v>
+        <v>-0.1309539410510183</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.08417019948365545</v>
+        <v>-0.1246706032558998</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.003842229391700203</v>
+        <v>-0.006283337795118554</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.01865661834749327</v>
+        <v>-0.02032280119394417</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.01915789471663962</v>
+        <v>-0.03923185960683606</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -732,10 +732,10 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
@@ -744,19 +744,19 @@
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>23.709</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>22.709</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
@@ -771,16 +771,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1441</t>
+          <t>4930</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>大東</t>
+          <t>燦星網</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -789,49 +789,49 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>8.720000267028809</v>
+        <v>16.14999961853027</v>
       </c>
       <c r="G3" t="n">
-        <v>8.840499925613404</v>
+        <v>16.09500007629395</v>
       </c>
       <c r="H3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>42.83500320322867</v>
+        <v>47.93366225065424</v>
       </c>
       <c r="J3" t="n">
-        <v>34.87556923249954</v>
+        <v>42.3548031383684</v>
       </c>
       <c r="K3" t="n">
-        <v>44.29068228982177</v>
+        <v>49.96518740466649</v>
       </c>
       <c r="L3" t="n">
-        <v>47668.4</v>
+        <v>96758.8</v>
       </c>
       <c r="M3" t="n">
-        <v>21749.45</v>
+        <v>36033.3</v>
       </c>
       <c r="N3" t="n">
-        <v>17031.5</v>
+        <v>59777.8</v>
       </c>
       <c r="O3" t="n">
-        <v>2.191705997163147</v>
+        <v>2.685260578409415</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.07785466714476996</v>
+        <v>-0.07216675353244639</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.06654456174527329</v>
+        <v>-0.08176951029341364</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.01131010539949667</v>
+        <v>0.009602756760967252</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0165890448942871</v>
+        <v>-0.003842229391700203</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.01149705012827114</v>
+        <v>-0.01865661834749327</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -878,10 +878,10 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-25.97</v>
+        <v>9</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -890,23 +890,23 @@
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>-25.97</v>
+        <v>9</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-11.41</v>
+        <v>16.709</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AM3" t="n">
-        <v>-10.41</v>
+        <v>15.709</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3346</t>
+          <t>1441</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>麗清</t>
+          <t>大東</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,124 +935,124 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>19.75</v>
+        <v>10.00464725494385</v>
       </c>
       <c r="G4" t="n">
-        <v>19.60249996185303</v>
+        <v>10.27713174819946</v>
       </c>
       <c r="H4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>32.77107519753392</v>
+      </c>
+      <c r="J4" t="n">
+        <v>30.89592353687041</v>
+      </c>
+      <c r="K4" t="n">
+        <v>39.01788144327882</v>
+      </c>
+      <c r="L4" t="n">
+        <v>40943.6</v>
+      </c>
+      <c r="M4" t="n">
+        <v>17836.25</v>
+      </c>
+      <c r="N4" t="n">
+        <v>14847.75</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.295527367019413</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-0.0933981463153728</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-0.07416103156286386</v>
+      </c>
+      <c r="R4" t="n">
+        <v>-0.01923711475250894</v>
+      </c>
+      <c r="S4" t="n">
+        <v>-0.01331728347509598</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-0.01831345406637405</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>-25.97</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>-25.97</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>-12.41</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
         <v>1</v>
       </c>
-      <c r="I4" t="n">
-        <v>49.95963639245484</v>
-      </c>
-      <c r="J4" t="n">
-        <v>41.98051439225708</v>
-      </c>
-      <c r="K4" t="n">
-        <v>48.74302681866537</v>
-      </c>
-      <c r="L4" t="n">
-        <v>678310.6</v>
-      </c>
-      <c r="M4" t="n">
-        <v>340421.1</v>
-      </c>
-      <c r="N4" t="n">
-        <v>341490.65</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.992563328183829</v>
-      </c>
-      <c r="P4" t="n">
-        <v>-0.3576237721918716</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>-0.483507468666879</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.1258836964750074</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.09992702688669475</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0.1034656615528102</v>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB4" t="n">
-        <v>54.042</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>54.042</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>-300.123</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.674000000000001</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>-298.449</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>-831.8530000000001</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>3.147000000000001</v>
-      </c>
       <c r="AM4" t="n">
-        <v>-828.7059999999999</v>
+        <v>-11.41</v>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
     </row>
@@ -1067,63 +1067,63 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>7547</t>
+          <t>3704</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>碩網</t>
+          <t>合勤控</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>50.20000076293945</v>
+        <v>40.29999923706055</v>
       </c>
       <c r="G5" t="n">
-        <v>50.66999950408935</v>
+        <v>40.81500053405762</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>42.31673194004082</v>
+        <v>35.52854598107042</v>
       </c>
       <c r="J5" t="n">
-        <v>33.44627033046578</v>
+        <v>30.48668986309131</v>
       </c>
       <c r="K5" t="n">
-        <v>46.70427731132254</v>
+        <v>44.14316916141746</v>
       </c>
       <c r="L5" t="n">
-        <v>29658.6</v>
+        <v>4290320.8</v>
       </c>
       <c r="M5" t="n">
-        <v>16317.4</v>
+        <v>2232536.15</v>
       </c>
       <c r="N5" t="n">
-        <v>19059.475</v>
+        <v>3016809.35</v>
       </c>
       <c r="O5" t="n">
-        <v>1.817605746013458</v>
+        <v>1.921725119658197</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.6986777455452682</v>
+        <v>-0.9672157702981607</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.735866658166582</v>
+        <v>-1.10872907001128</v>
       </c>
       <c r="R5" t="n">
-        <v>0.03718891262131385</v>
+        <v>0.1415132997131197</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.01718704951946504</v>
+        <v>0.1115562785657858</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1629380206734168</v>
+        <v>0.08634510786556859</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1161,44 +1161,44 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>87.059</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.374</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>88.43299999999999</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>-4456.375</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>-139.562</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>-4595.937</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>-10940.416</v>
       </c>
       <c r="AK5" t="n">
         <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>8.735000000000007</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>-10931.681</v>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
@@ -1213,12 +1213,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4953</t>
+          <t>7547</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>緯致</t>
+          <t>碩網</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1227,49 +1227,49 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>121</v>
+        <v>49.70000076293945</v>
       </c>
       <c r="G6" t="n">
-        <v>121.1</v>
+        <v>50.43499946594238</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>41.35391703787671</v>
+        <v>40.92594099005651</v>
       </c>
       <c r="J6" t="n">
-        <v>31.72541155025957</v>
+        <v>35.93949389774694</v>
       </c>
       <c r="K6" t="n">
-        <v>47.15788545709405</v>
+        <v>45.16140971452066</v>
       </c>
       <c r="L6" t="n">
-        <v>367634.4</v>
+        <v>30020.4</v>
       </c>
       <c r="M6" t="n">
-        <v>212079</v>
+        <v>16107.85</v>
       </c>
       <c r="N6" t="n">
-        <v>254893.175</v>
+        <v>18979.7</v>
       </c>
       <c r="O6" t="n">
-        <v>1.733478562233885</v>
+        <v>1.863712413512666</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.173998670369386</v>
+        <v>-0.68071524322729</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.299501446332937</v>
+        <v>-0.7248363751787237</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1255027759635514</v>
+        <v>0.04412113195143363</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.005459447640173476</v>
+        <v>0.03718891262131385</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1945889012733262</v>
+        <v>-0.01718704951946504</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
@@ -1359,63 +1359,63 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1813</t>
+          <t>7803</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>寶利徠</t>
+          <t>雲象科技-創</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>11.25</v>
+        <v>19.29999923706055</v>
       </c>
       <c r="G7" t="n">
-        <v>11.46750001907349</v>
+        <v>19.25249996185303</v>
       </c>
       <c r="H7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>39.99116359294389</v>
+        <v>42.12033893125158</v>
       </c>
       <c r="J7" t="n">
-        <v>38.01418961529213</v>
+        <v>39.95662844463997</v>
       </c>
       <c r="K7" t="n">
-        <v>36.6382687600792</v>
+        <v>48.66654012999673</v>
       </c>
       <c r="L7" t="n">
-        <v>24326.6</v>
+        <v>76768.60000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>15278.95</v>
+        <v>41672.9</v>
       </c>
       <c r="N7" t="n">
-        <v>14735.625</v>
+        <v>48836.45</v>
       </c>
       <c r="O7" t="n">
-        <v>1.592164383023702</v>
+        <v>1.842170811246638</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.08085514768273505</v>
+        <v>-0.3144826074763039</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.06563609630193987</v>
+        <v>-0.3222309082536988</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.01521905138079518</v>
+        <v>0.007748300777394967</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.011964643410467</v>
+        <v>-0.03873629122699818</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.004872339304104148</v>
+        <v>0.007054433011096872</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -1453,44 +1453,44 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>-32</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>-36</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>-66</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>-0.6360000000000001</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-66.636</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>-5.169</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>10.482</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>5.313000000000004</v>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
@@ -1505,138 +1505,284 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>6645</t>
+          <t>4953</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>金萬林-創</t>
+          <t>緯致</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>119</v>
+      </c>
+      <c r="G8" t="n">
+        <v>120.9</v>
+      </c>
+      <c r="H8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>36.82853728517861</v>
+      </c>
+      <c r="J8" t="n">
+        <v>33.42645347481792</v>
+      </c>
+      <c r="K8" t="n">
+        <v>41.68573427872012</v>
+      </c>
+      <c r="L8" t="n">
+        <v>394259.6</v>
+      </c>
+      <c r="M8" t="n">
+        <v>222686</v>
+      </c>
+      <c r="N8" t="n">
+        <v>254541.725</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.770473222384883</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-1.180561733885469</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-1.260009695750203</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.07944796186473435</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.1192772165915039</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-0.01217297877346102</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>70</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1418</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>東華</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="F8" t="n">
-        <v>12.64999961853027</v>
-      </c>
-      <c r="G8" t="n">
-        <v>12.63499989509583</v>
-      </c>
-      <c r="H8" t="b">
+      <c r="F9" t="n">
+        <v>17.60000038146973</v>
+      </c>
+      <c r="G9" t="n">
+        <v>17.69499998092651</v>
+      </c>
+      <c r="H9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>45.89576325315176</v>
+      </c>
+      <c r="J9" t="n">
+        <v>43.59996596974185</v>
+      </c>
+      <c r="K9" t="n">
+        <v>45.78462461261086</v>
+      </c>
+      <c r="L9" t="n">
+        <v>24905</v>
+      </c>
+      <c r="M9" t="n">
+        <v>15534.35</v>
+      </c>
+      <c r="N9" t="n">
+        <v>15059.575</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.603221248394687</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-0.1065680220032057</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-0.1282379862307939</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.02166996422758816</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.02377295334781027</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-0.003461403666907614</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
         <v>1</v>
       </c>
-      <c r="I8" t="n">
-        <v>39.13213431878399</v>
-      </c>
-      <c r="J8" t="n">
-        <v>36.72072401999707</v>
-      </c>
-      <c r="K8" t="n">
-        <v>47.06731149353106</v>
-      </c>
-      <c r="L8" t="n">
-        <v>44131.8</v>
-      </c>
-      <c r="M8" t="n">
-        <v>28116.7</v>
-      </c>
-      <c r="N8" t="n">
-        <v>27329.575</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.569593871258007</v>
-      </c>
-      <c r="P8" t="n">
-        <v>-0.1825177100290745</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>-0.2700284224956727</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.08751071246659825</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.09319885509086956</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0.09872512167908232</v>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB8" t="n">
-        <v>-6</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>-17</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>-23</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>-7</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>-36.286</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>-43.286</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>20.528</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>-48.195</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>-27.667</v>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>3.415</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>4.415</v>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN9"/>
+  <dimension ref="A1:AN7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -629,12 +629,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8923</t>
+          <t>7716</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>時報</t>
+          <t>昱臺國際</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -643,49 +643,49 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>18.5</v>
+        <v>23.5</v>
       </c>
       <c r="G2" t="n">
-        <v>18.56750011444092</v>
+        <v>23.73499994277954</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>45.99591622757954</v>
+        <v>40.85123843466386</v>
       </c>
       <c r="J2" t="n">
-        <v>35.22650233995557</v>
+        <v>36.36211058258015</v>
       </c>
       <c r="K2" t="n">
-        <v>48.77631556349957</v>
+        <v>40.28235607169909</v>
       </c>
       <c r="L2" t="n">
-        <v>19000</v>
+        <v>9600</v>
       </c>
       <c r="M2" t="n">
-        <v>6400.35</v>
+        <v>4750</v>
       </c>
       <c r="N2" t="n">
-        <v>9158</v>
+        <v>4475.05</v>
       </c>
       <c r="O2" t="n">
-        <v>2.968587655362597</v>
+        <v>2.021052631578947</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.1309539410510183</v>
+        <v>-0.2359859474591559</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.1246706032558998</v>
+        <v>-0.2217119899087349</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.006283337795118554</v>
+        <v>-0.01427395755042102</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.02032280119394417</v>
+        <v>-0.03313922610944808</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.03923185960683606</v>
+        <v>-0.03692954980168955</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>
@@ -771,16 +771,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4930</t>
+          <t>1441</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>燦星網</t>
+          <t>大東</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -789,120 +789,120 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>16.14999961853027</v>
+        <v>10.13247013092041</v>
       </c>
       <c r="G3" t="n">
-        <v>16.09500007629395</v>
+        <v>10.27248406410217</v>
       </c>
       <c r="H3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>41.29245485957468</v>
+      </c>
+      <c r="J3" t="n">
+        <v>34.36143402060745</v>
+      </c>
+      <c r="K3" t="n">
+        <v>43.50704937428907</v>
+      </c>
+      <c r="L3" t="n">
+        <v>35829.4</v>
+      </c>
+      <c r="M3" t="n">
+        <v>17418.65</v>
+      </c>
+      <c r="N3" t="n">
+        <v>14007.6</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.056956193505237</v>
+      </c>
+      <c r="P3" t="n">
+        <v>-0.09155209531634334</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-0.07891451523216587</v>
+      </c>
+      <c r="R3" t="n">
+        <v>-0.01263758008417747</v>
+      </c>
+      <c r="S3" t="n">
+        <v>-0.01873243857919472</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-0.01277320973984533</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>-25.97</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>-25.97</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>-12.41</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
         <v>1</v>
       </c>
-      <c r="I3" t="n">
-        <v>47.93366225065424</v>
-      </c>
-      <c r="J3" t="n">
-        <v>42.3548031383684</v>
-      </c>
-      <c r="K3" t="n">
-        <v>49.96518740466649</v>
-      </c>
-      <c r="L3" t="n">
-        <v>96758.8</v>
-      </c>
-      <c r="M3" t="n">
-        <v>36033.3</v>
-      </c>
-      <c r="N3" t="n">
-        <v>59777.8</v>
-      </c>
-      <c r="O3" t="n">
-        <v>2.685260578409415</v>
-      </c>
-      <c r="P3" t="n">
-        <v>-0.07216675353244639</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>-0.08176951029341364</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.009602756760967252</v>
-      </c>
-      <c r="S3" t="n">
-        <v>-0.003842229391700203</v>
-      </c>
-      <c r="T3" t="n">
-        <v>-0.01865661834749327</v>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>9</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>9</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>16.709</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>-1</v>
-      </c>
       <c r="AM3" t="n">
-        <v>15.709</v>
+        <v>-11.41</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
@@ -921,63 +921,63 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1441</t>
+          <t>7547</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>大東</t>
+          <t>碩網</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>10.00464725494385</v>
+        <v>49.95000076293945</v>
       </c>
       <c r="G4" t="n">
-        <v>10.27713174819946</v>
+        <v>50.2774995803833</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>32.77107519753392</v>
+        <v>41.7169592707027</v>
       </c>
       <c r="J4" t="n">
-        <v>30.89592353687041</v>
+        <v>37.86531569786978</v>
       </c>
       <c r="K4" t="n">
-        <v>39.01788144327882</v>
+        <v>46.19581221115337</v>
       </c>
       <c r="L4" t="n">
-        <v>40943.6</v>
+        <v>30004.2</v>
       </c>
       <c r="M4" t="n">
-        <v>17836.25</v>
+        <v>15803.8</v>
       </c>
       <c r="N4" t="n">
-        <v>14847.75</v>
+        <v>18552.675</v>
       </c>
       <c r="O4" t="n">
-        <v>2.295527367019413</v>
+        <v>1.898543388299017</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.0933981463153728</v>
+        <v>-0.6457694912113396</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.07416103156286386</v>
+        <v>-0.7176600808554757</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.01923711475250894</v>
+        <v>0.07189058964413608</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.01331728347509598</v>
+        <v>0.04754518485633286</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.01831345406637405</v>
+        <v>0.0408813496225986</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1024,10 +1024,10 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>-25.97</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
@@ -1036,23 +1036,23 @@
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>-25.97</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-12.41</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>-11.41</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>
@@ -1067,63 +1067,63 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3704</t>
+          <t>8044</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>合勤控</t>
+          <t>網家</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>40.29999923706055</v>
+        <v>23.5</v>
       </c>
       <c r="G5" t="n">
-        <v>40.81500053405762</v>
+        <v>24.00999994277954</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>35.52854598107042</v>
+        <v>46.68093477017568</v>
       </c>
       <c r="J5" t="n">
-        <v>30.48668986309131</v>
+        <v>38.60833149624967</v>
       </c>
       <c r="K5" t="n">
-        <v>44.14316916141746</v>
+        <v>39.35175073591686</v>
       </c>
       <c r="L5" t="n">
-        <v>4290320.8</v>
+        <v>1021480.8</v>
       </c>
       <c r="M5" t="n">
-        <v>2232536.15</v>
+        <v>545988.25</v>
       </c>
       <c r="N5" t="n">
-        <v>3016809.35</v>
+        <v>463841.45</v>
       </c>
       <c r="O5" t="n">
-        <v>1.921725119658197</v>
+        <v>1.870884217746444</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.9672157702981607</v>
+        <v>-0.6109523167268378</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.10872907001128</v>
+        <v>-0.7118759137388808</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1415132997131197</v>
+        <v>0.100923597012043</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1115562785657858</v>
+        <v>0.1094116456041992</v>
       </c>
       <c r="T5" t="n">
-        <v>0.08634510786556859</v>
+        <v>0.05325189782446904</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1161,44 +1161,44 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>87.059</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.374</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>88.43299999999999</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>-4456.375</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-139.562</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>-4595.937</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-10940.416</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
         <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>8.735000000000007</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>-10931.681</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>
@@ -1213,63 +1213,63 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>7547</t>
+          <t>7803</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>碩網</t>
+          <t>雲象科技-創</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>49.70000076293945</v>
+        <v>18.89999961853027</v>
       </c>
       <c r="G6" t="n">
-        <v>50.43499946594238</v>
+        <v>19.21749992370605</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>40.92594099005651</v>
+        <v>46.7468875335931</v>
       </c>
       <c r="J6" t="n">
-        <v>35.93949389774694</v>
+        <v>42.2200481220445</v>
       </c>
       <c r="K6" t="n">
-        <v>45.16140971452066</v>
+        <v>44.15734507041385</v>
       </c>
       <c r="L6" t="n">
-        <v>30020.4</v>
+        <v>80580.8</v>
       </c>
       <c r="M6" t="n">
-        <v>16107.85</v>
+        <v>43875.95</v>
       </c>
       <c r="N6" t="n">
-        <v>18979.7</v>
+        <v>48837.975</v>
       </c>
       <c r="O6" t="n">
-        <v>1.863712413512666</v>
+        <v>1.83655966423519</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.68071524322729</v>
+        <v>-0.3048703579301169</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.7248363751787237</v>
+        <v>-0.3187587981889825</v>
       </c>
       <c r="R6" t="n">
-        <v>0.04412113195143363</v>
+        <v>0.0138884402588656</v>
       </c>
       <c r="S6" t="n">
-        <v>0.03718891262131385</v>
+        <v>0.007748300777394967</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.01718704951946504</v>
+        <v>-0.03873629122699818</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1307,44 +1307,44 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>-1.787</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>9.213000000000001</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>-53</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>-5.388</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>-58.388</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>11.831</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>7.418999999999999</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>19.25</v>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>
@@ -1359,12 +1359,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>7803</t>
+          <t>3704</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>雲象科技-創</t>
+          <t>合勤控</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1373,49 +1373,49 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>19.29999923706055</v>
+        <v>41.15000152587891</v>
       </c>
       <c r="G7" t="n">
-        <v>19.25249996185303</v>
+        <v>40.79000053405762</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>42.12033893125158</v>
+        <v>45.28195154210098</v>
       </c>
       <c r="J7" t="n">
-        <v>39.95662844463997</v>
+        <v>35.4184437590114</v>
       </c>
       <c r="K7" t="n">
-        <v>48.66654012999673</v>
+        <v>48.84014468566346</v>
       </c>
       <c r="L7" t="n">
-        <v>76768.60000000001</v>
+        <v>4035421.2</v>
       </c>
       <c r="M7" t="n">
-        <v>41672.9</v>
+        <v>2210211.6</v>
       </c>
       <c r="N7" t="n">
-        <v>48836.45</v>
+        <v>2972438.9</v>
       </c>
       <c r="O7" t="n">
-        <v>1.842170811246638</v>
+        <v>1.82580762855466</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.3144826074763039</v>
+        <v>-0.8303703643390534</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.3222309082536988</v>
+        <v>-1.044420246406624</v>
       </c>
       <c r="R7" t="n">
-        <v>0.007748300777394967</v>
+        <v>0.2140498820675709</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.03873629122699818</v>
+        <v>0.1380892468082215</v>
       </c>
       <c r="T7" t="n">
-        <v>0.007054433011096872</v>
+        <v>0.1078638415645023</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -1453,336 +1453,44 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>-32</v>
+        <v>914</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>-4</v>
+        <v>22.54</v>
       </c>
       <c r="AE7" t="n">
-        <v>-36</v>
+        <v>936.54</v>
       </c>
       <c r="AF7" t="n">
-        <v>-66</v>
+        <v>-3000.393</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0.6360000000000001</v>
+        <v>-25.413</v>
       </c>
       <c r="AI7" t="n">
-        <v>-66.636</v>
+        <v>-3025.806</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-5.169</v>
+        <v>-9317.315999999997</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>10.482</v>
+        <v>26.43800000000002</v>
       </c>
       <c r="AM7" t="n">
-        <v>5.313000000000004</v>
+        <v>-9290.877999999999</v>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>70</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>4953</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>緯致</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>119</v>
-      </c>
-      <c r="G8" t="n">
-        <v>120.9</v>
-      </c>
-      <c r="H8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>36.82853728517861</v>
-      </c>
-      <c r="J8" t="n">
-        <v>33.42645347481792</v>
-      </c>
-      <c r="K8" t="n">
-        <v>41.68573427872012</v>
-      </c>
-      <c r="L8" t="n">
-        <v>394259.6</v>
-      </c>
-      <c r="M8" t="n">
-        <v>222686</v>
-      </c>
-      <c r="N8" t="n">
-        <v>254541.725</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.770473222384883</v>
-      </c>
-      <c r="P8" t="n">
-        <v>-1.180561733885469</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>-1.260009695750203</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.07944796186473435</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.1192772165915039</v>
-      </c>
-      <c r="T8" t="n">
-        <v>-0.01217297877346102</v>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>70</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1418</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>東華</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>17.60000038146973</v>
-      </c>
-      <c r="G9" t="n">
-        <v>17.69499998092651</v>
-      </c>
-      <c r="H9" t="b">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>45.89576325315176</v>
-      </c>
-      <c r="J9" t="n">
-        <v>43.59996596974185</v>
-      </c>
-      <c r="K9" t="n">
-        <v>45.78462461261086</v>
-      </c>
-      <c r="L9" t="n">
-        <v>24905</v>
-      </c>
-      <c r="M9" t="n">
-        <v>15534.35</v>
-      </c>
-      <c r="N9" t="n">
-        <v>15059.575</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.603221248394687</v>
-      </c>
-      <c r="P9" t="n">
-        <v>-0.1065680220032057</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>-0.1282379862307939</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.02166996422758816</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.02377295334781027</v>
-      </c>
-      <c r="T9" t="n">
-        <v>-0.003461403666907614</v>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>3.415</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>4.415</v>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN7"/>
+  <dimension ref="A1:AN9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -652,13 +652,13 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>40.85123843466386</v>
+        <v>40.85123843357112</v>
       </c>
       <c r="J2" t="n">
-        <v>36.36211058258015</v>
+        <v>36.36211056145378</v>
       </c>
       <c r="K2" t="n">
-        <v>40.28235607169909</v>
+        <v>43.43424497686013</v>
       </c>
       <c r="L2" t="n">
         <v>9600</v>
@@ -673,19 +673,19 @@
         <v>2.021052631578947</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.2359859474591559</v>
+        <v>-0.2296189469922219</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.2217119899087349</v>
+        <v>-0.2123878463652206</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.01427395755042102</v>
+        <v>-0.01723110062700123</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.03313922610944808</v>
+        <v>-0.03632815595876049</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.03692954980168955</v>
+        <v>-0.04036795156828349</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -771,71 +771,71 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1441</t>
+          <t>5348</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>大東</t>
+          <t>正能量智能</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>10.13247013092041</v>
+        <v>16.39999961853027</v>
       </c>
       <c r="G3" t="n">
-        <v>10.27248406410217</v>
+        <v>16.40749988555908</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>41.29245485957468</v>
+        <v>46.33115137164528</v>
       </c>
       <c r="J3" t="n">
-        <v>34.36143402060745</v>
+        <v>42.95432092571004</v>
       </c>
       <c r="K3" t="n">
-        <v>43.50704937428907</v>
+        <v>49.9639570133517</v>
       </c>
       <c r="L3" t="n">
-        <v>35829.4</v>
+        <v>6742.2</v>
       </c>
       <c r="M3" t="n">
-        <v>17418.65</v>
+        <v>3626.75</v>
       </c>
       <c r="N3" t="n">
-        <v>14007.6</v>
+        <v>4849.825</v>
       </c>
       <c r="O3" t="n">
-        <v>2.056956193505237</v>
+        <v>1.859019783552768</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.09155209531634334</v>
+        <v>-0.1465746553403804</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.07891451523216587</v>
+        <v>-0.1042086752320918</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.01263758008417747</v>
+        <v>-0.04236598010828854</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.01873243857919472</v>
+        <v>-0.080039364776929</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.01277320973984533</v>
+        <v>-0.08627146933421144</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -878,10 +878,10 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-25.97</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -890,23 +890,23 @@
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>-25.97</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-12.41</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>-11.41</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>
@@ -944,40 +944,40 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>41.7169592707027</v>
+        <v>41.7169592702656</v>
       </c>
       <c r="J4" t="n">
-        <v>37.86531569786978</v>
+        <v>37.86531568941921</v>
       </c>
       <c r="K4" t="n">
-        <v>46.19581221115337</v>
+        <v>45.05293664644619</v>
       </c>
       <c r="L4" t="n">
-        <v>30004.2</v>
+        <v>30000</v>
       </c>
       <c r="M4" t="n">
-        <v>15803.8</v>
+        <v>15802.75</v>
       </c>
       <c r="N4" t="n">
-        <v>18552.675</v>
+        <v>18552.15</v>
       </c>
       <c r="O4" t="n">
-        <v>1.898543388299017</v>
+        <v>1.898403758839442</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.6457694912113396</v>
+        <v>-0.6497907667745721</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.7176600808554757</v>
+        <v>-0.7235490313549127</v>
       </c>
       <c r="R4" t="n">
-        <v>0.07189058964413608</v>
+        <v>0.07375826458034052</v>
       </c>
       <c r="S4" t="n">
-        <v>0.04754518485633286</v>
+        <v>0.04955925187934496</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0408813496225986</v>
+        <v>0.04305297833103405</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>8044</t>
+          <t>3128</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>網家</t>
+          <t>昇銳</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1081,49 +1081,49 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>23.5</v>
+        <v>20.45000076293945</v>
       </c>
       <c r="G5" t="n">
-        <v>24.00999994277954</v>
+        <v>20.39872636795044</v>
       </c>
       <c r="H5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>46.68093477017568</v>
+        <v>32.68649062534388</v>
       </c>
       <c r="J5" t="n">
-        <v>38.60833149624967</v>
+        <v>30.67321641659039</v>
       </c>
       <c r="K5" t="n">
-        <v>39.35175073591686</v>
+        <v>48.90317366615158</v>
       </c>
       <c r="L5" t="n">
-        <v>1021480.8</v>
+        <v>297091.4</v>
       </c>
       <c r="M5" t="n">
-        <v>545988.25</v>
+        <v>158380.45</v>
       </c>
       <c r="N5" t="n">
-        <v>463841.45</v>
+        <v>139728.275</v>
       </c>
       <c r="O5" t="n">
-        <v>1.870884217746444</v>
+        <v>1.875808535712583</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.6109523167268378</v>
+        <v>-0.1290410820741492</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.7118759137388808</v>
+        <v>-0.1977556499677689</v>
       </c>
       <c r="R5" t="n">
-        <v>0.100923597012043</v>
+        <v>0.06871456789361968</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1094116456041992</v>
+        <v>0.06259006742728077</v>
       </c>
       <c r="T5" t="n">
-        <v>0.05325189782446904</v>
+        <v>0.07107393069868556</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1213,63 +1213,63 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>7803</t>
+          <t>8044</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>雲象科技-創</t>
+          <t>網家</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>18.89999961853027</v>
+        <v>23.5</v>
       </c>
       <c r="G6" t="n">
-        <v>19.21749992370605</v>
+        <v>24.00999994277954</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>46.7468875335931</v>
+        <v>46.68093477165367</v>
       </c>
       <c r="J6" t="n">
-        <v>42.2200481220445</v>
+        <v>38.60833152482403</v>
       </c>
       <c r="K6" t="n">
-        <v>44.15734507041385</v>
+        <v>37.5544318165702</v>
       </c>
       <c r="L6" t="n">
-        <v>80580.8</v>
+        <v>1021667.2</v>
       </c>
       <c r="M6" t="n">
-        <v>43875.95</v>
+        <v>546034.85</v>
       </c>
       <c r="N6" t="n">
-        <v>48837.975</v>
+        <v>463864.75</v>
       </c>
       <c r="O6" t="n">
-        <v>1.83655966423519</v>
+        <v>1.871065921891249</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.3048703579301169</v>
+        <v>-0.6119576292260263</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.3187587981889825</v>
+        <v>-0.7133481420035405</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0138884402588656</v>
+        <v>0.1013905127775142</v>
       </c>
       <c r="S6" t="n">
-        <v>0.007748300777394967</v>
+        <v>0.1099151591586901</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.03873629122699818</v>
+        <v>0.05379480154988203</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1307,40 +1307,40 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>-1.787</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>9.213000000000001</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>-53</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>-5.388</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>-58.388</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>11.831</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>7.418999999999999</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>19.25</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
@@ -1359,136 +1359,428 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>7803</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>雲象科技-創</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>18.89999961853027</v>
+      </c>
+      <c r="G7" t="n">
+        <v>19.21749992370605</v>
+      </c>
+      <c r="H7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>46.7468875328035</v>
+      </c>
+      <c r="J7" t="n">
+        <v>42.22004810677897</v>
+      </c>
+      <c r="K7" t="n">
+        <v>44.15734507041385</v>
+      </c>
+      <c r="L7" t="n">
+        <v>80400.39999999999</v>
+      </c>
+      <c r="M7" t="n">
+        <v>43830.85</v>
+      </c>
+      <c r="N7" t="n">
+        <v>48815.425</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.834333580115375</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-0.303194832837054</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-0.3163050781744171</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.01311024533736316</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.006909109385736634</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-0.03964113307048228</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>-2.483</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>-45</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.1290000000000002</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>-44.871</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>6.831</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>8.936</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>15.767</v>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>70</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>3704</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>合勤控</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="F7" t="n">
+      <c r="F8" t="n">
         <v>41.15000152587891</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G8" t="n">
         <v>40.79000053405762</v>
       </c>
-      <c r="H7" t="b">
+      <c r="H8" t="b">
         <v>1</v>
       </c>
-      <c r="I7" t="n">
-        <v>45.28195154210098</v>
-      </c>
-      <c r="J7" t="n">
-        <v>35.4184437590114</v>
-      </c>
-      <c r="K7" t="n">
-        <v>48.84014468566346</v>
-      </c>
-      <c r="L7" t="n">
-        <v>4035421.2</v>
-      </c>
-      <c r="M7" t="n">
-        <v>2210211.6</v>
-      </c>
-      <c r="N7" t="n">
-        <v>2972438.9</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.82580762855466</v>
-      </c>
-      <c r="P7" t="n">
-        <v>-0.8303703643390534</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>-1.044420246406624</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.2140498820675709</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.1380892468082215</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.1078638415645023</v>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB7" t="n">
-        <v>914</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>22.54</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>936.54</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>-3000.393</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>-25.413</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>-3025.806</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>-9317.315999999997</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>26.43800000000002</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>-9290.877999999999</v>
-      </c>
-      <c r="AN7" t="inlineStr">
+      <c r="I8" t="n">
+        <v>45.2819515431601</v>
+      </c>
+      <c r="J8" t="n">
+        <v>35.41844377948777</v>
+      </c>
+      <c r="K8" t="n">
+        <v>49.34549331163809</v>
+      </c>
+      <c r="L8" t="n">
+        <v>4034590.4</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2210003.9</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2972335.05</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.825603294184232</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-0.8320458894321163</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-1.046873966421186</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.2148280769890694</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.1389284381998714</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.1087686834079868</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>1260.245</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>14.011</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1274.256</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>-1750.663</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>39.09700000000001</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>-1711.566000000001</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>-8014.798</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>30.95900000000001</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>-7983.839</v>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>70</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2424</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>隴華</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>8.260000228881836</v>
+      </c>
+      <c r="G9" t="n">
+        <v>8.096500134468078</v>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>44.20798923436406</v>
+      </c>
+      <c r="J9" t="n">
+        <v>41.46311506258414</v>
+      </c>
+      <c r="K9" t="n">
+        <v>48.43761920194094</v>
+      </c>
+      <c r="L9" t="n">
+        <v>63334.8</v>
+      </c>
+      <c r="M9" t="n">
+        <v>37278.7</v>
+      </c>
+      <c r="N9" t="n">
+        <v>29617.9</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.698954094429259</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-0.09801899504610567</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-0.152198100591976</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.05417910554587033</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.04484055580129376</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.06729274935909771</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>-90.09999999999999</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>-90.09999999999999</v>
+      </c>
+      <c r="AN9" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN9"/>
+  <dimension ref="A1:AN17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -629,63 +629,63 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>7716</t>
+          <t>1737</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>昱臺國際</t>
+          <t>臺鹽</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>23.5</v>
+        <v>30.10000038146973</v>
       </c>
       <c r="G2" t="n">
-        <v>23.73499994277954</v>
+        <v>30.53499994277954</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>40.85123843357112</v>
+        <v>47.49047248818857</v>
       </c>
       <c r="J2" t="n">
-        <v>36.36211056145378</v>
+        <v>39.31324820895546</v>
       </c>
       <c r="K2" t="n">
-        <v>43.43424497686013</v>
+        <v>39.50095149094502</v>
       </c>
       <c r="L2" t="n">
-        <v>9600</v>
+        <v>1244992.8</v>
       </c>
       <c r="M2" t="n">
-        <v>4750</v>
+        <v>471964.2</v>
       </c>
       <c r="N2" t="n">
-        <v>4475.05</v>
+        <v>360723.05</v>
       </c>
       <c r="O2" t="n">
-        <v>2.021052631578947</v>
+        <v>2.637896687926754</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.2296189469922219</v>
+        <v>-0.3764924038664859</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.2123878463652206</v>
+        <v>-0.3545168402536317</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.01723110062700123</v>
+        <v>-0.02197556361285413</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.03632815595876049</v>
+        <v>-0.02989489506506116</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.04036795156828349</v>
+        <v>-0.05531635050979133</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>-151</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -732,35 +732,35 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>-151</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>-1294.057</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>-1244.057</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>-2453.883</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>-173</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>-2626.883</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
@@ -775,63 +775,63 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>5348</t>
+          <t>3716</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>正能量智能</t>
+          <t>中化控股</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>16.39999961853027</v>
+        <v>33.84999847412109</v>
       </c>
       <c r="G3" t="n">
-        <v>16.40749988555908</v>
+        <v>34.23999977111816</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>46.33115137164528</v>
+        <v>41.21900596797504</v>
       </c>
       <c r="J3" t="n">
-        <v>42.95432092571004</v>
+        <v>30.26750223299895</v>
       </c>
       <c r="K3" t="n">
-        <v>49.9639570133517</v>
+        <v>45.76096765202963</v>
       </c>
       <c r="L3" t="n">
-        <v>6742.2</v>
+        <v>695955.2</v>
       </c>
       <c r="M3" t="n">
-        <v>3626.75</v>
+        <v>390035.65</v>
       </c>
       <c r="N3" t="n">
-        <v>4849.825</v>
+        <v>483655.025</v>
       </c>
       <c r="O3" t="n">
-        <v>1.859019783552768</v>
+        <v>1.7843374060807</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.1465746553403804</v>
+        <v>-0.219203747142295</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1042086752320918</v>
+        <v>-0.1778249438932712</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.04236598010828854</v>
+        <v>-0.04137880324902379</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.080039364776929</v>
+        <v>-0.05595500180004451</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.08627146933421144</v>
+        <v>-0.1026404801627916</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>-46</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -878,35 +878,35 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>-46</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>-294.116</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>-285.116</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>-1851.071</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>-1866.071</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
@@ -917,67 +917,67 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>7547</t>
+          <t>1436</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>碩網</t>
+          <t>華友聯</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>49.95000076293945</v>
+        <v>36.90000152587891</v>
       </c>
       <c r="G4" t="n">
-        <v>50.2774995803833</v>
+        <v>37.63250045776367</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>41.7169592702656</v>
+        <v>35.32528763170918</v>
       </c>
       <c r="J4" t="n">
-        <v>37.86531568941921</v>
+        <v>30.83083171141018</v>
       </c>
       <c r="K4" t="n">
-        <v>45.05293664644619</v>
+        <v>44.165291102922</v>
       </c>
       <c r="L4" t="n">
-        <v>30000</v>
+        <v>244478.6</v>
       </c>
       <c r="M4" t="n">
-        <v>15802.75</v>
+        <v>141281.6</v>
       </c>
       <c r="N4" t="n">
-        <v>18552.15</v>
+        <v>180158.45</v>
       </c>
       <c r="O4" t="n">
-        <v>1.898403758839442</v>
+        <v>1.730434819537717</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.6497907667745721</v>
+        <v>-0.422754113472962</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.7235490313549127</v>
+        <v>-0.496667117016231</v>
       </c>
       <c r="R4" t="n">
-        <v>0.07375826458034052</v>
+        <v>0.07391300354326896</v>
       </c>
       <c r="S4" t="n">
-        <v>0.04955925187934496</v>
+        <v>0.09163494525040261</v>
       </c>
       <c r="T4" t="n">
-        <v>0.04305297833103405</v>
+        <v>0.06882941672259735</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1015,44 +1015,44 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>69.21299999999999</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>66.21299999999999</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>144.079</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>148.079</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>343.093</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>355.093</v>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
@@ -1063,67 +1063,67 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3128</t>
+          <t>6754</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>昇銳</t>
+          <t>匯僑設計</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>20.45000076293945</v>
+        <v>41.79999923706055</v>
       </c>
       <c r="G5" t="n">
-        <v>20.39872636795044</v>
+        <v>41.9774995803833</v>
       </c>
       <c r="H5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>32.68649062534388</v>
+        <v>47.96391682510117</v>
       </c>
       <c r="J5" t="n">
-        <v>30.67321641659039</v>
+        <v>45.34961724251736</v>
       </c>
       <c r="K5" t="n">
-        <v>48.90317366615158</v>
+        <v>48.11381709490516</v>
       </c>
       <c r="L5" t="n">
-        <v>297091.4</v>
+        <v>18851.4</v>
       </c>
       <c r="M5" t="n">
-        <v>158380.45</v>
+        <v>11362.85</v>
       </c>
       <c r="N5" t="n">
-        <v>139728.275</v>
+        <v>11284.05</v>
       </c>
       <c r="O5" t="n">
-        <v>1.875808535712583</v>
+        <v>1.659038005429976</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1290410820741492</v>
+        <v>-0.1117897236098031</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.1977556499677689</v>
+        <v>-0.1164104885459863</v>
       </c>
       <c r="R5" t="n">
-        <v>0.06871456789361968</v>
+        <v>0.0046207649361832</v>
       </c>
       <c r="S5" t="n">
-        <v>0.06259006742728077</v>
+        <v>0.005369204669687294</v>
       </c>
       <c r="T5" t="n">
-        <v>0.07107393069868556</v>
+        <v>-0.03799396775763697</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1170,35 +1170,35 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>9.557000000000002</v>
       </c>
       <c r="AK5" t="n">
         <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>12.557</v>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
@@ -1209,67 +1209,67 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>8044</t>
+          <t>1103</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>網家</t>
+          <t>嘉泥</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>23.5</v>
+        <v>13.10000038146973</v>
       </c>
       <c r="G6" t="n">
-        <v>24.00999994277954</v>
+        <v>13.16749997138977</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>46.68093477165367</v>
+        <v>43.60560210622006</v>
       </c>
       <c r="J6" t="n">
-        <v>38.60833152482403</v>
+        <v>37.58876742710517</v>
       </c>
       <c r="K6" t="n">
-        <v>37.5544318165702</v>
+        <v>46.08864681428155</v>
       </c>
       <c r="L6" t="n">
-        <v>1021667.2</v>
+        <v>565618.2</v>
       </c>
       <c r="M6" t="n">
-        <v>546034.85</v>
+        <v>341379</v>
       </c>
       <c r="N6" t="n">
-        <v>463864.75</v>
+        <v>351623.275</v>
       </c>
       <c r="O6" t="n">
-        <v>1.871065921891249</v>
+        <v>1.656862900178394</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.6119576292260263</v>
+        <v>-0.02949067106389158</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.7133481420035405</v>
+        <v>-0.03360458588101267</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1013905127775142</v>
+        <v>0.004113914817121089</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1099151591586901</v>
+        <v>0.00651316965832463</v>
       </c>
       <c r="T6" t="n">
-        <v>0.05379480154988203</v>
+        <v>0.005209256131352709</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>-115.6</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1316,35 +1316,35 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>-115.6</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>114.4</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>139.4</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>-483.2299999999998</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>-437.2299999999998</v>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
@@ -1355,16 +1355,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>7803</t>
+          <t>2548</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>雲象科技-創</t>
+          <t>華固</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1373,49 +1373,49 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>18.89999961853027</v>
+        <v>94.30000305175781</v>
       </c>
       <c r="G7" t="n">
-        <v>19.21749992370605</v>
+        <v>94.075</v>
       </c>
       <c r="H7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>46.7468875328035</v>
+        <v>39.43943706183018</v>
       </c>
       <c r="J7" t="n">
-        <v>42.22004810677897</v>
+        <v>37.72092438557463</v>
       </c>
       <c r="K7" t="n">
-        <v>44.15734507041385</v>
+        <v>49.93992878342104</v>
       </c>
       <c r="L7" t="n">
-        <v>80400.39999999999</v>
+        <v>1661621.8</v>
       </c>
       <c r="M7" t="n">
-        <v>43830.85</v>
+        <v>1025118.9</v>
       </c>
       <c r="N7" t="n">
-        <v>48815.425</v>
+        <v>1238017.8</v>
       </c>
       <c r="O7" t="n">
-        <v>1.834333580115375</v>
+        <v>1.62090641388038</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.303194832837054</v>
+        <v>-0.3375719194272051</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.3163050781744171</v>
+        <v>-0.4641985647950466</v>
       </c>
       <c r="R7" t="n">
-        <v>0.01311024533736316</v>
+        <v>0.1266266453678415</v>
       </c>
       <c r="S7" t="n">
-        <v>0.006909109385736634</v>
+        <v>0.1052584643190752</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.03964113307048228</v>
+        <v>0.1306670377318038</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1453,44 +1453,44 @@
         </is>
       </c>
       <c r="AB7" t="n">
+        <v>131.646</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>133.596</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>481.1399999999999</v>
+      </c>
+      <c r="AG7" t="n">
         <v>-3</v>
       </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0.517</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>-2.483</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>-45</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
       <c r="AH7" t="n">
-        <v>0.1290000000000002</v>
+        <v>64.39</v>
       </c>
       <c r="AI7" t="n">
-        <v>-44.871</v>
+        <v>542.53</v>
       </c>
       <c r="AJ7" t="n">
-        <v>6.831</v>
+        <v>-3054.208</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>-19.7</v>
       </c>
       <c r="AL7" t="n">
-        <v>8.936</v>
+        <v>67.51000000000002</v>
       </c>
       <c r="AM7" t="n">
-        <v>15.767</v>
+        <v>-3006.398</v>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
@@ -1501,16 +1501,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3704</t>
+          <t>6184</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>合勤控</t>
+          <t>大豐電</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1519,49 +1519,49 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>41.15000152587891</v>
+        <v>40.40000152587891</v>
       </c>
       <c r="G8" t="n">
-        <v>40.79000053405762</v>
+        <v>40.34750003814698</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>45.2819515431601</v>
+        <v>37.15293856531824</v>
       </c>
       <c r="J8" t="n">
-        <v>35.41844377948777</v>
+        <v>32.56539329320293</v>
       </c>
       <c r="K8" t="n">
-        <v>49.34549331163809</v>
+        <v>45.88640062233013</v>
       </c>
       <c r="L8" t="n">
-        <v>4034590.4</v>
+        <v>284786.6</v>
       </c>
       <c r="M8" t="n">
-        <v>2210003.9</v>
+        <v>186916.8</v>
       </c>
       <c r="N8" t="n">
-        <v>2972335.05</v>
+        <v>120414.325</v>
       </c>
       <c r="O8" t="n">
-        <v>1.825603294184232</v>
+        <v>1.523600874827731</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.8320458894321163</v>
+        <v>-0.4341906916975731</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.046873966421186</v>
+        <v>-0.5620874042138739</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2148280769890694</v>
+        <v>0.1278967125163009</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1389284381998714</v>
+        <v>0.1080934748002671</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1087686834079868</v>
+        <v>0.06591699692994912</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1599,44 +1599,44 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>1260.245</v>
+        <v>-28.936</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>14.011</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1274.256</v>
+        <v>-28.936</v>
       </c>
       <c r="AF8" t="n">
-        <v>-1750.663</v>
+        <v>101.434</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>39.09700000000001</v>
+        <v>5</v>
       </c>
       <c r="AI8" t="n">
-        <v>-1711.566000000001</v>
+        <v>106.434</v>
       </c>
       <c r="AJ8" t="n">
-        <v>-8014.798</v>
+        <v>101.039</v>
       </c>
       <c r="AK8" t="n">
         <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>30.95900000000001</v>
+        <v>8</v>
       </c>
       <c r="AM8" t="n">
-        <v>-7983.839</v>
+        <v>109.039</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
@@ -1651,138 +1651,1306 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>4183</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>福永生技</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>13.64999961853027</v>
+      </c>
+      <c r="G9" t="n">
+        <v>13.80249996185303</v>
+      </c>
+      <c r="H9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>44.48913643044764</v>
+      </c>
+      <c r="J9" t="n">
+        <v>37.90129258425644</v>
+      </c>
+      <c r="K9" t="n">
+        <v>47.36640975386072</v>
+      </c>
+      <c r="L9" t="n">
+        <v>18602</v>
+      </c>
+      <c r="M9" t="n">
+        <v>6302.7</v>
+      </c>
+      <c r="N9" t="n">
+        <v>6376.475</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.951433512621575</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-0.1998993230559343</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-0.2003272112742515</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.0004278882183172406</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-0.01473473643626552</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-0.1060510537386441</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>70</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>6856</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>鑫傳</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>41.79999923706055</v>
+      </c>
+      <c r="G10" t="n">
+        <v>41.83499965667725</v>
+      </c>
+      <c r="H10" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>40.41820571666486</v>
+      </c>
+      <c r="J10" t="n">
+        <v>39.74865349476848</v>
+      </c>
+      <c r="K10" t="n">
+        <v>46.67370089876696</v>
+      </c>
+      <c r="L10" t="n">
+        <v>7607.4</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3151.85</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4638.65</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.413630090264448</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-0.4300155868857658</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-0.544939825973721</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.1149242390879552</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.09878902246522991</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.05276425290435449</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>70</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>8044</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>網家</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>23.64999961853027</v>
+      </c>
+      <c r="G11" t="n">
+        <v>23.87999992370606</v>
+      </c>
+      <c r="H11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>47.35527013582377</v>
+      </c>
+      <c r="J11" t="n">
+        <v>44.34347275315994</v>
+      </c>
+      <c r="K11" t="n">
+        <v>40.77212323464666</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1176251.6</v>
+      </c>
+      <c r="M11" t="n">
+        <v>580187.95</v>
+      </c>
+      <c r="N11" t="n">
+        <v>469073.8</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.027363029514833</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-0.5234283105206039</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-0.6488970763847257</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.1254687658641218</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.1323354966111375</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.1013905127775142</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>70</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>4528</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>江興鍛</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>14.85000038146973</v>
+      </c>
+      <c r="G12" t="n">
+        <v>14.93999996185303</v>
+      </c>
+      <c r="H12" t="b">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>44.89268597668262</v>
+      </c>
+      <c r="J12" t="n">
+        <v>35.14662371334847</v>
+      </c>
+      <c r="K12" t="n">
+        <v>42.24035314082241</v>
+      </c>
+      <c r="L12" t="n">
+        <v>35746.2</v>
+      </c>
+      <c r="M12" t="n">
+        <v>18365.4</v>
+      </c>
+      <c r="N12" t="n">
+        <v>18873.9</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.946388317161619</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-0.07921113918568423</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-0.08403869999226199</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.004827560806577758</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.004014076527445232</v>
+      </c>
+      <c r="T12" t="n">
+        <v>-0.001470418979901578</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>70</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>3494</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>誠研</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>7.119999885559082</v>
+      </c>
+      <c r="G13" t="n">
+        <v>7.113000059127808</v>
+      </c>
+      <c r="H13" t="b">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>33.40885912071651</v>
+      </c>
+      <c r="J13" t="n">
+        <v>32.70529666207869</v>
+      </c>
+      <c r="K13" t="n">
+        <v>47.83810972093166</v>
+      </c>
+      <c r="L13" t="n">
+        <v>119251.2</v>
+      </c>
+      <c r="M13" t="n">
+        <v>70296.3</v>
+      </c>
+      <c r="N13" t="n">
+        <v>71987.75</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.696407919051216</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-0.004277879776014792</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-0.0273418771984334</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.02306399742241861</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.03028779147512276</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.0234704927985127</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>-36</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>-34</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>-135</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>-133</v>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>70</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>6222</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>立軒</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>19.04999923706055</v>
+      </c>
+      <c r="G14" t="n">
+        <v>19.66000003814697</v>
+      </c>
+      <c r="H14" t="b">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>32.64836896743243</v>
+      </c>
+      <c r="J14" t="n">
+        <v>32.42876944494298</v>
+      </c>
+      <c r="K14" t="n">
+        <v>41.68748850399481</v>
+      </c>
+      <c r="L14" t="n">
+        <v>28200</v>
+      </c>
+      <c r="M14" t="n">
+        <v>17305</v>
+      </c>
+      <c r="N14" t="n">
+        <v>13158.4</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.629586824617163</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-0.3370541552499589</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-0.2837490218645556</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-0.05330513338540327</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-0.06517555316107426</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-0.05436628059109294</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>70</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1474</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>弘裕</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>10</v>
+      </c>
+      <c r="G15" t="n">
+        <v>9.973500061035157</v>
+      </c>
+      <c r="H15" t="b">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>33.97379486226569</v>
+      </c>
+      <c r="J15" t="n">
+        <v>32.39504476686278</v>
+      </c>
+      <c r="K15" t="n">
+        <v>49.53605784634071</v>
+      </c>
+      <c r="L15" t="n">
+        <v>125358.6</v>
+      </c>
+      <c r="M15" t="n">
+        <v>81135.95</v>
+      </c>
+      <c r="N15" t="n">
+        <v>69681.375</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.545043843080657</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-0.0282551202007717</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-0.04707495802216109</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.01881983782138939</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.01882106846988264</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.01291114011189565</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v>-9</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>-9</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>-80</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>-71</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>-112.843</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>-98.843</v>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>70</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>2424</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>隴華</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="F9" t="n">
-        <v>8.260000228881836</v>
-      </c>
-      <c r="G9" t="n">
-        <v>8.096500134468078</v>
-      </c>
-      <c r="H9" t="b">
+      <c r="F16" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="G16" t="n">
+        <v>8.072500157356263</v>
+      </c>
+      <c r="H16" t="b">
         <v>1</v>
       </c>
-      <c r="I9" t="n">
-        <v>44.20798923436406</v>
-      </c>
-      <c r="J9" t="n">
-        <v>41.46311506258414</v>
-      </c>
-      <c r="K9" t="n">
-        <v>48.43761920194094</v>
-      </c>
-      <c r="L9" t="n">
-        <v>63334.8</v>
-      </c>
-      <c r="M9" t="n">
-        <v>37278.7</v>
-      </c>
-      <c r="N9" t="n">
-        <v>29617.9</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.698954094429259</v>
-      </c>
-      <c r="P9" t="n">
-        <v>-0.09801899504610567</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>-0.152198100591976</v>
-      </c>
-      <c r="R9" t="n">
+      <c r="I16" t="n">
+        <v>43.44254985704089</v>
+      </c>
+      <c r="J16" t="n">
+        <v>41.62455216511677</v>
+      </c>
+      <c r="K16" t="n">
+        <v>48.82773504958483</v>
+      </c>
+      <c r="L16" t="n">
+        <v>59216.4</v>
+      </c>
+      <c r="M16" t="n">
+        <v>38538.9</v>
+      </c>
+      <c r="N16" t="n">
+        <v>27922.5</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.536535811868009</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-0.0793470636982736</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-0.1291028303241997</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.04975576662592607</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.04262531444517925</v>
+      </c>
+      <c r="T16" t="n">
         <v>0.05417910554587033</v>
       </c>
-      <c r="S9" t="n">
-        <v>0.04484055580129376</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0.06729274935909771</v>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB9" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>-30</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>-30</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>-90.09999999999999</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>-90.09999999999999</v>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>-22</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>-22</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>-50</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>-50</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>-111.1</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>-111.1</v>
+      </c>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>70</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2515</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>中工</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>11.89999961853027</v>
+      </c>
+      <c r="G17" t="n">
+        <v>11.97999997138977</v>
+      </c>
+      <c r="H17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>31.15550581689418</v>
+      </c>
+      <c r="J17" t="n">
+        <v>30.12112136627886</v>
+      </c>
+      <c r="K17" t="n">
+        <v>45.69279870697267</v>
+      </c>
+      <c r="L17" t="n">
+        <v>8158391.2</v>
+      </c>
+      <c r="M17" t="n">
+        <v>5320705.8</v>
+      </c>
+      <c r="N17" t="n">
+        <v>5545821.3</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.53332875499337</v>
+      </c>
+      <c r="P17" t="n">
+        <v>-0.0358363120521048</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>-0.04138074534024724</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.005544433288142442</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.009261840524719026</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.004858374439178345</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB17" t="n">
+        <v>-2147.432</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>-27.116</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>-2174.548</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>-1102.578</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>-108.829</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>26.62</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>-1184.787</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1103.669000000001</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>-368.829</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>82.65199999999999</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>817.4920000000006</v>
+      </c>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN17"/>
+  <dimension ref="A1:AN12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -629,12 +629,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1737</t>
+          <t>1611</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>臺鹽</t>
+          <t>中電</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -643,49 +643,49 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>30.10000038146973</v>
+        <v>11.35000038146973</v>
       </c>
       <c r="G2" t="n">
-        <v>30.53499994277954</v>
+        <v>11.60499997138977</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>47.49047248818857</v>
+        <v>41.06594737296948</v>
       </c>
       <c r="J2" t="n">
-        <v>39.31324820895546</v>
+        <v>30.42962648346253</v>
       </c>
       <c r="K2" t="n">
-        <v>39.50095149094502</v>
+        <v>41.19899205734337</v>
       </c>
       <c r="L2" t="n">
-        <v>1244992.8</v>
+        <v>2831116.2</v>
       </c>
       <c r="M2" t="n">
-        <v>471964.2</v>
+        <v>1026730.95</v>
       </c>
       <c r="N2" t="n">
-        <v>360723.05</v>
+        <v>747284.5</v>
       </c>
       <c r="O2" t="n">
-        <v>2.637896687926754</v>
+        <v>2.757408062939955</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.3764924038664859</v>
+        <v>-0.1813834486184014</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.3545168402536317</v>
+        <v>-0.1747261277621337</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.02197556361285413</v>
+        <v>-0.006657320856267718</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.02989489506506116</v>
+        <v>-0.01082488416288874</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.05531635050979133</v>
+        <v>-0.0293241139581249</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -723,44 +723,44 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>-151</v>
+        <v>-278.023</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="AE2" t="n">
-        <v>-151</v>
+        <v>-278.024</v>
       </c>
       <c r="AF2" t="n">
-        <v>-1294.057</v>
+        <v>-3154.658</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>50</v>
+        <v>872.746</v>
       </c>
       <c r="AI2" t="n">
-        <v>-1244.057</v>
+        <v>-2281.912</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-2453.883</v>
+        <v>-4786.246000000001</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>-173</v>
+        <v>945.178</v>
       </c>
       <c r="AM2" t="n">
-        <v>-2626.883</v>
+        <v>-3841.068000000001</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -775,12 +775,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3716</t>
+          <t>2524</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>中化控股</t>
+          <t>京城</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -789,53 +789,53 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>33.84999847412109</v>
+        <v>35</v>
       </c>
       <c r="G3" t="n">
-        <v>34.23999977111816</v>
+        <v>34.85500011444092</v>
       </c>
       <c r="H3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>41.21900596797504</v>
+        <v>46.81287196348833</v>
       </c>
       <c r="J3" t="n">
-        <v>30.26750223299895</v>
+        <v>43.1615763649665</v>
       </c>
       <c r="K3" t="n">
-        <v>45.76096765202963</v>
+        <v>49.88659622010768</v>
       </c>
       <c r="L3" t="n">
-        <v>695955.2</v>
+        <v>166550.4</v>
       </c>
       <c r="M3" t="n">
-        <v>390035.65</v>
+        <v>85645.7</v>
       </c>
       <c r="N3" t="n">
-        <v>483655.025</v>
+        <v>81076.47500000001</v>
       </c>
       <c r="O3" t="n">
-        <v>1.7843374060807</v>
+        <v>1.944644039338811</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.219203747142295</v>
+        <v>0.005603969364308625</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1778249438932712</v>
+        <v>-0.1115606131095225</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.04137880324902379</v>
+        <v>0.1171645824738312</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.05595500180004451</v>
+        <v>0.1434137926953241</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1026404801627916</v>
+        <v>0.1346199311061973</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -855,12 +855,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>-46</v>
+        <v>-12</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -878,35 +878,35 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>-46</v>
+        <v>-12</v>
       </c>
       <c r="AF3" t="n">
-        <v>-294.116</v>
+        <v>5</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="AI3" t="n">
-        <v>-285.116</v>
+        <v>30.00000000000001</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-1851.071</v>
+        <v>53.156</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>-15</v>
+        <v>24</v>
       </c>
       <c r="AM3" t="n">
-        <v>-1866.071</v>
+        <v>77.15600000000001</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1436</t>
+          <t>3716</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>華友聯</t>
+          <t>中化控股</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,53 +935,53 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>36.90000152587891</v>
+        <v>33.95000076293945</v>
       </c>
       <c r="G4" t="n">
-        <v>37.63250045776367</v>
+        <v>34.14749984741211</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>35.32528763170918</v>
+        <v>46.22938698302133</v>
       </c>
       <c r="J4" t="n">
-        <v>30.83083171141018</v>
+        <v>35.58813049192104</v>
       </c>
       <c r="K4" t="n">
-        <v>44.165291102922</v>
+        <v>47.12166204900976</v>
       </c>
       <c r="L4" t="n">
-        <v>244478.6</v>
+        <v>677491</v>
       </c>
       <c r="M4" t="n">
-        <v>141281.6</v>
+        <v>380451.15</v>
       </c>
       <c r="N4" t="n">
-        <v>180158.45</v>
+        <v>478235.275</v>
       </c>
       <c r="O4" t="n">
-        <v>1.730434819537717</v>
+        <v>1.780756872465755</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.422754113472962</v>
+        <v>-0.2071376349839866</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.496667117016231</v>
+        <v>-0.1858698783314944</v>
       </c>
       <c r="R4" t="n">
-        <v>0.07391300354326896</v>
+        <v>-0.02126775665249225</v>
       </c>
       <c r="S4" t="n">
-        <v>0.09163494525040261</v>
+        <v>-0.04051295823217133</v>
       </c>
       <c r="T4" t="n">
-        <v>0.06882941672259735</v>
+        <v>-0.05502117026910816</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1001,12 +1001,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1015,44 +1015,44 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>69.21299999999999</v>
+        <v>-1.499</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>66.21299999999999</v>
+        <v>-1.499</v>
       </c>
       <c r="AF4" t="n">
-        <v>144.079</v>
+        <v>-205.615</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AI4" t="n">
-        <v>148.079</v>
+        <v>-196.615</v>
       </c>
       <c r="AJ4" t="n">
-        <v>343.093</v>
+        <v>-1793.973</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>12</v>
+        <v>-14</v>
       </c>
       <c r="AM4" t="n">
-        <v>355.093</v>
+        <v>-1807.973</v>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>6754</t>
+          <t>1103</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>匯僑設計</t>
+          <t>嘉泥</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1081,49 +1081,49 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>41.79999923706055</v>
+        <v>13.14999961853027</v>
       </c>
       <c r="G5" t="n">
-        <v>41.9774995803833</v>
+        <v>13.15999994277954</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>47.96391682510117</v>
+        <v>45.73702833484832</v>
       </c>
       <c r="J5" t="n">
-        <v>45.34961724251736</v>
+        <v>40.30485440437609</v>
       </c>
       <c r="K5" t="n">
-        <v>48.11381709490516</v>
+        <v>48.89253327887598</v>
       </c>
       <c r="L5" t="n">
-        <v>18851.4</v>
+        <v>584842.6</v>
       </c>
       <c r="M5" t="n">
-        <v>11362.85</v>
+        <v>344402.65</v>
       </c>
       <c r="N5" t="n">
-        <v>11284.05</v>
+        <v>338721.2</v>
       </c>
       <c r="O5" t="n">
-        <v>1.659038005429976</v>
+        <v>1.698136178685036</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1117897236098031</v>
+        <v>-0.02566515056284935</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.1164104885459863</v>
+        <v>-0.03128922878557155</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0046207649361832</v>
+        <v>0.005624078222722206</v>
       </c>
       <c r="S5" t="n">
-        <v>0.005369204669687294</v>
+        <v>0.00382529797653159</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.03799396775763697</v>
+        <v>0.00620189050229291</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>-2</v>
+        <v>-59.156</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1170,35 +1170,35 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-2</v>
+        <v>-59.156</v>
       </c>
       <c r="AF5" t="n">
-        <v>5</v>
+        <v>199.244</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="AI5" t="n">
-        <v>7</v>
+        <v>224.244</v>
       </c>
       <c r="AJ5" t="n">
-        <v>9.557000000000002</v>
+        <v>-510.0559999999999</v>
       </c>
       <c r="AK5" t="n">
         <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="AM5" t="n">
-        <v>12.557</v>
+        <v>-477.0559999999999</v>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -1213,12 +1213,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1103</t>
+          <t>2515</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>嘉泥</t>
+          <t>中工</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1227,49 +1227,49 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>13.10000038146973</v>
+        <v>11.94999980926514</v>
       </c>
       <c r="G6" t="n">
-        <v>13.16749997138977</v>
+        <v>11.97749996185303</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>43.60560210622006</v>
+        <v>31.18700139392723</v>
       </c>
       <c r="J6" t="n">
-        <v>37.58876742710517</v>
+        <v>30.47641469946793</v>
       </c>
       <c r="K6" t="n">
-        <v>46.08864681428155</v>
+        <v>48.19432164464343</v>
       </c>
       <c r="L6" t="n">
-        <v>565618.2</v>
+        <v>8984630</v>
       </c>
       <c r="M6" t="n">
-        <v>341379</v>
+        <v>5399103.65</v>
       </c>
       <c r="N6" t="n">
-        <v>351623.275</v>
+        <v>5497763.35</v>
       </c>
       <c r="O6" t="n">
-        <v>1.656862900178394</v>
+        <v>1.664096594996838</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.02949067106389158</v>
+        <v>-0.03189721351802177</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.03360458588101267</v>
+        <v>-0.03775214025248017</v>
       </c>
       <c r="R6" t="n">
-        <v>0.004113914817121089</v>
+        <v>0.005854926734458393</v>
       </c>
       <c r="S6" t="n">
-        <v>0.00651316965832463</v>
+        <v>0.004857318883574428</v>
       </c>
       <c r="T6" t="n">
-        <v>0.005209256131352709</v>
+        <v>0.008520773608749102</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1307,44 +1307,44 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>-115.6</v>
+        <v>2287.05</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>-4.038</v>
       </c>
       <c r="AE6" t="n">
-        <v>-115.6</v>
+        <v>2283.012</v>
       </c>
       <c r="AF6" t="n">
-        <v>114.4</v>
+        <v>1493.472000000001</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>-48.829</v>
       </c>
       <c r="AH6" t="n">
-        <v>25</v>
+        <v>25.548</v>
       </c>
       <c r="AI6" t="n">
-        <v>139.4</v>
+        <v>1470.191000000001</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-483.2299999999998</v>
+        <v>2060.725</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>-368.829</v>
       </c>
       <c r="AL6" t="n">
-        <v>46</v>
+        <v>22.614</v>
       </c>
       <c r="AM6" t="n">
-        <v>-437.2299999999998</v>
+        <v>1714.510000000001</v>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -1359,12 +1359,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2548</t>
+          <t>6184</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>華固</t>
+          <t>大豐電</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1373,49 +1373,49 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>94.30000305175781</v>
+        <v>40.40000152587891</v>
       </c>
       <c r="G7" t="n">
-        <v>94.075</v>
+        <v>40.28750019073486</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>39.43943706183018</v>
+        <v>37.97620366256384</v>
       </c>
       <c r="J7" t="n">
-        <v>37.72092438557463</v>
+        <v>34.36899676179892</v>
       </c>
       <c r="K7" t="n">
-        <v>49.93992878342104</v>
+        <v>42.44247195524491</v>
       </c>
       <c r="L7" t="n">
-        <v>1661621.8</v>
+        <v>281500.4</v>
       </c>
       <c r="M7" t="n">
-        <v>1025118.9</v>
+        <v>185448.4</v>
       </c>
       <c r="N7" t="n">
-        <v>1238017.8</v>
+        <v>120105.15</v>
       </c>
       <c r="O7" t="n">
-        <v>1.62090641388038</v>
+        <v>1.5179446142431</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.3375719194272051</v>
+        <v>-0.3895386105507654</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.4641985647950466</v>
+        <v>-0.5286688574666284</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1266266453678415</v>
+        <v>0.139130246915863</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1052584643190752</v>
+        <v>0.1283296405296351</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1306670377318038</v>
+        <v>0.1085603965028858</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -1453,44 +1453,44 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>131.646</v>
+        <v>-3</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>133.596</v>
+        <v>-3</v>
       </c>
       <c r="AF7" t="n">
-        <v>481.1399999999999</v>
+        <v>99.434</v>
       </c>
       <c r="AG7" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>64.39</v>
+        <v>5</v>
       </c>
       <c r="AI7" t="n">
-        <v>542.53</v>
+        <v>104.434</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-3054.208</v>
+        <v>76.03899999999999</v>
       </c>
       <c r="AK7" t="n">
-        <v>-19.7</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>67.51000000000002</v>
+        <v>6</v>
       </c>
       <c r="AM7" t="n">
-        <v>-3006.398</v>
+        <v>82.03899999999999</v>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -1501,67 +1501,67 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>6184</t>
+          <t>4154</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>大豐電</t>
+          <t>樂威科-KY</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>40.40000152587891</v>
+        <v>11.85000038146973</v>
       </c>
       <c r="G8" t="n">
-        <v>40.34750003814698</v>
+        <v>12.11999998092651</v>
       </c>
       <c r="H8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>37.15293856531824</v>
+        <v>43.44972854143012</v>
       </c>
       <c r="J8" t="n">
-        <v>32.56539329320293</v>
+        <v>40.26356870941535</v>
       </c>
       <c r="K8" t="n">
-        <v>45.88640062233013</v>
+        <v>46.58736978243079</v>
       </c>
       <c r="L8" t="n">
-        <v>284786.6</v>
+        <v>18000</v>
       </c>
       <c r="M8" t="n">
-        <v>186916.8</v>
+        <v>7275</v>
       </c>
       <c r="N8" t="n">
-        <v>120414.325</v>
+        <v>10932.675</v>
       </c>
       <c r="O8" t="n">
-        <v>1.523600874827731</v>
+        <v>2.474226804123711</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.4341906916975731</v>
+        <v>-0.1413762960993452</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.5620874042138739</v>
+        <v>-0.07476038420551435</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1278967125163009</v>
+        <v>-0.06661591189383086</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1080934748002671</v>
+        <v>-0.09539663212061612</v>
       </c>
       <c r="T8" t="n">
-        <v>0.06591699692994912</v>
+        <v>-0.1121274374787806</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>-28.936</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1608,35 +1608,35 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>-28.936</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>101.434</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>106.434</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>101.039</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
         <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>109.039</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -1651,12 +1651,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4183</t>
+          <t>6856</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>福永生技</t>
+          <t>鑫傳</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1665,49 +1665,49 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>13.64999961853027</v>
+        <v>41.84999847412109</v>
       </c>
       <c r="G9" t="n">
-        <v>13.80249996185303</v>
+        <v>41.8274995803833</v>
       </c>
       <c r="H9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>44.48913643044764</v>
+        <v>39.98893111071957</v>
       </c>
       <c r="J9" t="n">
-        <v>37.90129258425644</v>
+        <v>39.82874602004688</v>
       </c>
       <c r="K9" t="n">
-        <v>47.36640975386072</v>
+        <v>45.73330055889529</v>
       </c>
       <c r="L9" t="n">
-        <v>18602</v>
+        <v>7404.8</v>
       </c>
       <c r="M9" t="n">
-        <v>6302.7</v>
+        <v>3451.2</v>
       </c>
       <c r="N9" t="n">
-        <v>6376.475</v>
+        <v>4338.075</v>
       </c>
       <c r="O9" t="n">
-        <v>2.951433512621575</v>
+        <v>2.145572554473806</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1998993230559343</v>
+        <v>-0.3922985130534116</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.2003272112742515</v>
+        <v>-0.5224137198642038</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0004278882183172406</v>
+        <v>0.1301152068107922</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.01473473643626552</v>
+        <v>0.1180990188295198</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1060510537386441</v>
+        <v>0.1022130872444365</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -1797,63 +1797,63 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>6856</t>
+          <t>3432</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>鑫傳</t>
+          <t>台端</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>41.79999923706055</v>
+        <v>14.69999980926514</v>
       </c>
       <c r="G10" t="n">
-        <v>41.83499965667725</v>
+        <v>14.55250010490417</v>
       </c>
       <c r="H10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>40.41820571666486</v>
+        <v>48.18693265658862</v>
       </c>
       <c r="J10" t="n">
-        <v>39.74865349476848</v>
+        <v>47.00771235080394</v>
       </c>
       <c r="K10" t="n">
-        <v>46.67370089876696</v>
+        <v>48.129305165974</v>
       </c>
       <c r="L10" t="n">
-        <v>7607.4</v>
+        <v>73232.2</v>
       </c>
       <c r="M10" t="n">
-        <v>3151.85</v>
+        <v>34540.7</v>
       </c>
       <c r="N10" t="n">
-        <v>4638.65</v>
+        <v>31040.575</v>
       </c>
       <c r="O10" t="n">
-        <v>2.413630090264448</v>
+        <v>2.120171276204593</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.4300155868857658</v>
+        <v>-0.1428353152348905</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.544939825973721</v>
+        <v>-0.2811691004534506</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1149242390879552</v>
+        <v>0.1383337852185602</v>
       </c>
       <c r="S10" t="n">
-        <v>0.09878902246522991</v>
+        <v>0.1606147095075783</v>
       </c>
       <c r="T10" t="n">
-        <v>0.05276425290435449</v>
+        <v>0.1618679000536323</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1900,35 +1900,35 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -1943,12 +1943,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>8044</t>
+          <t>4535</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>網家</t>
+          <t>至興</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1957,49 +1957,49 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>23.64999961853027</v>
+        <v>27.10000038146973</v>
       </c>
       <c r="G11" t="n">
-        <v>23.87999992370606</v>
+        <v>27.63999996185303</v>
       </c>
       <c r="H11" t="b">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>47.35527013582377</v>
+        <v>44.17555511073171</v>
       </c>
       <c r="J11" t="n">
-        <v>44.34347275315994</v>
+        <v>41.25247528882831</v>
       </c>
       <c r="K11" t="n">
-        <v>40.77212323464666</v>
+        <v>38.27123254113788</v>
       </c>
       <c r="L11" t="n">
-        <v>1176251.6</v>
+        <v>30209.2</v>
       </c>
       <c r="M11" t="n">
-        <v>580187.95</v>
+        <v>14584.15</v>
       </c>
       <c r="N11" t="n">
-        <v>469073.8</v>
+        <v>12292.4</v>
       </c>
       <c r="O11" t="n">
-        <v>2.027363029514833</v>
+        <v>2.071372003167823</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.5234283105206039</v>
+        <v>-0.3394059121114701</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.6488970763847257</v>
+        <v>-0.2813406258423712</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1254687658641218</v>
+        <v>-0.0580652862690989</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1323354966111375</v>
+        <v>-0.07666632046672905</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1013905127775142</v>
+        <v>-0.08586839495844711</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -2089,63 +2089,63 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>4528</t>
+          <t>1472</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>江興鍛</t>
+          <t>三洋實業</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>14.85000038146973</v>
+        <v>88.09999847412109</v>
       </c>
       <c r="G12" t="n">
-        <v>14.93999996185303</v>
+        <v>88.81000022888183</v>
       </c>
       <c r="H12" t="b">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>44.89268597668262</v>
+        <v>37.6625699578121</v>
       </c>
       <c r="J12" t="n">
-        <v>35.14662371334847</v>
+        <v>32.21101461941552</v>
       </c>
       <c r="K12" t="n">
-        <v>42.24035314082241</v>
+        <v>47.06869309574193</v>
       </c>
       <c r="L12" t="n">
-        <v>35746.2</v>
+        <v>66692</v>
       </c>
       <c r="M12" t="n">
-        <v>18365.4</v>
+        <v>36285.2</v>
       </c>
       <c r="N12" t="n">
-        <v>18873.9</v>
+        <v>35375.875</v>
       </c>
       <c r="O12" t="n">
-        <v>1.946388317161619</v>
+        <v>1.837994554253525</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.07921113918568423</v>
+        <v>-0.3415819181309701</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.08403869999226199</v>
+        <v>-0.1421433333864604</v>
       </c>
       <c r="R12" t="n">
-        <v>0.004827560806577758</v>
+        <v>-0.1994385847445097</v>
       </c>
       <c r="S12" t="n">
-        <v>0.004014076527445232</v>
+        <v>-0.2709128830224075</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.001470418979901578</v>
+        <v>-0.2591282186991677</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
@@ -2183,774 +2183,44 @@
         </is>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>-17</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>-78</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>-71</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>16.665</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>-96.70400000000001</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>-80.039</v>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>70</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>3494</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>誠研</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>7.119999885559082</v>
-      </c>
-      <c r="G13" t="n">
-        <v>7.113000059127808</v>
-      </c>
-      <c r="H13" t="b">
-        <v>1</v>
-      </c>
-      <c r="I13" t="n">
-        <v>33.40885912071651</v>
-      </c>
-      <c r="J13" t="n">
-        <v>32.70529666207869</v>
-      </c>
-      <c r="K13" t="n">
-        <v>47.83810972093166</v>
-      </c>
-      <c r="L13" t="n">
-        <v>119251.2</v>
-      </c>
-      <c r="M13" t="n">
-        <v>70296.3</v>
-      </c>
-      <c r="N13" t="n">
-        <v>71987.75</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.696407919051216</v>
-      </c>
-      <c r="P13" t="n">
-        <v>-0.004277879776014792</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>-0.0273418771984334</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0.02306399742241861</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0.03028779147512276</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0.0234704927985127</v>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>-36</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>-34</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>-135</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>-133</v>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>70</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>6222</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>立軒</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>19.04999923706055</v>
-      </c>
-      <c r="G14" t="n">
-        <v>19.66000003814697</v>
-      </c>
-      <c r="H14" t="b">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>32.64836896743243</v>
-      </c>
-      <c r="J14" t="n">
-        <v>32.42876944494298</v>
-      </c>
-      <c r="K14" t="n">
-        <v>41.68748850399481</v>
-      </c>
-      <c r="L14" t="n">
-        <v>28200</v>
-      </c>
-      <c r="M14" t="n">
-        <v>17305</v>
-      </c>
-      <c r="N14" t="n">
-        <v>13158.4</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.629586824617163</v>
-      </c>
-      <c r="P14" t="n">
-        <v>-0.3370541552499589</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>-0.2837490218645556</v>
-      </c>
-      <c r="R14" t="n">
-        <v>-0.05330513338540327</v>
-      </c>
-      <c r="S14" t="n">
-        <v>-0.06517555316107426</v>
-      </c>
-      <c r="T14" t="n">
-        <v>-0.05436628059109294</v>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>70</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>1474</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>弘裕</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>10</v>
-      </c>
-      <c r="G15" t="n">
-        <v>9.973500061035157</v>
-      </c>
-      <c r="H15" t="b">
-        <v>1</v>
-      </c>
-      <c r="I15" t="n">
-        <v>33.97379486226569</v>
-      </c>
-      <c r="J15" t="n">
-        <v>32.39504476686278</v>
-      </c>
-      <c r="K15" t="n">
-        <v>49.53605784634071</v>
-      </c>
-      <c r="L15" t="n">
-        <v>125358.6</v>
-      </c>
-      <c r="M15" t="n">
-        <v>81135.95</v>
-      </c>
-      <c r="N15" t="n">
-        <v>69681.375</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.545043843080657</v>
-      </c>
-      <c r="P15" t="n">
-        <v>-0.0282551202007717</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>-0.04707495802216109</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0.01881983782138939</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0.01882106846988264</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0.01291114011189565</v>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB15" t="n">
-        <v>-9</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>-9</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>-80</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>9</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>-71</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>-112.843</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>14</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>-98.843</v>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>70</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>2424</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>隴華</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="G16" t="n">
-        <v>8.072500157356263</v>
-      </c>
-      <c r="H16" t="b">
-        <v>1</v>
-      </c>
-      <c r="I16" t="n">
-        <v>43.44254985704089</v>
-      </c>
-      <c r="J16" t="n">
-        <v>41.62455216511677</v>
-      </c>
-      <c r="K16" t="n">
-        <v>48.82773504958483</v>
-      </c>
-      <c r="L16" t="n">
-        <v>59216.4</v>
-      </c>
-      <c r="M16" t="n">
-        <v>38538.9</v>
-      </c>
-      <c r="N16" t="n">
-        <v>27922.5</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.536535811868009</v>
-      </c>
-      <c r="P16" t="n">
-        <v>-0.0793470636982736</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>-0.1291028303241997</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.04975576662592607</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0.04262531444517925</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0.05417910554587033</v>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB16" t="n">
-        <v>-22</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>-22</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>-50</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>-50</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>-111.1</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>-111.1</v>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>70</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>2515</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>中工</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>11.89999961853027</v>
-      </c>
-      <c r="G17" t="n">
-        <v>11.97999997138977</v>
-      </c>
-      <c r="H17" t="b">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>31.15550581689418</v>
-      </c>
-      <c r="J17" t="n">
-        <v>30.12112136627886</v>
-      </c>
-      <c r="K17" t="n">
-        <v>45.69279870697267</v>
-      </c>
-      <c r="L17" t="n">
-        <v>8158391.2</v>
-      </c>
-      <c r="M17" t="n">
-        <v>5320705.8</v>
-      </c>
-      <c r="N17" t="n">
-        <v>5545821.3</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.53332875499337</v>
-      </c>
-      <c r="P17" t="n">
-        <v>-0.0358363120521048</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>-0.04138074534024724</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0.005544433288142442</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0.009261840524719026</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0.004858374439178345</v>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB17" t="n">
-        <v>-2147.432</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>-27.116</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>-2174.548</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>-1102.578</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>-108.829</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>26.62</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>-1184.787</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1103.669000000001</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>-368.829</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>82.65199999999999</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>817.4920000000006</v>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN12"/>
+  <dimension ref="A1:AN10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -629,12 +629,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1611</t>
+          <t>2506</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>中電</t>
+          <t>太設</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -643,49 +643,49 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>11.35000038146973</v>
+        <v>8.409999847412109</v>
       </c>
       <c r="G2" t="n">
-        <v>11.60499997138977</v>
+        <v>8.532999992370605</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>41.06594737296948</v>
+        <v>39.71532964824621</v>
       </c>
       <c r="J2" t="n">
-        <v>30.42962648346253</v>
+        <v>37.94589171031653</v>
       </c>
       <c r="K2" t="n">
-        <v>41.19899205734337</v>
+        <v>42.10905336186426</v>
       </c>
       <c r="L2" t="n">
-        <v>2831116.2</v>
+        <v>576221.8</v>
       </c>
       <c r="M2" t="n">
-        <v>1026730.95</v>
+        <v>246467.5</v>
       </c>
       <c r="N2" t="n">
-        <v>747284.5</v>
+        <v>188707.225</v>
       </c>
       <c r="O2" t="n">
-        <v>2.757408062939955</v>
+        <v>2.337922038402629</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.1813834486184014</v>
+        <v>-0.05813114702385924</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.1747261277621337</v>
+        <v>-0.03969277271440346</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.006657320856267718</v>
+        <v>-0.01843837430945578</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.01082488416288874</v>
+        <v>-0.02127126020480052</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0293241139581249</v>
+        <v>-0.02553805948737123</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -723,44 +723,44 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>-278.023</v>
+        <v>-56</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-278.024</v>
+        <v>-56</v>
       </c>
       <c r="AF2" t="n">
-        <v>-3154.658</v>
+        <v>-1841</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>872.746</v>
+        <v>38</v>
       </c>
       <c r="AI2" t="n">
-        <v>-2281.912</v>
+        <v>-1803</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-4786.246000000001</v>
+        <v>-2827.72</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>945.178</v>
+        <v>43</v>
       </c>
       <c r="AM2" t="n">
-        <v>-3841.068000000001</v>
+        <v>-2784.72</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -775,12 +775,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2524</t>
+          <t>3716</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>京城</t>
+          <t>中化控股</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -789,53 +789,53 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>35</v>
+        <v>33.95000076293945</v>
       </c>
       <c r="G3" t="n">
-        <v>34.85500011444092</v>
+        <v>34.08749980926514</v>
       </c>
       <c r="H3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>46.81287196348833</v>
+        <v>49.56964099265556</v>
       </c>
       <c r="J3" t="n">
-        <v>43.1615763649665</v>
+        <v>40.24863399328023</v>
       </c>
       <c r="K3" t="n">
-        <v>49.88659622010768</v>
+        <v>46.33501709893212</v>
       </c>
       <c r="L3" t="n">
-        <v>166550.4</v>
+        <v>650631.2</v>
       </c>
       <c r="M3" t="n">
-        <v>85645.7</v>
+        <v>358126.35</v>
       </c>
       <c r="N3" t="n">
-        <v>81076.47500000001</v>
+        <v>471407.825</v>
       </c>
       <c r="O3" t="n">
-        <v>1.944644039338811</v>
+        <v>1.816764390556573</v>
       </c>
       <c r="P3" t="n">
-        <v>0.005603969364308625</v>
+        <v>-0.1955892386352218</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1115606131095225</v>
+        <v>-0.1899961466123261</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1171645824738312</v>
+        <v>-0.005593092022895707</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1434137926953241</v>
+        <v>-0.02040191163562499</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1346199311061973</v>
+        <v>-0.03957912670121647</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -855,12 +855,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>-12</v>
+        <v>-3.72</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -878,35 +878,35 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>-12</v>
+        <v>-3.72</v>
       </c>
       <c r="AF3" t="n">
-        <v>5</v>
+        <v>-154.335</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="AI3" t="n">
-        <v>30.00000000000001</v>
+        <v>-146.335</v>
       </c>
       <c r="AJ3" t="n">
-        <v>53.156</v>
+        <v>-1510.549</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>24</v>
+        <v>-14</v>
       </c>
       <c r="AM3" t="n">
-        <v>77.15600000000001</v>
+        <v>-1524.549</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -917,71 +917,71 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3716</t>
+          <t>4183</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>中化控股</t>
+          <t>福永生技</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>33.95000076293945</v>
+        <v>13.30000019073486</v>
       </c>
       <c r="G4" t="n">
-        <v>34.14749984741211</v>
+        <v>13.79499998092651</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>46.22938698302133</v>
+        <v>47.75648542035075</v>
       </c>
       <c r="J4" t="n">
-        <v>35.58813049192104</v>
+        <v>46.21353917657769</v>
       </c>
       <c r="K4" t="n">
-        <v>47.12166204900976</v>
+        <v>43.12863696227856</v>
       </c>
       <c r="L4" t="n">
-        <v>677491</v>
+        <v>24000.8</v>
       </c>
       <c r="M4" t="n">
-        <v>380451.15</v>
+        <v>6850.45</v>
       </c>
       <c r="N4" t="n">
-        <v>478235.275</v>
+        <v>6251.325</v>
       </c>
       <c r="O4" t="n">
-        <v>1.780756872465755</v>
+        <v>3.503536264041049</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2071376349839866</v>
+        <v>-0.1671619821459149</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.1858698783314944</v>
+        <v>-0.1885136568758811</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.02126775665249225</v>
+        <v>0.02135167472996619</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.04051295823217133</v>
+        <v>0.05194115828125911</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.05502117026910816</v>
+        <v>0.0024935252284215</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>-1.499</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1024,35 +1024,35 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-1.499</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>-205.615</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>-196.615</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-1793.973</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>-1807.973</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -1063,16 +1063,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1103</t>
+          <t>1611</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>嘉泥</t>
+          <t>中電</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1081,49 +1081,49 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>13.14999961853027</v>
+        <v>11.39999961853027</v>
       </c>
       <c r="G5" t="n">
-        <v>13.15999994277954</v>
+        <v>11.57499995231628</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>45.73702833484832</v>
+        <v>45.32599738690413</v>
       </c>
       <c r="J5" t="n">
-        <v>40.30485440437609</v>
+        <v>35.39508344528207</v>
       </c>
       <c r="K5" t="n">
-        <v>48.89253327887598</v>
+        <v>42.05287754817356</v>
       </c>
       <c r="L5" t="n">
-        <v>584842.6</v>
+        <v>2822739.4</v>
       </c>
       <c r="M5" t="n">
-        <v>344402.65</v>
+        <v>1000403.05</v>
       </c>
       <c r="N5" t="n">
-        <v>338721.2</v>
+        <v>742427.475</v>
       </c>
       <c r="O5" t="n">
-        <v>1.698136178685036</v>
+        <v>2.821602153252131</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.02566515056284935</v>
+        <v>-0.1736540707641598</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.03128922878557155</v>
+        <v>-0.1748754513784414</v>
       </c>
       <c r="R5" t="n">
-        <v>0.005624078222722206</v>
+        <v>0.001221380614281536</v>
       </c>
       <c r="S5" t="n">
-        <v>0.00382529797653159</v>
+        <v>-0.006513012435971605</v>
       </c>
       <c r="T5" t="n">
-        <v>0.00620189050229291</v>
+        <v>-0.01066924458487206</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1161,44 +1161,44 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>-59.156</v>
+        <v>-194.032</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AE5" t="n">
-        <v>-59.156</v>
+        <v>-198.032</v>
       </c>
       <c r="AF5" t="n">
-        <v>199.244</v>
+        <v>-3369.018</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>25</v>
+        <v>877.746</v>
       </c>
       <c r="AI5" t="n">
-        <v>224.244</v>
+        <v>-2491.272</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-510.0559999999999</v>
+        <v>-5245.741</v>
       </c>
       <c r="AK5" t="n">
         <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>33</v>
+        <v>910.1780000000001</v>
       </c>
       <c r="AM5" t="n">
-        <v>-477.0559999999999</v>
+        <v>-4335.563</v>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -1209,67 +1209,67 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2515</t>
+          <t>3115</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>中工</t>
+          <t>富榮綱</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>11.94999980926514</v>
+        <v>7.980000019073486</v>
       </c>
       <c r="G6" t="n">
-        <v>11.97749996185303</v>
+        <v>8.519999814033508</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>31.18700139392723</v>
+        <v>35.82784087676091</v>
       </c>
       <c r="J6" t="n">
-        <v>30.47641469946793</v>
+        <v>30.61851595405025</v>
       </c>
       <c r="K6" t="n">
-        <v>48.19432164464343</v>
+        <v>34.08134058442728</v>
       </c>
       <c r="L6" t="n">
-        <v>8984630</v>
+        <v>33424</v>
       </c>
       <c r="M6" t="n">
-        <v>5399103.65</v>
+        <v>12683.2</v>
       </c>
       <c r="N6" t="n">
-        <v>5497763.35</v>
+        <v>8866.9</v>
       </c>
       <c r="O6" t="n">
-        <v>1.664096594996838</v>
+        <v>2.635297085908919</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.03189721351802177</v>
+        <v>-0.2386658511481627</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.03775214025248017</v>
+        <v>-0.1818358495795883</v>
       </c>
       <c r="R6" t="n">
-        <v>0.005854926734458393</v>
+        <v>-0.05683000156857443</v>
       </c>
       <c r="S6" t="n">
-        <v>0.004857318883574428</v>
+        <v>-0.05975396089364188</v>
       </c>
       <c r="T6" t="n">
-        <v>0.008520773608749102</v>
+        <v>-0.06105594249326041</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1307,44 +1307,44 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>2287.05</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>-4.038</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>2283.012</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1493.472000000001</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>-48.829</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>25.548</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>1470.191000000001</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2060.725</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>-368.829</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>22.614</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>1714.510000000001</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -1355,67 +1355,67 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>6184</t>
+          <t>8092</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>大豐電</t>
+          <t>建暐</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>40.40000152587891</v>
+        <v>12.89999961853027</v>
       </c>
       <c r="G7" t="n">
-        <v>40.28750019073486</v>
+        <v>12.85999994277954</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>37.97620366256384</v>
+        <v>32.79776461668928</v>
       </c>
       <c r="J7" t="n">
-        <v>34.36899676179892</v>
+        <v>30.38920403724528</v>
       </c>
       <c r="K7" t="n">
-        <v>42.44247195524491</v>
+        <v>49.54189035925414</v>
       </c>
       <c r="L7" t="n">
-        <v>281500.4</v>
+        <v>103601.2</v>
       </c>
       <c r="M7" t="n">
-        <v>185448.4</v>
+        <v>42207.75</v>
       </c>
       <c r="N7" t="n">
-        <v>120105.15</v>
+        <v>52085.15</v>
       </c>
       <c r="O7" t="n">
-        <v>1.5179446142431</v>
+        <v>2.45455396224627</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.3895386105507654</v>
+        <v>-0.07961671975824025</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.5286688574666284</v>
+        <v>-0.106853858152957</v>
       </c>
       <c r="R7" t="n">
-        <v>0.139130246915863</v>
+        <v>0.02723713839471673</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1283296405296351</v>
+        <v>0.02021108427563426</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1085603965028858</v>
+        <v>0.003873306265973278</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1462,35 +1462,35 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>99.434</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>104.434</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>76.03899999999999</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>82.03899999999999</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -1505,63 +1505,63 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4154</t>
+          <t>1472</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>樂威科-KY</t>
+          <t>三洋實業</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>11.85000038146973</v>
+        <v>88</v>
       </c>
       <c r="G8" t="n">
-        <v>12.11999998092651</v>
+        <v>88.73500022888183</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>43.44972854143012</v>
+        <v>44.55281852941837</v>
       </c>
       <c r="J8" t="n">
-        <v>40.26356870941535</v>
+        <v>36.32494925569367</v>
       </c>
       <c r="K8" t="n">
-        <v>46.58736978243079</v>
+        <v>46.51023846709424</v>
       </c>
       <c r="L8" t="n">
-        <v>18000</v>
+        <v>67014.2</v>
       </c>
       <c r="M8" t="n">
-        <v>7275</v>
+        <v>33025.75</v>
       </c>
       <c r="N8" t="n">
-        <v>10932.675</v>
+        <v>35771.15</v>
       </c>
       <c r="O8" t="n">
-        <v>2.474226804123711</v>
+        <v>2.029149981453866</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.1413762960993452</v>
+        <v>-0.3310312615038953</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.07476038420551435</v>
+        <v>-0.1828307991371738</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.06661591189383086</v>
+        <v>-0.1482004623667215</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.09539663212061612</v>
+        <v>-0.1982841173821325</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1121274374787806</v>
+        <v>-0.2696677663982495</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -1611,32 +1611,32 @@
         <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>-68</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>13.665</v>
       </c>
       <c r="AK8" t="n">
         <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>-96.70400000000001</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>-83.039</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -1651,63 +1651,63 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>6856</t>
+          <t>2524</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>鑫傳</t>
+          <t>京城</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>41.84999847412109</v>
+        <v>34.84999847412109</v>
       </c>
       <c r="G9" t="n">
-        <v>41.8274995803833</v>
+        <v>34.82250003814697</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>39.98893111071957</v>
+        <v>44.23538241680075</v>
       </c>
       <c r="J9" t="n">
-        <v>39.82874602004688</v>
+        <v>43.51951171666212</v>
       </c>
       <c r="K9" t="n">
-        <v>45.73330055889529</v>
+        <v>49.26870696265575</v>
       </c>
       <c r="L9" t="n">
-        <v>7404.8</v>
+        <v>157184.4</v>
       </c>
       <c r="M9" t="n">
-        <v>3451.2</v>
+        <v>85304.2</v>
       </c>
       <c r="N9" t="n">
-        <v>4338.075</v>
+        <v>79504.35000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>2.145572554473806</v>
+        <v>1.842633774186968</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.3922985130534116</v>
+        <v>-0.000880769032335138</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.5224137198642038</v>
+        <v>-0.08542357993215828</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1301152068107922</v>
+        <v>0.08454281089982314</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1180990188295198</v>
+        <v>0.1155771981079546</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1022130872444365</v>
+        <v>0.1417017662428792</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1754,35 +1754,35 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>-43</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>-20.99999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>23.15600000000001</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>45.15600000000001</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -1797,63 +1797,63 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3432</t>
+          <t>4402</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>台端</t>
+          <t>郡都開發</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>14.69999980926514</v>
+        <v>14.10000038146973</v>
       </c>
       <c r="G10" t="n">
-        <v>14.55250010490417</v>
+        <v>14.37000007629394</v>
       </c>
       <c r="H10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>48.18693265658862</v>
+        <v>41.89288397277223</v>
       </c>
       <c r="J10" t="n">
-        <v>47.00771235080394</v>
+        <v>41.78565467873618</v>
       </c>
       <c r="K10" t="n">
-        <v>48.129305165974</v>
+        <v>39.01198606053651</v>
       </c>
       <c r="L10" t="n">
-        <v>73232.2</v>
+        <v>34170</v>
       </c>
       <c r="M10" t="n">
-        <v>34540.7</v>
+        <v>20946.75</v>
       </c>
       <c r="N10" t="n">
-        <v>31040.575</v>
+        <v>21658.925</v>
       </c>
       <c r="O10" t="n">
-        <v>2.120171276204593</v>
+        <v>1.631279315406925</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.1428353152348905</v>
+        <v>-0.3749691025409252</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.2811691004534506</v>
+        <v>-0.3900088662078101</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1383337852185602</v>
+        <v>0.01503976366688486</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1606147095075783</v>
+        <v>-0.002829960682150134</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1618679000536323</v>
+        <v>-0.005012345669958562</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1900,327 +1900,35 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>-9</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>70</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>4535</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>至興</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>27.10000038146973</v>
-      </c>
-      <c r="G11" t="n">
-        <v>27.63999996185303</v>
-      </c>
-      <c r="H11" t="b">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>44.17555511073171</v>
-      </c>
-      <c r="J11" t="n">
-        <v>41.25247528882831</v>
-      </c>
-      <c r="K11" t="n">
-        <v>38.27123254113788</v>
-      </c>
-      <c r="L11" t="n">
-        <v>30209.2</v>
-      </c>
-      <c r="M11" t="n">
-        <v>14584.15</v>
-      </c>
-      <c r="N11" t="n">
-        <v>12292.4</v>
-      </c>
-      <c r="O11" t="n">
-        <v>2.071372003167823</v>
-      </c>
-      <c r="P11" t="n">
-        <v>-0.3394059121114701</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>-0.2813406258423712</v>
-      </c>
-      <c r="R11" t="n">
-        <v>-0.0580652862690989</v>
-      </c>
-      <c r="S11" t="n">
-        <v>-0.07666632046672905</v>
-      </c>
-      <c r="T11" t="n">
-        <v>-0.08586839495844711</v>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>70</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1472</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>三洋實業</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>88.09999847412109</v>
-      </c>
-      <c r="G12" t="n">
-        <v>88.81000022888183</v>
-      </c>
-      <c r="H12" t="b">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>37.6625699578121</v>
-      </c>
-      <c r="J12" t="n">
-        <v>32.21101461941552</v>
-      </c>
-      <c r="K12" t="n">
-        <v>47.06869309574193</v>
-      </c>
-      <c r="L12" t="n">
-        <v>66692</v>
-      </c>
-      <c r="M12" t="n">
-        <v>36285.2</v>
-      </c>
-      <c r="N12" t="n">
-        <v>35375.875</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.837994554253525</v>
-      </c>
-      <c r="P12" t="n">
-        <v>-0.3415819181309701</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>-0.1421433333864604</v>
-      </c>
-      <c r="R12" t="n">
-        <v>-0.1994385847445097</v>
-      </c>
-      <c r="S12" t="n">
-        <v>-0.2709128830224075</v>
-      </c>
-      <c r="T12" t="n">
-        <v>-0.2591282186991677</v>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>-17</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>-13</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>7</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>-78</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>-71</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>16.665</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>-96.70400000000001</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>-80.039</v>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -661,16 +661,16 @@
         <v>42.10905336186426</v>
       </c>
       <c r="L2" t="n">
-        <v>576221.8</v>
+        <v>576308.4</v>
       </c>
       <c r="M2" t="n">
-        <v>246467.5</v>
+        <v>246489.15</v>
       </c>
       <c r="N2" t="n">
-        <v>188707.225</v>
+        <v>188718.05</v>
       </c>
       <c r="O2" t="n">
-        <v>2.337922038402629</v>
+        <v>2.338068024495196</v>
       </c>
       <c r="P2" t="n">
         <v>-0.05813114702385924</v>
@@ -807,16 +807,16 @@
         <v>46.33501709893212</v>
       </c>
       <c r="L3" t="n">
-        <v>650631.2</v>
+        <v>649620.6</v>
       </c>
       <c r="M3" t="n">
-        <v>358126.35</v>
+        <v>357873.7</v>
       </c>
       <c r="N3" t="n">
-        <v>471407.825</v>
+        <v>471281.5</v>
       </c>
       <c r="O3" t="n">
-        <v>1.816764390556573</v>
+        <v>1.815223080097811</v>
       </c>
       <c r="P3" t="n">
         <v>-0.1955892386352218</v>
@@ -1099,16 +1099,16 @@
         <v>42.05287754817356</v>
       </c>
       <c r="L5" t="n">
-        <v>2822739.4</v>
+        <v>2821580.4</v>
       </c>
       <c r="M5" t="n">
-        <v>1000403.05</v>
+        <v>1000113.3</v>
       </c>
       <c r="N5" t="n">
-        <v>742427.475</v>
+        <v>742282.6</v>
       </c>
       <c r="O5" t="n">
-        <v>2.821602153252131</v>
+        <v>2.821260751156894</v>
       </c>
       <c r="P5" t="n">
         <v>-0.1736540707641598</v>
@@ -1245,16 +1245,16 @@
         <v>34.08134058442728</v>
       </c>
       <c r="L6" t="n">
-        <v>33424</v>
+        <v>33421.2</v>
       </c>
       <c r="M6" t="n">
-        <v>12683.2</v>
+        <v>12682.5</v>
       </c>
       <c r="N6" t="n">
-        <v>8866.9</v>
+        <v>8866.549999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>2.635297085908919</v>
+        <v>2.635221762270846</v>
       </c>
       <c r="P6" t="n">
         <v>-0.2386658511481627</v>
@@ -1391,16 +1391,16 @@
         <v>49.54189035925414</v>
       </c>
       <c r="L7" t="n">
-        <v>103601.2</v>
+        <v>103600.6</v>
       </c>
       <c r="M7" t="n">
-        <v>42207.75</v>
+        <v>42207.6</v>
       </c>
       <c r="N7" t="n">
-        <v>52085.15</v>
+        <v>52085.075</v>
       </c>
       <c r="O7" t="n">
-        <v>2.45455396224627</v>
+        <v>2.454548469943802</v>
       </c>
       <c r="P7" t="n">
         <v>-0.07961671975824025</v>
@@ -1537,16 +1537,16 @@
         <v>46.51023846709424</v>
       </c>
       <c r="L8" t="n">
-        <v>67014.2</v>
+        <v>67002.39999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>33025.75</v>
+        <v>33022.8</v>
       </c>
       <c r="N8" t="n">
-        <v>35771.15</v>
+        <v>35769.675</v>
       </c>
       <c r="O8" t="n">
-        <v>2.029149981453866</v>
+        <v>2.028973921048487</v>
       </c>
       <c r="P8" t="n">
         <v>-0.3310312615038953</v>
@@ -1683,16 +1683,16 @@
         <v>49.26870696265575</v>
       </c>
       <c r="L9" t="n">
-        <v>157184.4</v>
+        <v>157157</v>
       </c>
       <c r="M9" t="n">
-        <v>85304.2</v>
+        <v>85297.35000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>79504.35000000001</v>
+        <v>79500.925</v>
       </c>
       <c r="O9" t="n">
-        <v>1.842633774186968</v>
+        <v>1.842460521927117</v>
       </c>
       <c r="P9" t="n">
         <v>-0.000880769032335138</v>
@@ -1829,16 +1829,16 @@
         <v>39.01198606053651</v>
       </c>
       <c r="L10" t="n">
-        <v>34170</v>
+        <v>34169</v>
       </c>
       <c r="M10" t="n">
-        <v>20946.75</v>
+        <v>20946.5</v>
       </c>
       <c r="N10" t="n">
-        <v>21658.925</v>
+        <v>21658.8</v>
       </c>
       <c r="O10" t="n">
-        <v>1.631279315406925</v>
+        <v>1.631251044327215</v>
       </c>
       <c r="P10" t="n">
         <v>-0.3749691025409252</v>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN10"/>
+  <dimension ref="A1:AN6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,71 +625,71 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2506</t>
+          <t>3288</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>太設</t>
+          <t>點晶</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>8.409999847412109</v>
+        <v>20.89999961853027</v>
       </c>
       <c r="G2" t="n">
-        <v>8.532999992370605</v>
+        <v>20.78750009536743</v>
       </c>
       <c r="H2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>39.71532964824621</v>
+        <v>49.94965575577034</v>
       </c>
       <c r="J2" t="n">
-        <v>37.94589171031653</v>
+        <v>49.69690537440733</v>
       </c>
       <c r="K2" t="n">
-        <v>42.10905336186426</v>
+        <v>48.48361192711387</v>
       </c>
       <c r="L2" t="n">
-        <v>576308.4</v>
+        <v>104828.2</v>
       </c>
       <c r="M2" t="n">
-        <v>246489.15</v>
+        <v>45954.95</v>
       </c>
       <c r="N2" t="n">
-        <v>188718.05</v>
+        <v>50502.875</v>
       </c>
       <c r="O2" t="n">
-        <v>2.338068024495196</v>
+        <v>2.281107911117301</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.05813114702385924</v>
+        <v>-0.1667236368096994</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.03969277271440346</v>
+        <v>-0.304059462415278</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.01843837430945578</v>
+        <v>0.1373358256055787</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.02127126020480052</v>
+        <v>0.1645912504598506</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.02553805948737123</v>
+        <v>0.1890504573265774</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>-56</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -732,35 +732,35 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-56</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>-1841</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>-1803</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-2827.72</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>-2784.72</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-29</t>
         </is>
       </c>
     </row>
@@ -771,71 +771,71 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3716</t>
+          <t>2230</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>中化控股</t>
+          <t>泰茂</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>33.95000076293945</v>
+        <v>21.75</v>
       </c>
       <c r="G3" t="n">
-        <v>34.08749980926514</v>
+        <v>21.89499998092651</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>49.56964099265556</v>
+        <v>47.27637338703806</v>
       </c>
       <c r="J3" t="n">
-        <v>40.24863399328023</v>
+        <v>35.95501239340445</v>
       </c>
       <c r="K3" t="n">
-        <v>46.33501709893212</v>
+        <v>45.77639300770748</v>
       </c>
       <c r="L3" t="n">
-        <v>649620.6</v>
+        <v>221487.4</v>
       </c>
       <c r="M3" t="n">
-        <v>357873.7</v>
+        <v>110204.1</v>
       </c>
       <c r="N3" t="n">
-        <v>471281.5</v>
+        <v>122567.2</v>
       </c>
       <c r="O3" t="n">
-        <v>1.815223080097811</v>
+        <v>2.009792739108617</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.1955892386352218</v>
+        <v>-0.4906311371264209</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1899961466123261</v>
+        <v>-0.5737274014355255</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.005593092022895707</v>
+        <v>0.08309626430910455</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.02040191163562499</v>
+        <v>0.06701321309775787</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.03957912670121647</v>
+        <v>-0.02687681640216855</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>-3.72</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -878,35 +878,35 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>-3.72</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-154.335</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>-146.335</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-1510.549</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>-1524.549</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-29</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4183</t>
+          <t>6546</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>福永生技</t>
+          <t>正基</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,49 +935,49 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>13.30000019073486</v>
+        <v>58.59999847412109</v>
       </c>
       <c r="G4" t="n">
-        <v>13.79499998092651</v>
+        <v>60.53499984741211</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>47.75648542035075</v>
+        <v>34.18610773146303</v>
       </c>
       <c r="J4" t="n">
-        <v>46.21353917657769</v>
+        <v>33.28733692638864</v>
       </c>
       <c r="K4" t="n">
-        <v>43.12863696227856</v>
+        <v>42.21818475157023</v>
       </c>
       <c r="L4" t="n">
-        <v>24000.8</v>
+        <v>461995.8</v>
       </c>
       <c r="M4" t="n">
-        <v>6850.45</v>
+        <v>236668.2</v>
       </c>
       <c r="N4" t="n">
-        <v>6251.325</v>
+        <v>280576.025</v>
       </c>
       <c r="O4" t="n">
-        <v>3.503536264041049</v>
+        <v>1.952082282283805</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.1671619821459149</v>
+        <v>-0.8830525946715397</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.1885136568758811</v>
+        <v>-0.6944427464667224</v>
       </c>
       <c r="R4" t="n">
-        <v>0.02135167472996619</v>
+        <v>-0.1886098482048173</v>
       </c>
       <c r="S4" t="n">
-        <v>0.05194115828125911</v>
+        <v>-0.2022086532695517</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0024935252284215</v>
+        <v>-0.2179415148026154</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-29</t>
         </is>
       </c>
     </row>
@@ -1067,63 +1067,63 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1611</t>
+          <t>5344</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>中電</t>
+          <t>立衛</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>11.39999961853027</v>
+        <v>13.35000038146973</v>
       </c>
       <c r="G5" t="n">
-        <v>11.57499995231628</v>
+        <v>13.4050000667572</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>45.32599738690413</v>
+        <v>44.73089591693072</v>
       </c>
       <c r="J5" t="n">
-        <v>35.39508344528207</v>
+        <v>39.60988867841668</v>
       </c>
       <c r="K5" t="n">
-        <v>42.05287754817356</v>
+        <v>47.03928090938346</v>
       </c>
       <c r="L5" t="n">
-        <v>2821580.4</v>
+        <v>88783.2</v>
       </c>
       <c r="M5" t="n">
-        <v>1000113.3</v>
+        <v>45524.05</v>
       </c>
       <c r="N5" t="n">
-        <v>742282.6</v>
+        <v>42565.625</v>
       </c>
       <c r="O5" t="n">
-        <v>2.821260751156894</v>
+        <v>1.950248275362144</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1736540707641598</v>
+        <v>-0.1227288263487747</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.1748754513784414</v>
+        <v>-0.186255409425281</v>
       </c>
       <c r="R5" t="n">
-        <v>0.001221380614281536</v>
+        <v>0.06352658307650635</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.006513012435971605</v>
+        <v>0.07251626717645532</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.01066924458487206</v>
+        <v>0.05827953253853507</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1161,44 +1161,44 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>-194.032</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-198.032</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>-3369.018</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>877.746</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>-2491.272</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-5245.741</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
         <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>910.1780000000001</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>-4335.563</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-29</t>
         </is>
       </c>
     </row>
@@ -1213,12 +1213,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3115</t>
+          <t>6856</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>富榮綱</t>
+          <t>鑫傳</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1227,49 +1227,49 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>7.980000019073486</v>
+        <v>41.79999923706055</v>
       </c>
       <c r="G6" t="n">
-        <v>8.519999814033508</v>
+        <v>41.80499954223633</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>35.82784087676091</v>
+        <v>41.92743001728621</v>
       </c>
       <c r="J6" t="n">
-        <v>30.61851595405025</v>
+        <v>41.46649282230376</v>
       </c>
       <c r="K6" t="n">
-        <v>34.08134058442728</v>
+        <v>46.72074869750747</v>
       </c>
       <c r="L6" t="n">
-        <v>33421.2</v>
+        <v>7401</v>
       </c>
       <c r="M6" t="n">
-        <v>12682.5</v>
+        <v>4100.25</v>
       </c>
       <c r="N6" t="n">
-        <v>8866.549999999999</v>
+        <v>4462.6</v>
       </c>
       <c r="O6" t="n">
-        <v>2.635221762270846</v>
+        <v>1.805011889518932</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.2386658511481627</v>
+        <v>-0.288007934657287</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.1818358495795883</v>
+        <v>-0.4346652915656134</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.05683000156857443</v>
+        <v>0.1466573569083264</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.05975396089364188</v>
+        <v>0.1611287067526771</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.06105594249326041</v>
+        <v>0.1266874813420205</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1344,591 +1344,7 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>70</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>8092</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>建暐</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>12.89999961853027</v>
-      </c>
-      <c r="G7" t="n">
-        <v>12.85999994277954</v>
-      </c>
-      <c r="H7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7" t="n">
-        <v>32.79776461668928</v>
-      </c>
-      <c r="J7" t="n">
-        <v>30.38920403724528</v>
-      </c>
-      <c r="K7" t="n">
-        <v>49.54189035925414</v>
-      </c>
-      <c r="L7" t="n">
-        <v>103600.6</v>
-      </c>
-      <c r="M7" t="n">
-        <v>42207.6</v>
-      </c>
-      <c r="N7" t="n">
-        <v>52085.075</v>
-      </c>
-      <c r="O7" t="n">
-        <v>2.454548469943802</v>
-      </c>
-      <c r="P7" t="n">
-        <v>-0.07961671975824025</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>-0.106853858152957</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.02723713839471673</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.02021108427563426</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.003873306265973278</v>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>70</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1472</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>三洋實業</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>88</v>
-      </c>
-      <c r="G8" t="n">
-        <v>88.73500022888183</v>
-      </c>
-      <c r="H8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>44.55281852941837</v>
-      </c>
-      <c r="J8" t="n">
-        <v>36.32494925569367</v>
-      </c>
-      <c r="K8" t="n">
-        <v>46.51023846709424</v>
-      </c>
-      <c r="L8" t="n">
-        <v>67002.39999999999</v>
-      </c>
-      <c r="M8" t="n">
-        <v>33022.8</v>
-      </c>
-      <c r="N8" t="n">
-        <v>35769.675</v>
-      </c>
-      <c r="O8" t="n">
-        <v>2.028973921048487</v>
-      </c>
-      <c r="P8" t="n">
-        <v>-0.3310312615038953</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>-0.1828307991371738</v>
-      </c>
-      <c r="R8" t="n">
-        <v>-0.1482004623667215</v>
-      </c>
-      <c r="S8" t="n">
-        <v>-0.1982841173821325</v>
-      </c>
-      <c r="T8" t="n">
-        <v>-0.2696677663982495</v>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>-68</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>-60</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>13.665</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>-96.70400000000001</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>-83.039</v>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>70</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2524</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>京城</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>34.84999847412109</v>
-      </c>
-      <c r="G9" t="n">
-        <v>34.82250003814697</v>
-      </c>
-      <c r="H9" t="b">
-        <v>1</v>
-      </c>
-      <c r="I9" t="n">
-        <v>44.23538241680075</v>
-      </c>
-      <c r="J9" t="n">
-        <v>43.51951171666212</v>
-      </c>
-      <c r="K9" t="n">
-        <v>49.26870696265575</v>
-      </c>
-      <c r="L9" t="n">
-        <v>157157</v>
-      </c>
-      <c r="M9" t="n">
-        <v>85297.35000000001</v>
-      </c>
-      <c r="N9" t="n">
-        <v>79500.925</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.842460521927117</v>
-      </c>
-      <c r="P9" t="n">
-        <v>-0.000880769032335138</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>-0.08542357993215828</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.08454281089982314</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.1155771981079546</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0.1417017662428792</v>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB9" t="n">
-        <v>-15</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>-15</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>-43</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>-20.99999999999999</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>23.15600000000001</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>22</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>45.15600000000001</v>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>70</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>4402</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>郡都開發</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>14.10000038146973</v>
-      </c>
-      <c r="G10" t="n">
-        <v>14.37000007629394</v>
-      </c>
-      <c r="H10" t="b">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>41.89288397277223</v>
-      </c>
-      <c r="J10" t="n">
-        <v>41.78565467873618</v>
-      </c>
-      <c r="K10" t="n">
-        <v>39.01198606053651</v>
-      </c>
-      <c r="L10" t="n">
-        <v>34169</v>
-      </c>
-      <c r="M10" t="n">
-        <v>20946.5</v>
-      </c>
-      <c r="N10" t="n">
-        <v>21658.8</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.631251044327215</v>
-      </c>
-      <c r="P10" t="n">
-        <v>-0.3749691025409252</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>-0.3900088662078101</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.01503976366688486</v>
-      </c>
-      <c r="S10" t="n">
-        <v>-0.002829960682150134</v>
-      </c>
-      <c r="T10" t="n">
-        <v>-0.005012345669958562</v>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
+          <t>2026-09-29</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -652,40 +652,40 @@
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>49.94965575577034</v>
+        <v>49.94965575673093</v>
       </c>
       <c r="J2" t="n">
-        <v>49.69690537440733</v>
+        <v>49.69690539265871</v>
       </c>
       <c r="K2" t="n">
-        <v>48.48361192711387</v>
+        <v>47.92309313665962</v>
       </c>
       <c r="L2" t="n">
-        <v>104828.2</v>
+        <v>104813.8</v>
       </c>
       <c r="M2" t="n">
-        <v>45954.95</v>
+        <v>45951.35</v>
       </c>
       <c r="N2" t="n">
-        <v>50502.875</v>
+        <v>50501.075</v>
       </c>
       <c r="O2" t="n">
-        <v>2.281107911117301</v>
+        <v>2.280973246705483</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.1667236368096994</v>
+        <v>-0.1703417915162682</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.304059462415278</v>
+        <v>-0.3093559999051598</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1373358256055787</v>
+        <v>0.1390142083888917</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1645912504598506</v>
+        <v>0.1664009341468143</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1890504573265774</v>
+        <v>0.1910014140296086</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -798,40 +798,40 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>47.27637338703806</v>
+        <v>47.27637338933283</v>
       </c>
       <c r="J3" t="n">
-        <v>35.95501239340445</v>
+        <v>35.955012437005</v>
       </c>
       <c r="K3" t="n">
-        <v>45.77639300770748</v>
+        <v>44.74570471351977</v>
       </c>
       <c r="L3" t="n">
-        <v>221487.4</v>
+        <v>221253</v>
       </c>
       <c r="M3" t="n">
-        <v>110204.1</v>
+        <v>110145.5</v>
       </c>
       <c r="N3" t="n">
-        <v>122567.2</v>
+        <v>122537.9</v>
       </c>
       <c r="O3" t="n">
-        <v>2.009792739108617</v>
+        <v>2.008733901975115</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.4906311371264209</v>
+        <v>-0.4924402144797</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.5737274014355255</v>
+        <v>-0.5763756701804627</v>
       </c>
       <c r="R3" t="n">
-        <v>0.08309626430910455</v>
+        <v>0.08393545570076266</v>
       </c>
       <c r="S3" t="n">
-        <v>0.06701321309775787</v>
+        <v>0.0679180549412417</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.02687681640216855</v>
+        <v>-0.02590133805065231</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -944,40 +944,40 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>34.18610773146303</v>
+        <v>34.18610773317602</v>
       </c>
       <c r="J4" t="n">
-        <v>33.28733692638864</v>
+        <v>33.28733695893552</v>
       </c>
       <c r="K4" t="n">
-        <v>42.21818475157023</v>
+        <v>40.56850265441454</v>
       </c>
       <c r="L4" t="n">
-        <v>461995.8</v>
+        <v>461555.4</v>
       </c>
       <c r="M4" t="n">
-        <v>236668.2</v>
+        <v>236558.1</v>
       </c>
       <c r="N4" t="n">
-        <v>280576.025</v>
+        <v>280520.975</v>
       </c>
       <c r="O4" t="n">
-        <v>1.952082282283805</v>
+        <v>1.951129130644861</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.8830525946715397</v>
+        <v>-0.8982488333974175</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.6944427464667224</v>
+        <v>-0.7166881877605107</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.1886098482048173</v>
+        <v>-0.1815606456369068</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2022086532695517</v>
+        <v>-0.1946079873070055</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2179415148026154</v>
+        <v>-0.209747502603725</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1090,40 +1090,40 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>44.73089591693072</v>
+        <v>44.73089591697954</v>
       </c>
       <c r="J5" t="n">
-        <v>39.60988867841668</v>
+        <v>39.60988867934437</v>
       </c>
       <c r="K5" t="n">
-        <v>47.03928090938346</v>
+        <v>46.24359449614607</v>
       </c>
       <c r="L5" t="n">
-        <v>88783.2</v>
+        <v>88711.2</v>
       </c>
       <c r="M5" t="n">
-        <v>45524.05</v>
+        <v>45506.05</v>
       </c>
       <c r="N5" t="n">
-        <v>42565.625</v>
+        <v>42556.625</v>
       </c>
       <c r="O5" t="n">
-        <v>1.950248275362144</v>
+        <v>1.949437492377387</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1227288263487747</v>
+        <v>-0.123452460050526</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.186255409425281</v>
+        <v>-0.1873147209642007</v>
       </c>
       <c r="R5" t="n">
-        <v>0.06352658307650635</v>
+        <v>0.06386226091367472</v>
       </c>
       <c r="S5" t="n">
-        <v>0.07251626717645532</v>
+        <v>0.07287820529452749</v>
       </c>
       <c r="T5" t="n">
-        <v>0.05827953253853507</v>
+        <v>0.0586697253676022</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1236,40 +1236,40 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>41.92743001728621</v>
+        <v>41.92743001772564</v>
       </c>
       <c r="J6" t="n">
-        <v>41.46649282230376</v>
+        <v>41.46649283065278</v>
       </c>
       <c r="K6" t="n">
-        <v>46.72074869750747</v>
+        <v>45.12248202603304</v>
       </c>
       <c r="L6" t="n">
-        <v>7401</v>
+        <v>7402.4</v>
       </c>
       <c r="M6" t="n">
-        <v>4100.25</v>
+        <v>4100.6</v>
       </c>
       <c r="N6" t="n">
-        <v>4462.6</v>
+        <v>4462.775</v>
       </c>
       <c r="O6" t="n">
-        <v>1.805011889518932</v>
+        <v>1.805199239135736</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.288007934657287</v>
+        <v>-0.2923497368677559</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.4346652915656134</v>
+        <v>-0.4410211607990924</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1466573569083264</v>
+        <v>0.1486714239313365</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1611287067526771</v>
+        <v>0.1633003354611171</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1266874813420205</v>
+        <v>0.1290286383164353</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN6"/>
+  <dimension ref="A1:AN3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,67 +625,67 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3288</t>
+          <t>9919</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>點晶</t>
+          <t>康那香</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>20.89999961853027</v>
+        <v>13.85000038146973</v>
       </c>
       <c r="G2" t="n">
-        <v>20.78750009536743</v>
+        <v>13.95249991416931</v>
       </c>
       <c r="H2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>49.94965575673093</v>
+        <v>42.24232074453545</v>
       </c>
       <c r="J2" t="n">
-        <v>49.69690539265871</v>
+        <v>40.41589043932669</v>
       </c>
       <c r="K2" t="n">
-        <v>47.92309313665962</v>
+        <v>46.37466459696413</v>
       </c>
       <c r="L2" t="n">
-        <v>104813.8</v>
+        <v>331116</v>
       </c>
       <c r="M2" t="n">
-        <v>45951.35</v>
+        <v>217003.2</v>
       </c>
       <c r="N2" t="n">
-        <v>50501.075</v>
+        <v>211656.875</v>
       </c>
       <c r="O2" t="n">
-        <v>2.280973246705483</v>
+        <v>1.525857683204672</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.1703417915162682</v>
+        <v>-0.0194730518573536</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.3093559999051598</v>
+        <v>0.003999157635170658</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1390142083888917</v>
+        <v>-0.02347220949252425</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1664009341468143</v>
+        <v>-0.02490794193822189</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1910014140296086</v>
+        <v>-0.009986115626497222</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -714,28 +714,28 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>177</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
@@ -744,23 +744,23 @@
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>177</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>778.1510000000001</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>793.1510000000001</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -775,12 +775,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2230</t>
+          <t>6546</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>泰茂</t>
+          <t>正基</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -789,49 +789,49 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>21.75</v>
+        <v>59.40000152587891</v>
       </c>
       <c r="G3" t="n">
-        <v>21.89499998092651</v>
+        <v>60.35999984741211</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>47.27637338933283</v>
+        <v>41.83836618822166</v>
       </c>
       <c r="J3" t="n">
-        <v>35.955012437005</v>
+        <v>36.1376800673401</v>
       </c>
       <c r="K3" t="n">
-        <v>44.74570471351977</v>
+        <v>45.38959707074613</v>
       </c>
       <c r="L3" t="n">
-        <v>221253</v>
+        <v>472304.2</v>
       </c>
       <c r="M3" t="n">
-        <v>110145.5</v>
+        <v>241762.6</v>
       </c>
       <c r="N3" t="n">
-        <v>122537.9</v>
+        <v>281798.45</v>
       </c>
       <c r="O3" t="n">
-        <v>2.008733901975115</v>
+        <v>1.953586700341575</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.4924402144797</v>
+        <v>-0.8451925136215976</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.5763756701804627</v>
+        <v>-0.7369015790298381</v>
       </c>
       <c r="R3" t="n">
-        <v>0.08393545570076266</v>
+        <v>-0.1082909345917595</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0679180549412417</v>
+        <v>-0.1837322605385423</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.02590133805065231</v>
+        <v>-0.1969491293967955</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -906,445 +906,7 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>70</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>6546</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>正基</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>58.59999847412109</v>
-      </c>
-      <c r="G4" t="n">
-        <v>60.53499984741211</v>
-      </c>
-      <c r="H4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>34.18610773317602</v>
-      </c>
-      <c r="J4" t="n">
-        <v>33.28733695893552</v>
-      </c>
-      <c r="K4" t="n">
-        <v>40.56850265441454</v>
-      </c>
-      <c r="L4" t="n">
-        <v>461555.4</v>
-      </c>
-      <c r="M4" t="n">
-        <v>236558.1</v>
-      </c>
-      <c r="N4" t="n">
-        <v>280520.975</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.951129130644861</v>
-      </c>
-      <c r="P4" t="n">
-        <v>-0.8982488333974175</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>-0.7166881877605107</v>
-      </c>
-      <c r="R4" t="n">
-        <v>-0.1815606456369068</v>
-      </c>
-      <c r="S4" t="n">
-        <v>-0.1946079873070055</v>
-      </c>
-      <c r="T4" t="n">
-        <v>-0.209747502603725</v>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>70</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>5344</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>立衛</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>13.35000038146973</v>
-      </c>
-      <c r="G5" t="n">
-        <v>13.4050000667572</v>
-      </c>
-      <c r="H5" t="b">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>44.73089591697954</v>
-      </c>
-      <c r="J5" t="n">
-        <v>39.60988867934437</v>
-      </c>
-      <c r="K5" t="n">
-        <v>46.24359449614607</v>
-      </c>
-      <c r="L5" t="n">
-        <v>88711.2</v>
-      </c>
-      <c r="M5" t="n">
-        <v>45506.05</v>
-      </c>
-      <c r="N5" t="n">
-        <v>42556.625</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.949437492377387</v>
-      </c>
-      <c r="P5" t="n">
-        <v>-0.123452460050526</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>-0.1873147209642007</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.06386226091367472</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.07287820529452749</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.0586697253676022</v>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>70</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>6856</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>鑫傳</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>41.79999923706055</v>
-      </c>
-      <c r="G6" t="n">
-        <v>41.80499954223633</v>
-      </c>
-      <c r="H6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>41.92743001772564</v>
-      </c>
-      <c r="J6" t="n">
-        <v>41.46649283065278</v>
-      </c>
-      <c r="K6" t="n">
-        <v>45.12248202603304</v>
-      </c>
-      <c r="L6" t="n">
-        <v>7402.4</v>
-      </c>
-      <c r="M6" t="n">
-        <v>4100.6</v>
-      </c>
-      <c r="N6" t="n">
-        <v>4462.775</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.805199239135736</v>
-      </c>
-      <c r="P6" t="n">
-        <v>-0.2923497368677559</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>-0.4410211607990924</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.1486714239313365</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.1633003354611171</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0.1290286383164353</v>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN3"/>
+  <dimension ref="A1:AN4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -629,113 +629,113 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>9919</t>
+          <t>6546</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>康那香</t>
+          <t>正基</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>13.85000038146973</v>
+        <v>59.70000076293945</v>
       </c>
       <c r="G2" t="n">
-        <v>13.95249991416931</v>
+        <v>60.19499988555908</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>42.24232074453545</v>
+        <v>49.32081771861515</v>
       </c>
       <c r="J2" t="n">
-        <v>40.41589043932669</v>
+        <v>40.53205932244084</v>
       </c>
       <c r="K2" t="n">
-        <v>46.37466459696413</v>
+        <v>47.42082853499048</v>
       </c>
       <c r="L2" t="n">
-        <v>331116</v>
+        <v>476752.6</v>
       </c>
       <c r="M2" t="n">
-        <v>217003.2</v>
+        <v>243177.5</v>
       </c>
       <c r="N2" t="n">
-        <v>211656.875</v>
+        <v>280705.95</v>
       </c>
       <c r="O2" t="n">
-        <v>1.525857683204672</v>
+        <v>1.960512794152419</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.0194730518573536</v>
+        <v>-0.7787989560016086</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.003999157635170658</v>
+        <v>-0.7516831654583966</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.02347220949252425</v>
+        <v>-0.027115790543212</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.02490794193822189</v>
+        <v>-0.1057573608618585</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.009986115626497222</v>
+        <v>-0.1810009032927592</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
       <c r="AB2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>177</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
@@ -744,23 +744,23 @@
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>177</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>778.1510000000001</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>793.1510000000001</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -771,142 +771,288 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>80</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>6616</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>特昇-KY</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>8.260000228881836</v>
+      </c>
+      <c r="G3" t="n">
+        <v>8.324500036239623</v>
+      </c>
+      <c r="H3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>47.48855333589404</v>
+      </c>
+      <c r="J3" t="n">
+        <v>45.0822802885137</v>
+      </c>
+      <c r="K3" t="n">
+        <v>46.10044397132606</v>
+      </c>
+      <c r="L3" t="n">
+        <v>30057.4</v>
+      </c>
+      <c r="M3" t="n">
+        <v>16267.6</v>
+      </c>
+      <c r="N3" t="n">
+        <v>17307.15</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.847684968895227</v>
+      </c>
+      <c r="P3" t="n">
+        <v>-0.08367298854147798</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-0.08245089071069328</v>
+      </c>
+      <c r="R3" t="n">
+        <v>-0.001222097830784696</v>
+      </c>
+      <c r="S3" t="n">
+        <v>-0.007802147132390871</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-0.008307485016949695</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>70</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>6546</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>正基</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>7757</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>金色三麥</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v>59.40000152587891</v>
-      </c>
-      <c r="G3" t="n">
-        <v>60.35999984741211</v>
-      </c>
-      <c r="H3" t="b">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>41.83836618822166</v>
-      </c>
-      <c r="J3" t="n">
-        <v>36.1376800673401</v>
-      </c>
-      <c r="K3" t="n">
-        <v>45.38959707074613</v>
-      </c>
-      <c r="L3" t="n">
-        <v>472304.2</v>
-      </c>
-      <c r="M3" t="n">
-        <v>241762.6</v>
-      </c>
-      <c r="N3" t="n">
-        <v>281798.45</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.953586700341575</v>
-      </c>
-      <c r="P3" t="n">
-        <v>-0.8451925136215976</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>-0.7369015790298381</v>
-      </c>
-      <c r="R3" t="n">
-        <v>-0.1082909345917595</v>
-      </c>
-      <c r="S3" t="n">
-        <v>-0.1837322605385423</v>
-      </c>
-      <c r="T3" t="n">
-        <v>-0.1969491293967955</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="F4" t="n">
+        <v>89.19999694824219</v>
+      </c>
+      <c r="G4" t="n">
+        <v>89.09499893188476</v>
+      </c>
+      <c r="H4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>39.31296633660095</v>
+      </c>
+      <c r="J4" t="n">
+        <v>39.13095397419542</v>
+      </c>
+      <c r="K4" t="n">
+        <v>48.75714017270074</v>
+      </c>
+      <c r="L4" t="n">
+        <v>29813</v>
+      </c>
+      <c r="M4" t="n">
+        <v>15207.4</v>
+      </c>
+      <c r="N4" t="n">
+        <v>13413.075</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.960427160461354</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.07063693825296014</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-0.1183381901154378</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.188975128368398</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.2740988938667253</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.2875756409295793</v>
+      </c>
+      <c r="U4" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN4"/>
+  <dimension ref="A1:AN7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,71 +625,71 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>6546</t>
+          <t>2321</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>正基</t>
+          <t>東訊</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>59.70000076293945</v>
+        <v>25.35000038146973</v>
       </c>
       <c r="G2" t="n">
-        <v>60.19499988555908</v>
+        <v>26.14348058700562</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>49.32081771861515</v>
+        <v>36.41532893088417</v>
       </c>
       <c r="J2" t="n">
-        <v>40.53205932244084</v>
+        <v>34.12028665224084</v>
       </c>
       <c r="K2" t="n">
-        <v>47.42082853499048</v>
+        <v>46.02342049181372</v>
       </c>
       <c r="L2" t="n">
-        <v>476752.6</v>
+        <v>14525.2</v>
       </c>
       <c r="M2" t="n">
-        <v>243177.5</v>
+        <v>5666.95</v>
       </c>
       <c r="N2" t="n">
-        <v>280705.95</v>
+        <v>5857.35</v>
       </c>
       <c r="O2" t="n">
-        <v>1.960512794152419</v>
+        <v>2.563142431113739</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.7787989560016086</v>
+        <v>-0.6213315130455044</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.7516831654583966</v>
+        <v>-0.4965494959972625</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.027115790543212</v>
+        <v>-0.1247820170482419</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1057573608618585</v>
+        <v>-0.1961125604110884</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1810009032927592</v>
+        <v>-0.3376553642076515</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -729,10 +729,10 @@
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>-0.089</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>-0.089</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -741,10 +741,10 @@
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>-0.089</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>-0.089</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
@@ -753,14 +753,14 @@
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>-0.089</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>-0.089</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -771,71 +771,71 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>6616</t>
+          <t>6988</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>特昇-KY</t>
+          <t>威力暘-創</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>8.260000228881836</v>
+        <v>11.69999980926514</v>
       </c>
       <c r="G3" t="n">
-        <v>8.324500036239623</v>
+        <v>11.84499988555908</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>47.48855333589404</v>
+        <v>37.15533527575053</v>
       </c>
       <c r="J3" t="n">
-        <v>45.0822802885137</v>
+        <v>35.93277563805321</v>
       </c>
       <c r="K3" t="n">
-        <v>46.10044397132606</v>
+        <v>46.19289345804765</v>
       </c>
       <c r="L3" t="n">
-        <v>30057.4</v>
+        <v>150600</v>
       </c>
       <c r="M3" t="n">
-        <v>16267.6</v>
+        <v>70150</v>
       </c>
       <c r="N3" t="n">
-        <v>17307.15</v>
+        <v>58975</v>
       </c>
       <c r="O3" t="n">
-        <v>1.847684968895227</v>
+        <v>2.146828225231646</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.08367298854147798</v>
+        <v>-0.1093392892648151</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.08245089071069328</v>
+        <v>-0.09996359699054624</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.001222097830784696</v>
+        <v>-0.009375692274268821</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.007802147132390871</v>
+        <v>-0.0183403869499785</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.008307485016949695</v>
+        <v>-0.00423475856245234</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -869,44 +869,44 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>-346</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>-2.02</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>-348.02</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>-636.579</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>-41.23399999999999</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>-677.813</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>7757</t>
+          <t>8087</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>金色三麥</t>
+          <t>麗升能源</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,124 +935,562 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>89.19999694824219</v>
+        <v>24</v>
       </c>
       <c r="G4" t="n">
-        <v>89.09499893188476</v>
+        <v>24.66499996185303</v>
       </c>
       <c r="H4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>42.80020947801863</v>
+      </c>
+      <c r="J4" t="n">
+        <v>31.94138458924237</v>
+      </c>
+      <c r="K4" t="n">
+        <v>41.94983708769146</v>
+      </c>
+      <c r="L4" t="n">
+        <v>57400.8</v>
+      </c>
+      <c r="M4" t="n">
+        <v>30619.95</v>
+      </c>
+      <c r="N4" t="n">
+        <v>26496.375</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.874620957904895</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-0.875692535323342</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-0.9269228939976774</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.05123035867433534</v>
+      </c>
+      <c r="S4" t="n">
+        <v>-0.003063734658765527</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-0.07576244599724036</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>70</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>7753</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>星亞</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>35.65000152587891</v>
+      </c>
+      <c r="G5" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="H5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>45.44253845061415</v>
+      </c>
+      <c r="J5" t="n">
+        <v>36.28451844710329</v>
+      </c>
+      <c r="K5" t="n">
+        <v>36.44840990127505</v>
+      </c>
+      <c r="L5" t="n">
+        <v>28614.2</v>
+      </c>
+      <c r="M5" t="n">
+        <v>16281.45</v>
+      </c>
+      <c r="N5" t="n">
+        <v>17705.25</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.757472460990882</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-0.4596761537426346</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-0.5510495066473446</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.09137335290471005</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.08622709349021118</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.0740614508480808</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>70</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>6762</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>達亞</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>156</v>
+      </c>
+      <c r="G6" t="n">
+        <v>161.925</v>
+      </c>
+      <c r="H6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>42.61216654644564</v>
+      </c>
+      <c r="J6" t="n">
+        <v>36.73376269862848</v>
+      </c>
+      <c r="K6" t="n">
+        <v>31.40729571579921</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2669.6</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1689.3</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1398.35</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.580299532350678</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-2.357689799018516</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-2.068044665766936</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-0.2896451332515797</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-0.1711514941423113</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-0.44784930485404</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>70</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2063</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>世鎧精密</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>23.79999923706055</v>
+      </c>
+      <c r="G7" t="n">
+        <v>23.78499984741211</v>
+      </c>
+      <c r="H7" t="b">
         <v>1</v>
       </c>
-      <c r="I4" t="n">
-        <v>39.31296633660095</v>
-      </c>
-      <c r="J4" t="n">
-        <v>39.13095397419542</v>
-      </c>
-      <c r="K4" t="n">
-        <v>48.75714017270074</v>
-      </c>
-      <c r="L4" t="n">
-        <v>29813</v>
-      </c>
-      <c r="M4" t="n">
-        <v>15207.4</v>
-      </c>
-      <c r="N4" t="n">
-        <v>13413.075</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.960427160461354</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.07063693825296014</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>-0.1183381901154378</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.188975128368398</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.2740988938667253</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0.2875756409295793</v>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
+      <c r="I7" t="n">
+        <v>42.07171895081849</v>
+      </c>
+      <c r="J7" t="n">
+        <v>32.06941407016899</v>
+      </c>
+      <c r="K7" t="n">
+        <v>49.44815543561866</v>
+      </c>
+      <c r="L7" t="n">
+        <v>44602.8</v>
+      </c>
+      <c r="M7" t="n">
+        <v>29522.15</v>
+      </c>
+      <c r="N7" t="n">
+        <v>29661.325</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.510824922981558</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-0.1133821842877509</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-0.1142376711957007</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.0008554869079497457</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-0.01770532566038953</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-0.02890001123722963</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -869,40 +869,40 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>-4</v>
+        <v>-1.899</v>
       </c>
       <c r="AE3" t="n">
-        <v>1</v>
+        <v>0.101</v>
       </c>
       <c r="AF3" t="n">
-        <v>-346</v>
+        <v>-278</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>-2.02</v>
+        <v>-5.919</v>
       </c>
       <c r="AI3" t="n">
-        <v>-348.02</v>
+        <v>-283.919</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-636.579</v>
+        <v>-631.579</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>-41.23399999999999</v>
+        <v>-34.133</v>
       </c>
       <c r="AM3" t="n">
-        <v>-677.813</v>
+        <v>-665.712</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN7"/>
+  <dimension ref="A1:AN10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,16 +625,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2321</t>
+          <t>6794</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>東訊</t>
+          <t>向榮生技</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -643,49 +643,49 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>25.35000038146973</v>
+        <v>73.59999847412109</v>
       </c>
       <c r="G2" t="n">
-        <v>26.14348058700562</v>
+        <v>75.1150001525879</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>36.41532893088417</v>
+        <v>45.67400864993792</v>
       </c>
       <c r="J2" t="n">
-        <v>34.12028665224084</v>
+        <v>45.04394726501854</v>
       </c>
       <c r="K2" t="n">
-        <v>46.02342049181372</v>
+        <v>45.42724692665026</v>
       </c>
       <c r="L2" t="n">
-        <v>14525.2</v>
+        <v>116814.4</v>
       </c>
       <c r="M2" t="n">
-        <v>5666.95</v>
+        <v>44563.65</v>
       </c>
       <c r="N2" t="n">
-        <v>5857.35</v>
+        <v>43731.85</v>
       </c>
       <c r="O2" t="n">
-        <v>2.563142431113739</v>
+        <v>2.621293363537322</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.6213315130455044</v>
+        <v>-0.2557567791807855</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.4965494959972625</v>
+        <v>-0.2957588220473995</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.1247820170482419</v>
+        <v>0.04000204286661396</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1961125604110884</v>
+        <v>0.1443147738140153</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3376553642076515</v>
+        <v>0.05875464840272365</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -723,44 +723,44 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.089</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.089</v>
+        <v>5</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0.089</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0.089</v>
+        <v>62</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>80.416</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>-0.089</v>
+        <v>2</v>
       </c>
       <c r="AM2" t="n">
-        <v>-0.089</v>
+        <v>82.416</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>
@@ -771,16 +771,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>6988</t>
+          <t>8101</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>威力暘-創</t>
+          <t>華冠</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -789,49 +789,49 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>11.69999980926514</v>
+        <v>10.60000038146973</v>
       </c>
       <c r="G3" t="n">
-        <v>11.84499988555908</v>
+        <v>11.52250003814697</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>37.15533527575053</v>
+        <v>45.78576781220291</v>
       </c>
       <c r="J3" t="n">
-        <v>35.93277563805321</v>
+        <v>34.222849863879</v>
       </c>
       <c r="K3" t="n">
-        <v>46.19289345804765</v>
+        <v>40.57292044402338</v>
       </c>
       <c r="L3" t="n">
-        <v>150600</v>
+        <v>17843.6</v>
       </c>
       <c r="M3" t="n">
-        <v>70150</v>
+        <v>7662.1</v>
       </c>
       <c r="N3" t="n">
-        <v>58975</v>
+        <v>12534.1</v>
       </c>
       <c r="O3" t="n">
-        <v>2.146828225231646</v>
+        <v>2.328813249631302</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.1093392892648151</v>
+        <v>-0.3674228272998565</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.09996359699054624</v>
+        <v>-0.2952324499637203</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.009375692274268821</v>
+        <v>-0.07219037733613626</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0183403869499785</v>
+        <v>-0.06226709775363848</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.00423475856245234</v>
+        <v>-0.09828623371944689</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -869,44 +869,44 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>-1.899</v>
+        <v>0.225</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.101</v>
+        <v>0.225</v>
       </c>
       <c r="AF3" t="n">
-        <v>-278</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>-5.919</v>
+        <v>0.225</v>
       </c>
       <c r="AI3" t="n">
-        <v>-283.919</v>
+        <v>0.225</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-631.579</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>-34.133</v>
+        <v>0.225</v>
       </c>
       <c r="AM3" t="n">
-        <v>-665.712</v>
+        <v>0.225</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>
@@ -921,63 +921,63 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>8087</t>
+          <t>2321</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>麗升能源</t>
+          <t>東訊</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>24</v>
+        <v>25.5</v>
       </c>
       <c r="G4" t="n">
-        <v>24.66499996185303</v>
+        <v>26.09277420043945</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>42.80020947801863</v>
+        <v>48.51931019533956</v>
       </c>
       <c r="J4" t="n">
-        <v>31.94138458924237</v>
+        <v>38.9199611478012</v>
       </c>
       <c r="K4" t="n">
-        <v>41.94983708769146</v>
+        <v>45.94837645035378</v>
       </c>
       <c r="L4" t="n">
-        <v>57400.8</v>
+        <v>15313.8</v>
       </c>
       <c r="M4" t="n">
-        <v>30619.95</v>
+        <v>5861.3</v>
       </c>
       <c r="N4" t="n">
-        <v>26496.375</v>
+        <v>5917.8</v>
       </c>
       <c r="O4" t="n">
-        <v>1.874620957904895</v>
+        <v>2.612696841997509</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.875692535323342</v>
+        <v>-0.5695169995591165</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9269228939976774</v>
+        <v>-0.5094706335126689</v>
       </c>
       <c r="R4" t="n">
-        <v>0.05123035867433534</v>
+        <v>-0.06004636604644764</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.003063734658765527</v>
+        <v>-0.1254438386630213</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.07576244599724036</v>
+        <v>-0.1968260471518218</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1021,10 +1021,10 @@
         <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>-0.089</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>-0.089</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -1033,10 +1033,10 @@
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>-0.089</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>-0.089</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
@@ -1045,14 +1045,14 @@
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>-0.089</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>-0.089</v>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>7753</t>
+          <t>6597</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>星亞</t>
+          <t>立誠</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1081,49 +1081,49 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>35.65000152587891</v>
+        <v>64.90000152587891</v>
       </c>
       <c r="G5" t="n">
-        <v>35.9</v>
+        <v>69.23999977111816</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>45.44253845061415</v>
+        <v>34.04587448406922</v>
       </c>
       <c r="J5" t="n">
-        <v>36.28451844710329</v>
+        <v>33.22849082389921</v>
       </c>
       <c r="K5" t="n">
-        <v>36.44840990127505</v>
+        <v>35.9246585283211</v>
       </c>
       <c r="L5" t="n">
-        <v>28614.2</v>
+        <v>16800</v>
       </c>
       <c r="M5" t="n">
-        <v>16281.45</v>
+        <v>7800</v>
       </c>
       <c r="N5" t="n">
-        <v>17705.25</v>
+        <v>8375.275</v>
       </c>
       <c r="O5" t="n">
-        <v>1.757472460990882</v>
+        <v>2.153846153846154</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.4596761537426346</v>
+        <v>-1.587559736413596</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.5510495066473446</v>
+        <v>-0.8002630888379418</v>
       </c>
       <c r="R5" t="n">
-        <v>0.09137335290471005</v>
+        <v>-0.7872966475756538</v>
       </c>
       <c r="S5" t="n">
-        <v>0.08622709349021118</v>
+        <v>-0.9014579474895981</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0740614508480808</v>
+        <v>-0.9994251541703534</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>
@@ -1213,12 +1213,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>6762</t>
+          <t>6720</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>達亞</t>
+          <t>久昌</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1227,49 +1227,49 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>156</v>
+        <v>124.5</v>
       </c>
       <c r="G6" t="n">
-        <v>161.925</v>
+        <v>128.625</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>42.61216654644564</v>
+        <v>40.99237256478649</v>
       </c>
       <c r="J6" t="n">
-        <v>36.73376269862848</v>
+        <v>34.76378778334816</v>
       </c>
       <c r="K6" t="n">
-        <v>31.40729571579921</v>
+        <v>32.21235580684106</v>
       </c>
       <c r="L6" t="n">
-        <v>2669.6</v>
+        <v>55000</v>
       </c>
       <c r="M6" t="n">
-        <v>1689.3</v>
+        <v>28214.95</v>
       </c>
       <c r="N6" t="n">
-        <v>1398.35</v>
+        <v>23098.8</v>
       </c>
       <c r="O6" t="n">
-        <v>1.580299532350678</v>
+        <v>1.949321193197223</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.357689799018516</v>
+        <v>-2.221333686848624</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.068044665766936</v>
+        <v>-1.988632743485295</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.2896451332515797</v>
+        <v>-0.2327009433633291</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1711514941423113</v>
+        <v>-0.2065919405045518</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.44784930485404</v>
+        <v>-0.1195782326264945</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>
@@ -1359,138 +1359,576 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>8087</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>麗升能源</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>23.20000076293945</v>
+      </c>
+      <c r="G7" t="n">
+        <v>24.475</v>
+      </c>
+      <c r="H7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>36.86681294325993</v>
+      </c>
+      <c r="J7" t="n">
+        <v>33.58319407495583</v>
+      </c>
+      <c r="K7" t="n">
+        <v>37.60275942677426</v>
+      </c>
+      <c r="L7" t="n">
+        <v>60000.8</v>
+      </c>
+      <c r="M7" t="n">
+        <v>32319.95</v>
+      </c>
+      <c r="N7" t="n">
+        <v>27371.375</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.856463268043422</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-0.8729782278491456</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-0.9111037705422428</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.0381255426930972</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.04923970938002786</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-0.005209784055180577</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>70</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>5487</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>通泰</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>28.79999923706055</v>
+      </c>
+      <c r="G8" t="n">
+        <v>29.13499994277954</v>
+      </c>
+      <c r="H8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>32.03827663713649</v>
+      </c>
+      <c r="J8" t="n">
+        <v>31.41781674404452</v>
+      </c>
+      <c r="K8" t="n">
+        <v>47.07464543940775</v>
+      </c>
+      <c r="L8" t="n">
+        <v>94077.2</v>
+      </c>
+      <c r="M8" t="n">
+        <v>58398.65</v>
+      </c>
+      <c r="N8" t="n">
+        <v>63883.925</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.61094819828883</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-0.06830349613013809</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-0.01450310612625968</v>
+      </c>
+      <c r="R8" t="n">
+        <v>-0.0538003900038784</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-0.04933138242375661</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-0.06860564110532222</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>70</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>6762</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>達亞</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>156</v>
+      </c>
+      <c r="G9" t="n">
+        <v>161.475</v>
+      </c>
+      <c r="H9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>43.55962618124327</v>
+      </c>
+      <c r="J9" t="n">
+        <v>39.00905050310141</v>
+      </c>
+      <c r="K9" t="n">
+        <v>37.28315181512656</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2669.6</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1689.3</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1371.65</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.580299532350678</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-2.346002335251825</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-1.953785404938932</v>
+      </c>
+      <c r="R9" t="n">
+        <v>-0.3922169303128933</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-0.3568619480207478</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-0.243615591749468</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>70</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>2063</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>世鎧精密</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="F7" t="n">
-        <v>23.79999923706055</v>
-      </c>
-      <c r="G7" t="n">
-        <v>23.78499984741211</v>
-      </c>
-      <c r="H7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7" t="n">
-        <v>42.07171895081849</v>
-      </c>
-      <c r="J7" t="n">
-        <v>32.06941407016899</v>
-      </c>
-      <c r="K7" t="n">
-        <v>49.44815543561866</v>
-      </c>
-      <c r="L7" t="n">
-        <v>44602.8</v>
-      </c>
-      <c r="M7" t="n">
-        <v>29522.15</v>
-      </c>
-      <c r="N7" t="n">
-        <v>29661.325</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.510824922981558</v>
-      </c>
-      <c r="P7" t="n">
-        <v>-0.1133821842877509</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>-0.1142376711957007</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.0008554869079497457</v>
-      </c>
-      <c r="S7" t="n">
-        <v>-0.01770532566038953</v>
-      </c>
-      <c r="T7" t="n">
-        <v>-0.02890001123722963</v>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
+      <c r="F10" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="G10" t="n">
+        <v>23.76999988555908</v>
+      </c>
+      <c r="H10" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>37.30707581715189</v>
+      </c>
+      <c r="J10" t="n">
+        <v>33.81530130845434</v>
+      </c>
+      <c r="K10" t="n">
+        <v>41.28135773870192</v>
+      </c>
+      <c r="L10" t="n">
+        <v>40000</v>
+      </c>
+      <c r="M10" t="n">
+        <v>25722.15</v>
+      </c>
+      <c r="N10" t="n">
+        <v>30086.325</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.555079960267707</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-0.1216739559580127</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-0.1161822292695655</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-0.005491726688447135</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.00103645941868559</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-0.01751022552469521</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN10"/>
+  <dimension ref="A1:AN9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -629,12 +629,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>6794</t>
+          <t>8101</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>向榮生技</t>
+          <t>華冠</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -643,49 +643,49 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>73.59999847412109</v>
+        <v>10.19999980926514</v>
       </c>
       <c r="G2" t="n">
-        <v>75.1150001525879</v>
+        <v>11.43250002861023</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>45.67400864993792</v>
+        <v>40.96340180659534</v>
       </c>
       <c r="J2" t="n">
-        <v>45.04394726501854</v>
+        <v>36.46970046861549</v>
       </c>
       <c r="K2" t="n">
-        <v>45.42724692665026</v>
+        <v>36.95992248001282</v>
       </c>
       <c r="L2" t="n">
-        <v>116814.4</v>
+        <v>16715.8</v>
       </c>
       <c r="M2" t="n">
-        <v>44563.65</v>
+        <v>7780.35</v>
       </c>
       <c r="N2" t="n">
-        <v>43731.85</v>
+        <v>12137.475</v>
       </c>
       <c r="O2" t="n">
-        <v>2.621293363537322</v>
+        <v>2.148463758057157</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.2557567791807855</v>
+        <v>-0.4192299397869128</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.2957588220473995</v>
+        <v>-0.3227756848798042</v>
       </c>
       <c r="R2" t="n">
-        <v>0.04000204286661396</v>
+        <v>-0.09645425490710857</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1443147738140153</v>
+        <v>-0.07110456988531622</v>
       </c>
       <c r="T2" t="n">
-        <v>0.05875464840272365</v>
+        <v>-0.06109652670874066</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -723,44 +723,44 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>0.225</v>
       </c>
       <c r="AE2" t="n">
-        <v>5</v>
+        <v>0.225</v>
       </c>
       <c r="AF2" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>0.225</v>
       </c>
       <c r="AI2" t="n">
-        <v>62</v>
+        <v>0.225</v>
       </c>
       <c r="AJ2" t="n">
-        <v>80.416</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>2</v>
+        <v>0.225</v>
       </c>
       <c r="AM2" t="n">
-        <v>82.416</v>
+        <v>0.225</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -771,16 +771,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>8101</t>
+          <t>1467</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>華冠</t>
+          <t>南緯</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -789,49 +789,49 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>10.60000038146973</v>
+        <v>8.210000038146973</v>
       </c>
       <c r="G3" t="n">
-        <v>11.52250003814697</v>
+        <v>8.103499960899352</v>
       </c>
       <c r="H3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>45.78576781220291</v>
+        <v>46.21977898022163</v>
       </c>
       <c r="J3" t="n">
-        <v>34.222849863879</v>
+        <v>45.36872431806854</v>
       </c>
       <c r="K3" t="n">
-        <v>40.57292044402338</v>
+        <v>49.65275989398086</v>
       </c>
       <c r="L3" t="n">
-        <v>17843.6</v>
+        <v>672300.2</v>
       </c>
       <c r="M3" t="n">
-        <v>7662.1</v>
+        <v>266832.85</v>
       </c>
       <c r="N3" t="n">
-        <v>12534.1</v>
+        <v>265943.575</v>
       </c>
       <c r="O3" t="n">
-        <v>2.328813249631302</v>
+        <v>2.519555594447985</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.3674228272998565</v>
+        <v>-0.0714324942909812</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2952324499637203</v>
+        <v>-0.1160784624651062</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.07219037733613626</v>
+        <v>0.044645968174125</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.06226709775363848</v>
+        <v>0.04345950770641824</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.09828623371944689</v>
+        <v>0.06116435381077001</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -869,44 +869,44 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>-15.652</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.225</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.225</v>
+        <v>-15.652</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>-148.965</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.225</v>
+        <v>-23.004</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.225</v>
+        <v>-171.969</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>-31.965</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.225</v>
+        <v>-47.004</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.225</v>
+        <v>-78.96900000000001</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -921,63 +921,63 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2321</t>
+          <t>6597</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>東訊</t>
+          <t>立誠</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>25.5</v>
+        <v>64.80000305175781</v>
       </c>
       <c r="G4" t="n">
-        <v>26.09277420043945</v>
+        <v>68.85499992370606</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>48.51931019533956</v>
+        <v>36.62761944501383</v>
       </c>
       <c r="J4" t="n">
-        <v>38.9199611478012</v>
+        <v>34.3615337404397</v>
       </c>
       <c r="K4" t="n">
-        <v>45.94837645035378</v>
+        <v>37.39825283008025</v>
       </c>
       <c r="L4" t="n">
-        <v>15313.8</v>
+        <v>15800</v>
       </c>
       <c r="M4" t="n">
-        <v>5861.3</v>
+        <v>7800</v>
       </c>
       <c r="N4" t="n">
-        <v>5917.8</v>
+        <v>8125.275</v>
       </c>
       <c r="O4" t="n">
-        <v>2.612696841997509</v>
+        <v>2.025641025641026</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.5695169995591165</v>
+        <v>-1.642209324374349</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.5094706335126689</v>
+        <v>-0.9686523359452234</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.06004636604644764</v>
+        <v>-0.6735569884291256</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1254438386630213</v>
+        <v>-0.7872966475756538</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1968260471518218</v>
+        <v>-0.9014579474895981</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1021,10 +1021,10 @@
         <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0.089</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0.089</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -1033,10 +1033,10 @@
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0.089</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.089</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
@@ -1045,14 +1045,14 @@
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>-0.089</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>-0.089</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>6597</t>
+          <t>8024</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>立誠</t>
+          <t>佑華</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1081,49 +1081,49 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>64.90000152587891</v>
+        <v>12.19999980926514</v>
       </c>
       <c r="G5" t="n">
-        <v>69.23999977111816</v>
+        <v>12.6875</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>34.04587448406922</v>
+        <v>47.06377518895079</v>
       </c>
       <c r="J5" t="n">
-        <v>33.22849082389921</v>
+        <v>46.87078826154868</v>
       </c>
       <c r="K5" t="n">
-        <v>35.9246585283211</v>
+        <v>37.89133783381681</v>
       </c>
       <c r="L5" t="n">
-        <v>16800</v>
+        <v>117814</v>
       </c>
       <c r="M5" t="n">
-        <v>7800</v>
+        <v>64368.65</v>
       </c>
       <c r="N5" t="n">
-        <v>8375.275</v>
+        <v>51158.75</v>
       </c>
       <c r="O5" t="n">
-        <v>2.153846153846154</v>
+        <v>1.830300930654907</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.587559736413596</v>
+        <v>-0.2768509042429379</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.8002630888379418</v>
+        <v>-0.2783648399447723</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.7872966475756538</v>
+        <v>0.001513935701834446</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9014579474895981</v>
+        <v>0.01179401429109145</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9994251541703534</v>
+        <v>0.01089983533981403</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -1213,12 +1213,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>6720</t>
+          <t>8087</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>久昌</t>
+          <t>麗升能源</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1227,49 +1227,49 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>124.5</v>
+        <v>23.5</v>
       </c>
       <c r="G6" t="n">
-        <v>128.625</v>
+        <v>24.3</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>40.99237256478649</v>
+        <v>38.53136023137093</v>
       </c>
       <c r="J6" t="n">
-        <v>34.76378778334816</v>
+        <v>35.23258283659647</v>
       </c>
       <c r="K6" t="n">
-        <v>32.21235580684106</v>
+        <v>40.65829851522468</v>
       </c>
       <c r="L6" t="n">
-        <v>55000</v>
+        <v>56400</v>
       </c>
       <c r="M6" t="n">
-        <v>28214.95</v>
+        <v>32419.95</v>
       </c>
       <c r="N6" t="n">
-        <v>23098.8</v>
+        <v>27396.375</v>
       </c>
       <c r="O6" t="n">
-        <v>1.949321193197223</v>
+        <v>1.739669555320104</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.221333686848624</v>
+        <v>-0.8396146318387494</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.988632743485295</v>
+        <v>-0.8958913580029801</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.2327009433633291</v>
+        <v>0.05627672616423074</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2065919405045518</v>
+        <v>0.03776360457502648</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1195782326264945</v>
+        <v>0.04884951655096081</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -1359,63 +1359,63 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>8087</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>麗升能源</t>
+          <t>宜新實業</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>23.20000076293945</v>
+        <v>17.45000076293945</v>
       </c>
       <c r="G7" t="n">
-        <v>24.475</v>
+        <v>17.53249998092651</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>36.86681294325993</v>
+        <v>40.67842568070256</v>
       </c>
       <c r="J7" t="n">
-        <v>33.58319407495583</v>
+        <v>39.04349456937123</v>
       </c>
       <c r="K7" t="n">
-        <v>37.60275942677426</v>
+        <v>47.93289334437646</v>
       </c>
       <c r="L7" t="n">
-        <v>60000.8</v>
+        <v>63922.8</v>
       </c>
       <c r="M7" t="n">
-        <v>32319.95</v>
+        <v>36750.1</v>
       </c>
       <c r="N7" t="n">
-        <v>27371.375</v>
+        <v>46296.375</v>
       </c>
       <c r="O7" t="n">
-        <v>1.856463268043422</v>
+        <v>1.739391185330108</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.8729782278491456</v>
+        <v>-0.05083599773273306</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9111037705422428</v>
+        <v>-0.02747666906739614</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0381255426930972</v>
+        <v>-0.02335932866533692</v>
       </c>
       <c r="S7" t="n">
-        <v>0.04923970938002786</v>
+        <v>-0.03130777186336196</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.005209784055180577</v>
+        <v>-0.0003285377835912703</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -1453,44 +1453,44 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>-27</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>-79.40000000000001</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>-32</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-111.4</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>-89.40000000000001</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>-103.188</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>-192.588</v>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -1505,63 +1505,63 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>5487</t>
+          <t>6754</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>通泰</t>
+          <t>匯僑設計</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>28.79999923706055</v>
+        <v>40.5</v>
       </c>
       <c r="G8" t="n">
-        <v>29.13499994277954</v>
+        <v>41.67249984741211</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>32.03827663713649</v>
+        <v>45.2449954169259</v>
       </c>
       <c r="J8" t="n">
-        <v>31.41781674404452</v>
+        <v>43.93988660805142</v>
       </c>
       <c r="K8" t="n">
-        <v>47.07464543940775</v>
+        <v>39.45780370741554</v>
       </c>
       <c r="L8" t="n">
-        <v>94077.2</v>
+        <v>26536</v>
       </c>
       <c r="M8" t="n">
-        <v>58398.65</v>
+        <v>16591.85</v>
       </c>
       <c r="N8" t="n">
-        <v>63883.925</v>
+        <v>12423.175</v>
       </c>
       <c r="O8" t="n">
-        <v>1.61094819828883</v>
+        <v>1.599339434722469</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.06830349613013809</v>
+        <v>-0.2485722456074626</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.01450310612625968</v>
+        <v>-0.1663007978245593</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.0538003900038784</v>
+        <v>-0.08227144778290335</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.04933138242375661</v>
+        <v>-0.03461097737999042</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.06860564110532222</v>
+        <v>-0.08082910242531693</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1608,10 +1608,10 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>-42</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -1620,23 +1620,23 @@
         <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>-42</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>-42.758</v>
       </c>
       <c r="AK8" t="n">
         <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>-40.758</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -1651,12 +1651,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>6762</t>
+          <t>7753</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>達亞</t>
+          <t>星亞</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1665,49 +1665,49 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>156</v>
+        <v>35.5</v>
       </c>
       <c r="G9" t="n">
-        <v>161.475</v>
+        <v>35.82000007629394</v>
       </c>
       <c r="H9" t="b">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>43.55962618124327</v>
+        <v>44.64115080930264</v>
       </c>
       <c r="J9" t="n">
-        <v>39.00905050310141</v>
+        <v>42.18351620868729</v>
       </c>
       <c r="K9" t="n">
-        <v>37.28315181512656</v>
+        <v>37.72235392323162</v>
       </c>
       <c r="L9" t="n">
-        <v>2669.6</v>
+        <v>26400</v>
       </c>
       <c r="M9" t="n">
-        <v>1689.3</v>
+        <v>16779.45</v>
       </c>
       <c r="N9" t="n">
-        <v>1371.65</v>
+        <v>17455.25</v>
       </c>
       <c r="O9" t="n">
-        <v>1.580299532350678</v>
+        <v>1.573353119440744</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.346002335251825</v>
+        <v>-0.402191933564751</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.953785404938932</v>
+        <v>-0.4852487657628003</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.3922169303128933</v>
+        <v>0.08305683219804927</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3568619480207478</v>
+        <v>0.09151732938325263</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.243615591749468</v>
+        <v>0.08435796610012714</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -1782,153 +1782,7 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>70</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>2063</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>世鎧精密</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="G10" t="n">
-        <v>23.76999988555908</v>
-      </c>
-      <c r="H10" t="b">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>37.30707581715189</v>
-      </c>
-      <c r="J10" t="n">
-        <v>33.81530130845434</v>
-      </c>
-      <c r="K10" t="n">
-        <v>41.28135773870192</v>
-      </c>
-      <c r="L10" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M10" t="n">
-        <v>25722.15</v>
-      </c>
-      <c r="N10" t="n">
-        <v>30086.325</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.555079960267707</v>
-      </c>
-      <c r="P10" t="n">
-        <v>-0.1216739559580127</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>-0.1161822292695655</v>
-      </c>
-      <c r="R10" t="n">
-        <v>-0.005491726688447135</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.00103645941868559</v>
-      </c>
-      <c r="T10" t="n">
-        <v>-0.01751022552469521</v>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN9"/>
+  <dimension ref="A1:AN10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,49 +643,49 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>10.19999980926514</v>
+        <v>10.30000019073486</v>
       </c>
       <c r="G2" t="n">
-        <v>11.43250002861023</v>
+        <v>11.35000004768372</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>40.96340180659534</v>
+        <v>41.53399199887997</v>
       </c>
       <c r="J2" t="n">
-        <v>36.46970046861549</v>
+        <v>38.1577976025347</v>
       </c>
       <c r="K2" t="n">
-        <v>36.95992248001282</v>
+        <v>38.23175545645226</v>
       </c>
       <c r="L2" t="n">
-        <v>16715.8</v>
+        <v>15862.8</v>
       </c>
       <c r="M2" t="n">
-        <v>7780.35</v>
+        <v>7631.7</v>
       </c>
       <c r="N2" t="n">
-        <v>12137.475</v>
+        <v>11645.65</v>
       </c>
       <c r="O2" t="n">
-        <v>2.148463758057157</v>
+        <v>2.078540823145564</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.4192299397869128</v>
+        <v>-0.4452572388135643</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.3227756848798042</v>
+        <v>-0.3473081887880206</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.09645425490710857</v>
+        <v>-0.09794905002554372</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.07110456988531622</v>
+        <v>-0.09644012782106692</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.06109652670874066</v>
+        <v>-0.07108937529969372</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
@@ -771,16 +771,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1467</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>南緯</t>
+          <t>宜新實業</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -789,53 +789,53 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>8.210000038146973</v>
+        <v>17.45000076293945</v>
       </c>
       <c r="G3" t="n">
-        <v>8.103499960899352</v>
+        <v>17.525</v>
       </c>
       <c r="H3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>46.21977898022163</v>
+        <v>46.1666214027115</v>
       </c>
       <c r="J3" t="n">
-        <v>45.36872431806854</v>
+        <v>41.41787019405794</v>
       </c>
       <c r="K3" t="n">
-        <v>49.65275989398086</v>
+        <v>47.93289334437646</v>
       </c>
       <c r="L3" t="n">
-        <v>672300.2</v>
+        <v>68724.8</v>
       </c>
       <c r="M3" t="n">
-        <v>266832.85</v>
+        <v>38750.6</v>
       </c>
       <c r="N3" t="n">
-        <v>265943.575</v>
+        <v>43421.625</v>
       </c>
       <c r="O3" t="n">
-        <v>2.519555594447985</v>
+        <v>1.773515764917188</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.0714324942909812</v>
+        <v>-0.04860462444314351</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1160784624651062</v>
+        <v>-0.03170226014254562</v>
       </c>
       <c r="R3" t="n">
-        <v>0.044645968174125</v>
+        <v>-0.01690236430059789</v>
       </c>
       <c r="S3" t="n">
-        <v>0.04345950770641824</v>
+        <v>-0.02335932866533692</v>
       </c>
       <c r="T3" t="n">
-        <v>0.06116435381077001</v>
+        <v>-0.03130777186336196</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -869,44 +869,44 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>-15.652</v>
+        <v>-16</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="AE3" t="n">
-        <v>-15.652</v>
+        <v>-27</v>
       </c>
       <c r="AF3" t="n">
-        <v>-148.965</v>
+        <v>-79.40000000000001</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>-23.004</v>
+        <v>-32</v>
       </c>
       <c r="AI3" t="n">
-        <v>-171.969</v>
+        <v>-111.4</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-31.965</v>
+        <v>-89.40000000000001</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>-47.004</v>
+        <v>-103.188</v>
       </c>
       <c r="AM3" t="n">
-        <v>-78.96900000000001</v>
+        <v>-192.588</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
@@ -917,16 +917,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>6597</t>
+          <t>2063</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>立誠</t>
+          <t>世鎧精密</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,53 +935,53 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>64.80000305175781</v>
+        <v>23.54999923706055</v>
       </c>
       <c r="G4" t="n">
-        <v>68.85499992370606</v>
+        <v>23.71999979019165</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>36.62761944501383</v>
+        <v>35.09940185807341</v>
       </c>
       <c r="J4" t="n">
-        <v>34.3615337404397</v>
+        <v>34.72492818856328</v>
       </c>
       <c r="K4" t="n">
-        <v>37.39825283008025</v>
+        <v>43.93247799794383</v>
       </c>
       <c r="L4" t="n">
-        <v>15800</v>
+        <v>45419.8</v>
       </c>
       <c r="M4" t="n">
-        <v>7800</v>
+        <v>28277.1</v>
       </c>
       <c r="N4" t="n">
-        <v>8125.275</v>
+        <v>30038.8</v>
       </c>
       <c r="O4" t="n">
-        <v>2.025641025641026</v>
+        <v>1.606239678043364</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.642209324374349</v>
+        <v>-0.1206401315278889</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9686523359452234</v>
+        <v>-0.1167031529012742</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.6735569884291256</v>
+        <v>-0.003936978626614657</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7872966475756538</v>
+        <v>-0.005591438464839948</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9014579474895981</v>
+        <v>-0.00608022223339108</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
@@ -1063,67 +1063,67 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>8024</t>
+          <t>3150</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>佑華</t>
+          <t>鈺寶-創</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>12.19999980926514</v>
+        <v>15.60000038146973</v>
       </c>
       <c r="G5" t="n">
-        <v>12.6875</v>
+        <v>15.42000002861023</v>
       </c>
       <c r="H5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>47.06377518895079</v>
+        <v>47.32557756523483</v>
       </c>
       <c r="J5" t="n">
-        <v>46.87078826154868</v>
+        <v>43.85800626952652</v>
       </c>
       <c r="K5" t="n">
-        <v>37.89133783381681</v>
+        <v>47.77025384672108</v>
       </c>
       <c r="L5" t="n">
-        <v>117814</v>
+        <v>60860.2</v>
       </c>
       <c r="M5" t="n">
-        <v>64368.65</v>
+        <v>39717.6</v>
       </c>
       <c r="N5" t="n">
-        <v>51158.75</v>
+        <v>33558.825</v>
       </c>
       <c r="O5" t="n">
-        <v>1.830300930654907</v>
+        <v>1.532323201804741</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2768509042429379</v>
+        <v>-0.2910770792122097</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2783648399447723</v>
+        <v>-0.3452543816320634</v>
       </c>
       <c r="R5" t="n">
-        <v>0.001513935701834446</v>
+        <v>0.05417730241985369</v>
       </c>
       <c r="S5" t="n">
-        <v>0.01179401429109145</v>
+        <v>0.02654508077698242</v>
       </c>
       <c r="T5" t="n">
-        <v>0.01089983533981403</v>
+        <v>0.04145790283459583</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1161,44 +1161,44 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>19.15</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>13.15</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>-41</v>
       </c>
       <c r="AK5" t="n">
         <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>-26.68</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>-67.68000000000001</v>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
@@ -1213,63 +1213,63 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>8087</t>
+          <t>1467</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>麗升能源</t>
+          <t>南緯</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>23.5</v>
+        <v>8.199999809265137</v>
       </c>
       <c r="G6" t="n">
-        <v>24.3</v>
+        <v>8.102999949455262</v>
       </c>
       <c r="H6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>38.53136023137093</v>
+        <v>46.9944199529879</v>
       </c>
       <c r="J6" t="n">
-        <v>35.23258283659647</v>
+        <v>45.91062282020604</v>
       </c>
       <c r="K6" t="n">
-        <v>40.65829851522468</v>
+        <v>49.41128834036997</v>
       </c>
       <c r="L6" t="n">
-        <v>56400</v>
+        <v>630876.2</v>
       </c>
       <c r="M6" t="n">
-        <v>32419.95</v>
+        <v>269157.85</v>
       </c>
       <c r="N6" t="n">
-        <v>27396.375</v>
+        <v>255017.325</v>
       </c>
       <c r="O6" t="n">
-        <v>1.739669555320104</v>
+        <v>2.343889282813041</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.8396146318387494</v>
+        <v>-0.06174186606003396</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.8958913580029801</v>
+        <v>-0.1052111431840918</v>
       </c>
       <c r="R6" t="n">
-        <v>0.05627672616423074</v>
+        <v>0.04346927712405781</v>
       </c>
       <c r="S6" t="n">
-        <v>0.03776360457502648</v>
+        <v>0.044645968174125</v>
       </c>
       <c r="T6" t="n">
-        <v>0.04884951655096081</v>
+        <v>0.04345950770641824</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>-15.652</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1316,35 +1316,35 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>-15.652</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>-148.965</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>-23.004</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>-171.969</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>-31.965</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>-47.004</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>-78.96900000000001</v>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
@@ -1359,63 +1359,63 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4440</t>
+          <t>5487</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>宜新實業</t>
+          <t>通泰</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>17.45000076293945</v>
+        <v>28.95000076293945</v>
       </c>
       <c r="G7" t="n">
-        <v>17.53249998092651</v>
+        <v>29.21499996185303</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>40.67842568070256</v>
+        <v>43.54481448608249</v>
       </c>
       <c r="J7" t="n">
-        <v>39.04349456937123</v>
+        <v>39.93778854176217</v>
       </c>
       <c r="K7" t="n">
-        <v>47.93289334437646</v>
+        <v>48.40887882245898</v>
       </c>
       <c r="L7" t="n">
-        <v>63922.8</v>
+        <v>134206</v>
       </c>
       <c r="M7" t="n">
-        <v>36750.1</v>
+        <v>66698.39999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>46296.375</v>
+        <v>69234.675</v>
       </c>
       <c r="O7" t="n">
-        <v>1.739391185330108</v>
+        <v>2.012132225060871</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.05083599773273306</v>
+        <v>-0.0163413444752365</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.02747666906739614</v>
+        <v>-0.01466877985360663</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.02335932866533692</v>
+        <v>-0.001672564621629865</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.03130777186336196</v>
+        <v>0.01433844886162413</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0003285377835912703</v>
+        <v>-0.05274496540053971</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -1453,44 +1453,44 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-27</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>-79.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>-32</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>-111.4</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-89.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>-103.188</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>-192.588</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
@@ -1505,63 +1505,63 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>6754</t>
+          <t>8024</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>匯僑設計</t>
+          <t>佑華</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>40.5</v>
+        <v>12.35000038146973</v>
       </c>
       <c r="G8" t="n">
-        <v>41.67249984741211</v>
+        <v>12.65250000953674</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>45.2449954169259</v>
+        <v>48.04251679472656</v>
       </c>
       <c r="J8" t="n">
-        <v>43.93988660805142</v>
+        <v>47.26136447830024</v>
       </c>
       <c r="K8" t="n">
-        <v>39.45780370741554</v>
+        <v>43.17774093944967</v>
       </c>
       <c r="L8" t="n">
-        <v>26536</v>
+        <v>129604</v>
       </c>
       <c r="M8" t="n">
-        <v>16591.85</v>
+        <v>66568.55</v>
       </c>
       <c r="N8" t="n">
-        <v>12423.175</v>
+        <v>51908.75</v>
       </c>
       <c r="O8" t="n">
-        <v>1.599339434722469</v>
+        <v>1.946925387438963</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.2485722456074626</v>
+        <v>-0.2686228263816339</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.1663007978245593</v>
+        <v>-0.2753306277103014</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.08227144778290335</v>
+        <v>0.00670780132866744</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.03461097737999042</v>
+        <v>0.001090116923094686</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.08082910242531693</v>
+        <v>0.01133817005663024</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1608,10 +1608,10 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>-42</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -1620,23 +1620,23 @@
         <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>-42</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>-42.758</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
         <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>-40.758</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
@@ -1665,49 +1665,49 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>35.5</v>
+        <v>35.70000076293945</v>
       </c>
       <c r="G9" t="n">
-        <v>35.82000007629394</v>
+        <v>35.78000011444092</v>
       </c>
       <c r="H9" t="b">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>44.64115080930264</v>
+        <v>49.76080111627473</v>
       </c>
       <c r="J9" t="n">
-        <v>42.18351620868729</v>
+        <v>44.70927787542806</v>
       </c>
       <c r="K9" t="n">
-        <v>37.72235392323162</v>
+        <v>41.97322542461996</v>
       </c>
       <c r="L9" t="n">
-        <v>26400</v>
+        <v>25200</v>
       </c>
       <c r="M9" t="n">
-        <v>16779.45</v>
+        <v>16679.45</v>
       </c>
       <c r="N9" t="n">
-        <v>17455.25</v>
+        <v>17430.25</v>
       </c>
       <c r="O9" t="n">
-        <v>1.573353119440744</v>
+        <v>1.51084118481125</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.402191933564751</v>
+        <v>-0.3721585607778124</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.4852487657628003</v>
+        <v>-0.4628116931345025</v>
       </c>
       <c r="R9" t="n">
-        <v>0.08305683219804927</v>
+        <v>0.09065313235669009</v>
       </c>
       <c r="S9" t="n">
-        <v>0.09151732938325263</v>
+        <v>0.08312746870607834</v>
       </c>
       <c r="T9" t="n">
-        <v>0.08435796610012714</v>
+        <v>0.09159330347063122</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -1782,7 +1782,153 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>70</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1799</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>易威</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>28.60000038146973</v>
+      </c>
+      <c r="G10" t="n">
+        <v>28.85250005722046</v>
+      </c>
+      <c r="H10" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>33.98032071255129</v>
+      </c>
+      <c r="J10" t="n">
+        <v>32.3531571558309</v>
+      </c>
+      <c r="K10" t="n">
+        <v>43.2139443256531</v>
+      </c>
+      <c r="L10" t="n">
+        <v>161528.2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>107026.15</v>
+      </c>
+      <c r="N10" t="n">
+        <v>115348.075</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.509240498700551</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-0.4745516666771366</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-0.5014128391373867</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.0268611724602501</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.0009488472937357884</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.02800945476863892</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN10"/>
+  <dimension ref="A1:AN9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -652,13 +652,13 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>41.53399199887997</v>
+        <v>41.53399199027459</v>
       </c>
       <c r="J2" t="n">
-        <v>38.1577976025347</v>
+        <v>38.15779744362221</v>
       </c>
       <c r="K2" t="n">
-        <v>38.23175545645226</v>
+        <v>38.16191986781902</v>
       </c>
       <c r="L2" t="n">
         <v>15862.8</v>
@@ -673,19 +673,19 @@
         <v>2.078540823145564</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.4452572388135643</v>
+        <v>-0.4452883531293619</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.3473081887880206</v>
+        <v>-0.3473534301898581</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.09794905002554372</v>
+        <v>-0.09793492293950379</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.09644012782106692</v>
+        <v>-0.09642493323544665</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.07108937529969372</v>
+        <v>-0.0710730389589283</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -798,13 +798,13 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>46.1666214027115</v>
+        <v>46.1666214082308</v>
       </c>
       <c r="J3" t="n">
-        <v>41.41787019405794</v>
+        <v>41.41787029583858</v>
       </c>
       <c r="K3" t="n">
-        <v>47.93289334437646</v>
+        <v>48.17238165734962</v>
       </c>
       <c r="L3" t="n">
         <v>68724.8</v>
@@ -819,19 +819,19 @@
         <v>1.773515764917188</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.04860462444314351</v>
+        <v>-0.0418564750316115</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.03170226014254562</v>
+        <v>-0.02183258298308014</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.01690236430059789</v>
+        <v>-0.02002389204853135</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.02335932866533692</v>
+        <v>-0.0267239732610325</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.03130777186336196</v>
+        <v>-0.03493380165047685</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -869,40 +869,40 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>-16</v>
+        <v>-5.635</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>-11</v>
+        <v>-2</v>
       </c>
       <c r="AE3" t="n">
-        <v>-27</v>
+        <v>-7.635</v>
       </c>
       <c r="AF3" t="n">
-        <v>-79.40000000000001</v>
+        <v>-65.63499999999999</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>-32</v>
+        <v>-30</v>
       </c>
       <c r="AI3" t="n">
-        <v>-111.4</v>
+        <v>-95.63499999999999</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-89.40000000000001</v>
+        <v>-98.035</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>-103.188</v>
+        <v>-100.188</v>
       </c>
       <c r="AM3" t="n">
-        <v>-192.588</v>
+        <v>-198.223</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
@@ -944,13 +944,13 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>35.09940185807341</v>
+        <v>35.09940185561469</v>
       </c>
       <c r="J4" t="n">
-        <v>34.72492818856328</v>
+        <v>34.72492814291309</v>
       </c>
       <c r="K4" t="n">
-        <v>43.93247799794383</v>
+        <v>43.54827054748496</v>
       </c>
       <c r="L4" t="n">
         <v>45419.8</v>
@@ -965,19 +965,19 @@
         <v>1.606239678043364</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.1206401315278889</v>
+        <v>-0.1201250329017398</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.1167031529012742</v>
+        <v>-0.1159505792457936</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.003936978626614657</v>
+        <v>-0.004174453655946209</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.005591438464839948</v>
+        <v>-0.005847310659976901</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.00608022223339108</v>
+        <v>-0.006355856121840059</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1090,13 +1090,13 @@
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>47.32557756523483</v>
+        <v>47.32557757001707</v>
       </c>
       <c r="J5" t="n">
-        <v>43.85800626952652</v>
+        <v>43.85800635791131</v>
       </c>
       <c r="K5" t="n">
-        <v>47.77025384672108</v>
+        <v>46.24215149631041</v>
       </c>
       <c r="L5" t="n">
         <v>60860.2</v>
@@ -1111,19 +1111,19 @@
         <v>1.532323201804741</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2910770792122097</v>
+        <v>-0.2893589194991044</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.3452543816320634</v>
+        <v>-0.342741709174782</v>
       </c>
       <c r="R5" t="n">
-        <v>0.05417730241985369</v>
+        <v>0.05338278967567756</v>
       </c>
       <c r="S5" t="n">
-        <v>0.02654508077698242</v>
+        <v>0.02568872103146796</v>
       </c>
       <c r="T5" t="n">
-        <v>0.04145790283459583</v>
+        <v>0.04053505472448371</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1161,40 +1161,40 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>-8</v>
+        <v>-8.763</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>-2</v>
+        <v>2.598</v>
       </c>
       <c r="AE5" t="n">
-        <v>-10</v>
+        <v>-6.165</v>
       </c>
       <c r="AF5" t="n">
-        <v>-6</v>
+        <v>-9.762999999999998</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>19.15</v>
+        <v>17.763</v>
       </c>
       <c r="AI5" t="n">
-        <v>13.15</v>
+        <v>8.000000000000002</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-41</v>
+        <v>-50.763</v>
       </c>
       <c r="AK5" t="n">
         <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>-26.68</v>
+        <v>-24.082</v>
       </c>
       <c r="AM5" t="n">
-        <v>-67.68000000000001</v>
+        <v>-74.84500000000001</v>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
@@ -1213,63 +1213,63 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1467</t>
+          <t>5487</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>南緯</t>
+          <t>通泰</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>8.199999809265137</v>
+        <v>28.95000076293945</v>
       </c>
       <c r="G6" t="n">
-        <v>8.102999949455262</v>
+        <v>29.21499996185303</v>
       </c>
       <c r="H6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>46.9944199529879</v>
+        <v>43.54481449089267</v>
       </c>
       <c r="J6" t="n">
-        <v>45.91062282020604</v>
+        <v>39.93778863062546</v>
       </c>
       <c r="K6" t="n">
-        <v>49.41128834036997</v>
+        <v>47.1456801506443</v>
       </c>
       <c r="L6" t="n">
-        <v>630876.2</v>
+        <v>134206</v>
       </c>
       <c r="M6" t="n">
-        <v>269157.85</v>
+        <v>66698.39999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>255017.325</v>
+        <v>69234.675</v>
       </c>
       <c r="O6" t="n">
-        <v>2.343889282813041</v>
+        <v>2.012132225060871</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.06174186606003396</v>
+        <v>-0.01712263735537789</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.1052111431840918</v>
+        <v>-0.01581201085181758</v>
       </c>
       <c r="R6" t="n">
-        <v>0.04346927712405781</v>
+        <v>-0.001310626503560307</v>
       </c>
       <c r="S6" t="n">
-        <v>0.044645968174125</v>
+        <v>0.01472864169068619</v>
       </c>
       <c r="T6" t="n">
-        <v>0.04345950770641824</v>
+        <v>-0.05232438282060107</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>-15.652</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1316,31 +1316,31 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-15.652</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>-148.965</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>-23.004</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>-171.969</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-31.965</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>-47.004</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>-78.96900000000001</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
@@ -1359,12 +1359,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>5487</t>
+          <t>8024</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>通泰</t>
+          <t>佑華</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1373,49 +1373,49 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>28.95000076293945</v>
+        <v>12.35000038146973</v>
       </c>
       <c r="G7" t="n">
-        <v>29.21499996185303</v>
+        <v>12.65250000953674</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>43.54481448608249</v>
+        <v>48.04251679780837</v>
       </c>
       <c r="J7" t="n">
-        <v>39.93778854176217</v>
+        <v>47.26136453472114</v>
       </c>
       <c r="K7" t="n">
-        <v>48.40887882245898</v>
+        <v>35.09694945731663</v>
       </c>
       <c r="L7" t="n">
-        <v>134206</v>
+        <v>129604</v>
       </c>
       <c r="M7" t="n">
-        <v>66698.39999999999</v>
+        <v>66568.55</v>
       </c>
       <c r="N7" t="n">
-        <v>69234.675</v>
+        <v>51908.75</v>
       </c>
       <c r="O7" t="n">
-        <v>2.012132225060871</v>
+        <v>1.946925387438963</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.0163413444752365</v>
+        <v>-0.28076393682068</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.01466877985360663</v>
+        <v>-0.2930958858942394</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.001672564621629865</v>
+        <v>0.01233194907355939</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01433844886162413</v>
+        <v>0.007153278611985336</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.05274496540053971</v>
+        <v>0.01787351294394224</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>8024</t>
+          <t>7753</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>佑華</t>
+          <t>星亞</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1519,49 +1519,49 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>12.35000038146973</v>
+        <v>35.70000076293945</v>
       </c>
       <c r="G8" t="n">
-        <v>12.65250000953674</v>
+        <v>35.78000011444092</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>48.04251679472656</v>
+        <v>49.76080112066801</v>
       </c>
       <c r="J8" t="n">
-        <v>47.26136447830024</v>
+        <v>44.70927795666579</v>
       </c>
       <c r="K8" t="n">
-        <v>43.17774093944967</v>
+        <v>40.45896918018003</v>
       </c>
       <c r="L8" t="n">
-        <v>129604</v>
+        <v>25200</v>
       </c>
       <c r="M8" t="n">
-        <v>66568.55</v>
+        <v>16679.45</v>
       </c>
       <c r="N8" t="n">
-        <v>51908.75</v>
+        <v>17430.25</v>
       </c>
       <c r="O8" t="n">
-        <v>1.946925387438963</v>
+        <v>1.51084118481125</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.2686228263816339</v>
+        <v>-0.3697835827235352</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.2753306277103014</v>
+        <v>-0.4593367805433597</v>
       </c>
       <c r="R8" t="n">
-        <v>0.00670780132866744</v>
+        <v>0.08955319781982457</v>
       </c>
       <c r="S8" t="n">
-        <v>0.001090116923094686</v>
+        <v>0.08194170307556042</v>
       </c>
       <c r="T8" t="n">
-        <v>0.01133817005663024</v>
+        <v>0.09031522741196718</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -1651,12 +1651,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>7753</t>
+          <t>1799</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>星亞</t>
+          <t>易威</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1665,49 +1665,49 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>35.70000076293945</v>
+        <v>28.60000038146973</v>
       </c>
       <c r="G9" t="n">
-        <v>35.78000011444092</v>
+        <v>28.85250005722046</v>
       </c>
       <c r="H9" t="b">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>49.76080111627473</v>
+        <v>33.98032071379907</v>
       </c>
       <c r="J9" t="n">
-        <v>44.70927787542806</v>
+        <v>32.35315717916581</v>
       </c>
       <c r="K9" t="n">
-        <v>41.97322542461996</v>
+        <v>42.92676994368112</v>
       </c>
       <c r="L9" t="n">
-        <v>25200</v>
+        <v>161528.2</v>
       </c>
       <c r="M9" t="n">
-        <v>16679.45</v>
+        <v>107026.15</v>
       </c>
       <c r="N9" t="n">
-        <v>17430.25</v>
+        <v>115348.075</v>
       </c>
       <c r="O9" t="n">
-        <v>1.51084118481125</v>
+        <v>1.509240498700551</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.3721585607778124</v>
+        <v>-0.476145366753201</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.4628116931345025</v>
+        <v>-0.5037445425356341</v>
       </c>
       <c r="R9" t="n">
-        <v>0.09065313235669009</v>
+        <v>0.02759917578243309</v>
       </c>
       <c r="S9" t="n">
-        <v>0.08312746870607834</v>
+        <v>0.001744427537495818</v>
       </c>
       <c r="T9" t="n">
-        <v>0.09159330347063122</v>
+        <v>0.02886695626930658</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -1781,152 +1781,6 @@
         <v>0</v>
       </c>
       <c r="AN9" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>70</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1799</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>易威</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>28.60000038146973</v>
-      </c>
-      <c r="G10" t="n">
-        <v>28.85250005722046</v>
-      </c>
-      <c r="H10" t="b">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>33.98032071255129</v>
-      </c>
-      <c r="J10" t="n">
-        <v>32.3531571558309</v>
-      </c>
-      <c r="K10" t="n">
-        <v>43.2139443256531</v>
-      </c>
-      <c r="L10" t="n">
-        <v>161528.2</v>
-      </c>
-      <c r="M10" t="n">
-        <v>107026.15</v>
-      </c>
-      <c r="N10" t="n">
-        <v>115348.075</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.509240498700551</v>
-      </c>
-      <c r="P10" t="n">
-        <v>-0.4745516666771366</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>-0.5014128391373867</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.0268611724602501</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.0009488472937357884</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0.02800945476863892</v>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN10" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -869,40 +869,40 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>-5.635</v>
+        <v>9</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>-2</v>
+        <v>-6</v>
       </c>
       <c r="AE3" t="n">
-        <v>-7.635</v>
+        <v>3</v>
       </c>
       <c r="AF3" t="n">
-        <v>-65.63499999999999</v>
+        <v>-72.63500000000001</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>-30</v>
+        <v>-29</v>
       </c>
       <c r="AI3" t="n">
-        <v>-95.63499999999999</v>
+        <v>-101.635</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-98.035</v>
+        <v>-87.035</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>-100.188</v>
+        <v>-103.188</v>
       </c>
       <c r="AM3" t="n">
-        <v>-198.223</v>
+        <v>-190.223</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
@@ -1063,67 +1063,67 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3150</t>
+          <t>5487</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>鈺寶-創</t>
+          <t>通泰</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>15.60000038146973</v>
+        <v>28.95000076293945</v>
       </c>
       <c r="G5" t="n">
-        <v>15.42000002861023</v>
+        <v>29.21499996185303</v>
       </c>
       <c r="H5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>47.32557757001707</v>
+        <v>43.54481449089267</v>
       </c>
       <c r="J5" t="n">
-        <v>43.85800635791131</v>
+        <v>39.93778863062546</v>
       </c>
       <c r="K5" t="n">
-        <v>46.24215149631041</v>
+        <v>47.1456801506443</v>
       </c>
       <c r="L5" t="n">
-        <v>60860.2</v>
+        <v>134206</v>
       </c>
       <c r="M5" t="n">
-        <v>39717.6</v>
+        <v>66698.39999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>33558.825</v>
+        <v>69234.675</v>
       </c>
       <c r="O5" t="n">
-        <v>1.532323201804741</v>
+        <v>2.012132225060871</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2893589194991044</v>
+        <v>-0.01712263735537789</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.342741709174782</v>
+        <v>-0.01581201085181758</v>
       </c>
       <c r="R5" t="n">
-        <v>0.05338278967567756</v>
+        <v>-0.001310626503560307</v>
       </c>
       <c r="S5" t="n">
-        <v>0.02568872103146796</v>
+        <v>0.01472864169068619</v>
       </c>
       <c r="T5" t="n">
-        <v>0.04053505472448371</v>
+        <v>-0.05232438282060107</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1161,40 +1161,40 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>-8.763</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.598</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-6.165</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>-9.762999999999998</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>17.763</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>8.000000000000002</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-50.763</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
         <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>-24.082</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>-74.84500000000001</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
@@ -1213,12 +1213,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5487</t>
+          <t>8024</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>通泰</t>
+          <t>佑華</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1227,49 +1227,49 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>28.95000076293945</v>
+        <v>12.35000038146973</v>
       </c>
       <c r="G6" t="n">
-        <v>29.21499996185303</v>
+        <v>12.65250000953674</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>43.54481449089267</v>
+        <v>48.04251679780837</v>
       </c>
       <c r="J6" t="n">
-        <v>39.93778863062546</v>
+        <v>47.26136453472114</v>
       </c>
       <c r="K6" t="n">
-        <v>47.1456801506443</v>
+        <v>35.09694945731663</v>
       </c>
       <c r="L6" t="n">
-        <v>134206</v>
+        <v>129604</v>
       </c>
       <c r="M6" t="n">
-        <v>66698.39999999999</v>
+        <v>66568.55</v>
       </c>
       <c r="N6" t="n">
-        <v>69234.675</v>
+        <v>51908.75</v>
       </c>
       <c r="O6" t="n">
-        <v>2.012132225060871</v>
+        <v>1.946925387438963</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.01712263735537789</v>
+        <v>-0.28076393682068</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.01581201085181758</v>
+        <v>-0.2930958858942394</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.001310626503560307</v>
+        <v>0.01233194907355939</v>
       </c>
       <c r="S6" t="n">
-        <v>0.01472864169068619</v>
+        <v>0.007153278611985336</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.05232438282060107</v>
+        <v>0.01787351294394224</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1359,63 +1359,63 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>8024</t>
+          <t>3150</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>佑華</t>
+          <t>鈺寶-創</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>12.35000038146973</v>
+        <v>15.60000038146973</v>
       </c>
       <c r="G7" t="n">
-        <v>12.65250000953674</v>
+        <v>15.42000002861023</v>
       </c>
       <c r="H7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>48.04251679780837</v>
+        <v>47.32557757001707</v>
       </c>
       <c r="J7" t="n">
-        <v>47.26136453472114</v>
+        <v>43.85800635791131</v>
       </c>
       <c r="K7" t="n">
-        <v>35.09694945731663</v>
+        <v>46.24215149631041</v>
       </c>
       <c r="L7" t="n">
-        <v>129604</v>
+        <v>60860.2</v>
       </c>
       <c r="M7" t="n">
-        <v>66568.55</v>
+        <v>39717.6</v>
       </c>
       <c r="N7" t="n">
-        <v>51908.75</v>
+        <v>33558.825</v>
       </c>
       <c r="O7" t="n">
-        <v>1.946925387438963</v>
+        <v>1.532323201804741</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.28076393682068</v>
+        <v>-0.2893589194991044</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.2930958858942394</v>
+        <v>-0.342741709174782</v>
       </c>
       <c r="R7" t="n">
-        <v>0.01233194907355939</v>
+        <v>0.05338278967567756</v>
       </c>
       <c r="S7" t="n">
-        <v>0.007153278611985336</v>
+        <v>0.02568872103146796</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01787351294394224</v>
+        <v>0.04053505472448371</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -1453,40 +1453,40 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>-3.687</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>-0.6869999999999998</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>-28.45</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>15.518</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-12.932</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>-56.45</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>-16.084</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>-72.53400000000001</v>
       </c>
       <c r="AN7" t="inlineStr">
         <is>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN9"/>
+  <dimension ref="A1:AN5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,67 +625,67 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8101</t>
+          <t>2756</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>華冠</t>
+          <t>聯發國際</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>10.30000019073486</v>
+        <v>61.5</v>
       </c>
       <c r="G2" t="n">
-        <v>11.35000004768372</v>
+        <v>62.04500007629395</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>41.53399199027459</v>
+        <v>45.54362253699551</v>
       </c>
       <c r="J2" t="n">
-        <v>38.15779744362221</v>
+        <v>41.91949164270919</v>
       </c>
       <c r="K2" t="n">
-        <v>38.16191986781902</v>
+        <v>48.68184674458032</v>
       </c>
       <c r="L2" t="n">
-        <v>15862.8</v>
+        <v>68319.8</v>
       </c>
       <c r="M2" t="n">
-        <v>7631.7</v>
+        <v>33150.05</v>
       </c>
       <c r="N2" t="n">
-        <v>11645.65</v>
+        <v>31354.425</v>
       </c>
       <c r="O2" t="n">
-        <v>2.078540823145564</v>
+        <v>2.060926001619907</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.4452883531293619</v>
+        <v>-0.2215178753980922</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.3473534301898581</v>
+        <v>0.05213562770951449</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.09793492293950379</v>
+        <v>-0.2736535031076067</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.09642493323544665</v>
+        <v>-0.3561811857585787</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0710730389589283</v>
+        <v>-0.3070868203208129</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -729,10 +729,10 @@
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.225</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.225</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -741,10 +741,10 @@
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.225</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.225</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
@@ -753,14 +753,14 @@
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.225</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.225</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -771,91 +771,91 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4440</t>
+          <t>8092</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>宜新實業</t>
+          <t>建暐</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>17.45000076293945</v>
+        <v>12.64999961853027</v>
       </c>
       <c r="G3" t="n">
-        <v>17.525</v>
+        <v>12.60499997138977</v>
       </c>
       <c r="H3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>46.1666214082308</v>
+        <v>47.12525949901908</v>
       </c>
       <c r="J3" t="n">
-        <v>41.41787029583858</v>
+        <v>35.07564682712468</v>
       </c>
       <c r="K3" t="n">
-        <v>48.17238165734962</v>
+        <v>49.49960195785653</v>
       </c>
       <c r="L3" t="n">
-        <v>68724.8</v>
+        <v>174614.4</v>
       </c>
       <c r="M3" t="n">
-        <v>38750.6</v>
+        <v>90225.10000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>43421.625</v>
+        <v>63218.55</v>
       </c>
       <c r="O3" t="n">
-        <v>1.773515764917188</v>
+        <v>1.935319550768023</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.0418564750316115</v>
+        <v>-0.09569783066831583</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.02183258298308014</v>
+        <v>-0.1321190656571258</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.02002389204853135</v>
+        <v>0.03642123498881</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0267239732610325</v>
+        <v>0.02990112308745296</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.03493380165047685</v>
+        <v>0.01396100392130287</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -869,44 +869,44 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-72.63500000000001</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>-29</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>-101.635</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-87.035</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>-103.188</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>-190.223</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -917,16 +917,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2063</t>
+          <t>3629</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>世鎧精密</t>
+          <t>地心引力</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,73 +935,73 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>23.54999923706055</v>
+        <v>14.39999961853027</v>
       </c>
       <c r="G4" t="n">
-        <v>23.71999979019165</v>
+        <v>16.60750021934509</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>35.09940185561469</v>
+        <v>45.93221909434828</v>
       </c>
       <c r="J4" t="n">
-        <v>34.72492814291309</v>
+        <v>37.98464344410975</v>
       </c>
       <c r="K4" t="n">
-        <v>43.54827054748496</v>
+        <v>41.06303871840601</v>
       </c>
       <c r="L4" t="n">
-        <v>45419.8</v>
+        <v>8600</v>
       </c>
       <c r="M4" t="n">
-        <v>28277.1</v>
+        <v>4737.45</v>
       </c>
       <c r="N4" t="n">
-        <v>30038.8</v>
+        <v>6077</v>
       </c>
       <c r="O4" t="n">
-        <v>1.606239678043364</v>
+        <v>1.815322589156614</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.1201250329017398</v>
+        <v>-0.761897729225705</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.1159505792457936</v>
+        <v>-0.5005199616121038</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.004174453655946209</v>
+        <v>-0.2613777676136012</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.005847310659976901</v>
+        <v>-0.2694023288470383</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.006355856121840059</v>
+        <v>-0.3297071310246915</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5487</t>
+          <t>4432</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>通泰</t>
+          <t>銘旺實</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1081,49 +1081,49 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>28.95000076293945</v>
+        <v>15.35000038146973</v>
       </c>
       <c r="G5" t="n">
-        <v>29.21499996185303</v>
+        <v>15.44250001907349</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>43.54481449089267</v>
+        <v>49.7729043784336</v>
       </c>
       <c r="J5" t="n">
-        <v>39.93778863062546</v>
+        <v>42.92226917241841</v>
       </c>
       <c r="K5" t="n">
-        <v>47.1456801506443</v>
+        <v>45.05086928519868</v>
       </c>
       <c r="L5" t="n">
-        <v>134206</v>
+        <v>51447</v>
       </c>
       <c r="M5" t="n">
-        <v>66698.39999999999</v>
+        <v>30917.8</v>
       </c>
       <c r="N5" t="n">
-        <v>69234.675</v>
+        <v>26853.325</v>
       </c>
       <c r="O5" t="n">
-        <v>2.012132225060871</v>
+        <v>1.66399291023294</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.01712263735537789</v>
+        <v>-0.1164897913473286</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.01581201085181758</v>
+        <v>-0.1203831247455769</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.001310626503560307</v>
+        <v>0.003893333398248294</v>
       </c>
       <c r="S5" t="n">
-        <v>0.01472864169068619</v>
+        <v>-0.003909087140682582</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.05232438282060107</v>
+        <v>-0.01935619918626388</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1198,591 +1198,7 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>70</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>8024</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>佑華</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>12.35000038146973</v>
-      </c>
-      <c r="G6" t="n">
-        <v>12.65250000953674</v>
-      </c>
-      <c r="H6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>48.04251679780837</v>
-      </c>
-      <c r="J6" t="n">
-        <v>47.26136453472114</v>
-      </c>
-      <c r="K6" t="n">
-        <v>35.09694945731663</v>
-      </c>
-      <c r="L6" t="n">
-        <v>129604</v>
-      </c>
-      <c r="M6" t="n">
-        <v>66568.55</v>
-      </c>
-      <c r="N6" t="n">
-        <v>51908.75</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.946925387438963</v>
-      </c>
-      <c r="P6" t="n">
-        <v>-0.28076393682068</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>-0.2930958858942394</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.01233194907355939</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.007153278611985336</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0.01787351294394224</v>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>70</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>3150</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>鈺寶-創</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>15.60000038146973</v>
-      </c>
-      <c r="G7" t="n">
-        <v>15.42000002861023</v>
-      </c>
-      <c r="H7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7" t="n">
-        <v>47.32557757001707</v>
-      </c>
-      <c r="J7" t="n">
-        <v>43.85800635791131</v>
-      </c>
-      <c r="K7" t="n">
-        <v>46.24215149631041</v>
-      </c>
-      <c r="L7" t="n">
-        <v>60860.2</v>
-      </c>
-      <c r="M7" t="n">
-        <v>39717.6</v>
-      </c>
-      <c r="N7" t="n">
-        <v>33558.825</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.532323201804741</v>
-      </c>
-      <c r="P7" t="n">
-        <v>-0.2893589194991044</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>-0.342741709174782</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.05338278967567756</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.02568872103146796</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.04053505472448371</v>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB7" t="n">
-        <v>-3.687</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>-0.6869999999999998</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>-28.45</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>15.518</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>-12.932</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>-56.45</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>-16.084</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>-72.53400000000001</v>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>70</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>7753</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>星亞</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>35.70000076293945</v>
-      </c>
-      <c r="G8" t="n">
-        <v>35.78000011444092</v>
-      </c>
-      <c r="H8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>49.76080112066801</v>
-      </c>
-      <c r="J8" t="n">
-        <v>44.70927795666579</v>
-      </c>
-      <c r="K8" t="n">
-        <v>40.45896918018003</v>
-      </c>
-      <c r="L8" t="n">
-        <v>25200</v>
-      </c>
-      <c r="M8" t="n">
-        <v>16679.45</v>
-      </c>
-      <c r="N8" t="n">
-        <v>17430.25</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.51084118481125</v>
-      </c>
-      <c r="P8" t="n">
-        <v>-0.3697835827235352</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>-0.4593367805433597</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.08955319781982457</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.08194170307556042</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0.09031522741196718</v>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>70</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1799</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>易威</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>28.60000038146973</v>
-      </c>
-      <c r="G9" t="n">
-        <v>28.85250005722046</v>
-      </c>
-      <c r="H9" t="b">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>33.98032071379907</v>
-      </c>
-      <c r="J9" t="n">
-        <v>32.35315717916581</v>
-      </c>
-      <c r="K9" t="n">
-        <v>42.92676994368112</v>
-      </c>
-      <c r="L9" t="n">
-        <v>161528.2</v>
-      </c>
-      <c r="M9" t="n">
-        <v>107026.15</v>
-      </c>
-      <c r="N9" t="n">
-        <v>115348.075</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.509240498700551</v>
-      </c>
-      <c r="P9" t="n">
-        <v>-0.476145366753201</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>-0.5037445425356341</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.02759917578243309</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.001744427537495818</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0.02886695626930658</v>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN5"/>
+  <dimension ref="A1:AN9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,16 +625,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2756</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>聯發國際</t>
+          <t>金穎生技</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -643,53 +643,53 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>61.5</v>
+        <v>29.29999923706055</v>
       </c>
       <c r="G2" t="n">
-        <v>62.04500007629395</v>
+        <v>29.48749980926514</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>45.54362253699551</v>
+        <v>34.21913133510645</v>
       </c>
       <c r="J2" t="n">
-        <v>41.91949164270919</v>
+        <v>33.97894716985556</v>
       </c>
       <c r="K2" t="n">
-        <v>48.68184674458032</v>
+        <v>45.94078050840252</v>
       </c>
       <c r="L2" t="n">
-        <v>68319.8</v>
+        <v>19822.2</v>
       </c>
       <c r="M2" t="n">
-        <v>33150.05</v>
+        <v>13061.05</v>
       </c>
       <c r="N2" t="n">
-        <v>31354.425</v>
+        <v>14956.65</v>
       </c>
       <c r="O2" t="n">
-        <v>2.060926001619907</v>
+        <v>1.517657462455163</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.2215178753980922</v>
+        <v>-0.1594981511994646</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.05213562770951449</v>
+        <v>-0.1460251576936206</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.2736535031076067</v>
+        <v>-0.01347299350584405</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3561811857585787</v>
+        <v>-0.01730334883661422</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3070868203208129</v>
+        <v>-0.01989230789429874</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -775,12 +775,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>8092</t>
+          <t>9949</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>建暐</t>
+          <t>琉園</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -789,49 +789,49 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>12.64999961853027</v>
+        <v>24.20000076293945</v>
       </c>
       <c r="G3" t="n">
-        <v>12.60499997138977</v>
+        <v>24.15249986648559</v>
       </c>
       <c r="H3" t="b">
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>47.12525949901908</v>
+        <v>37.0222422717444</v>
       </c>
       <c r="J3" t="n">
-        <v>35.07564682712468</v>
+        <v>35.51843972477845</v>
       </c>
       <c r="K3" t="n">
-        <v>49.49960195785653</v>
+        <v>49.0701968892679</v>
       </c>
       <c r="L3" t="n">
-        <v>174614.4</v>
+        <v>313221.4</v>
       </c>
       <c r="M3" t="n">
-        <v>90225.10000000001</v>
+        <v>100371.15</v>
       </c>
       <c r="N3" t="n">
-        <v>63218.55</v>
+        <v>68723.925</v>
       </c>
       <c r="O3" t="n">
-        <v>1.935319550768023</v>
+        <v>3.12063177516647</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.09569783066831583</v>
+        <v>0.06025973967355824</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1321190656571258</v>
+        <v>0.04523973808438519</v>
       </c>
       <c r="R3" t="n">
-        <v>0.03642123498881</v>
+        <v>0.01502000158917306</v>
       </c>
       <c r="S3" t="n">
-        <v>0.02990112308745296</v>
+        <v>0.02478584877907909</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01396100392130287</v>
+        <v>-0.01830952087834201</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3629</t>
+          <t>4157</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>地心引力</t>
+          <t>太景*-KY</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,49 +935,49 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>14.39999961853027</v>
+        <v>8.800000190734863</v>
       </c>
       <c r="G4" t="n">
-        <v>16.60750021934509</v>
+        <v>8.847500038146972</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>45.93221909434828</v>
+        <v>45.88195007481825</v>
       </c>
       <c r="J4" t="n">
-        <v>37.98464344410975</v>
+        <v>44.22801811964723</v>
       </c>
       <c r="K4" t="n">
-        <v>41.06303871840601</v>
+        <v>48.91984747275139</v>
       </c>
       <c r="L4" t="n">
-        <v>8600</v>
+        <v>2790616.2</v>
       </c>
       <c r="M4" t="n">
-        <v>4737.45</v>
+        <v>1239215.2</v>
       </c>
       <c r="N4" t="n">
-        <v>6077</v>
+        <v>988984.4</v>
       </c>
       <c r="O4" t="n">
-        <v>1.815322589156614</v>
+        <v>2.251922184298579</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.761897729225705</v>
+        <v>0.01063903643603581</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.5005199616121038</v>
+        <v>-0.002662917596586213</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.2613777676136012</v>
+        <v>0.01330195403262202</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2694023288470383</v>
+        <v>0.02334489605210566</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3297071310246915</v>
+        <v>0.02528440525433917</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4432</t>
+          <t>6180</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>銘旺實</t>
+          <t>橘子</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1081,49 +1081,49 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>15.35000038146973</v>
+        <v>40.25</v>
       </c>
       <c r="G5" t="n">
-        <v>15.44250001907349</v>
+        <v>40.58000030517578</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>49.7729043784336</v>
+        <v>37.95650170428486</v>
       </c>
       <c r="J5" t="n">
-        <v>42.92226917241841</v>
+        <v>33.89417324229827</v>
       </c>
       <c r="K5" t="n">
-        <v>45.05086928519868</v>
+        <v>44.77519895086012</v>
       </c>
       <c r="L5" t="n">
-        <v>51447</v>
+        <v>581405.2</v>
       </c>
       <c r="M5" t="n">
-        <v>30917.8</v>
+        <v>319424.2</v>
       </c>
       <c r="N5" t="n">
-        <v>26853.325</v>
+        <v>312603.35</v>
       </c>
       <c r="O5" t="n">
-        <v>1.66399291023294</v>
+        <v>1.82016641193748</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1164897913473286</v>
+        <v>-0.4184905277985891</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.1203831247455769</v>
+        <v>-0.3565345540607071</v>
       </c>
       <c r="R5" t="n">
-        <v>0.003893333398248294</v>
+        <v>-0.06195597373788198</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.003909087140682582</v>
+        <v>-0.1074515145809138</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.01935619918626388</v>
+        <v>-0.1355446885056974</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1198,7 +1198,591 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>70</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>3629</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>地心引力</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>14.39999961853027</v>
+      </c>
+      <c r="G6" t="n">
+        <v>16.60750021934509</v>
+      </c>
+      <c r="H6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>45.93221909738547</v>
+      </c>
+      <c r="J6" t="n">
+        <v>37.98464350080399</v>
+      </c>
+      <c r="K6" t="n">
+        <v>40.69411263497764</v>
+      </c>
+      <c r="L6" t="n">
+        <v>8600</v>
+      </c>
+      <c r="M6" t="n">
+        <v>4737.45</v>
+      </c>
+      <c r="N6" t="n">
+        <v>6077</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.815322589156614</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-0.761897729225705</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-0.5005199616121038</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-0.2613777676136012</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-0.2694023288470383</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-0.3297071310246915</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
           <t>2026-10-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>70</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>8092</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>建暐</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>12.39999961853027</v>
+      </c>
+      <c r="G7" t="n">
+        <v>12.58999996185303</v>
+      </c>
+      <c r="H7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>42.95529461990483</v>
+      </c>
+      <c r="J7" t="n">
+        <v>37.70219607234667</v>
+      </c>
+      <c r="K7" t="n">
+        <v>44.4684599726675</v>
+      </c>
+      <c r="L7" t="n">
+        <v>161806.4</v>
+      </c>
+      <c r="M7" t="n">
+        <v>91420.10000000001</v>
+      </c>
+      <c r="N7" t="n">
+        <v>63717.55</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.769921494288455</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-0.1026699552085706</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-0.1266865359666954</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.02401658075812479</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.03660220404784362</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.03009621950198432</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>70</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>4207</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>環泰</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>19.29999923706055</v>
+      </c>
+      <c r="G8" t="n">
+        <v>19.40500001907349</v>
+      </c>
+      <c r="H8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>47.39128230658497</v>
+      </c>
+      <c r="J8" t="n">
+        <v>46.45232509400192</v>
+      </c>
+      <c r="K8" t="n">
+        <v>39.77931278697724</v>
+      </c>
+      <c r="L8" t="n">
+        <v>191769</v>
+      </c>
+      <c r="M8" t="n">
+        <v>120190.85</v>
+      </c>
+      <c r="N8" t="n">
+        <v>102506.6</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.595537430677959</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-0.1701468357126075</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-0.1914313294493503</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.02128449373674288</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.02260570862095346</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.03077567291693994</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>70</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3349</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>寶德</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>18.85000038146973</v>
+      </c>
+      <c r="G9" t="n">
+        <v>19.36500015258789</v>
+      </c>
+      <c r="H9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>37.60482290654189</v>
+      </c>
+      <c r="J9" t="n">
+        <v>33.2783706383258</v>
+      </c>
+      <c r="K9" t="n">
+        <v>33.87763849764255</v>
+      </c>
+      <c r="L9" t="n">
+        <v>287030</v>
+      </c>
+      <c r="M9" t="n">
+        <v>188168</v>
+      </c>
+      <c r="N9" t="n">
+        <v>202141.075</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.52539220271247</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-0.7475991553599606</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-0.8252576112665266</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.07765845590656606</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.06184930347564954</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.04373980999189941</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN9"/>
+  <dimension ref="A1:AN7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,49 +643,49 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>29.29999923706055</v>
+        <v>29.25</v>
       </c>
       <c r="G2" t="n">
-        <v>29.48749980926514</v>
+        <v>29.48999977111816</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>34.21913133510645</v>
+        <v>39.47942089110586</v>
       </c>
       <c r="J2" t="n">
-        <v>33.97894716985556</v>
+        <v>35.81243842959032</v>
       </c>
       <c r="K2" t="n">
-        <v>45.94078050840252</v>
+        <v>45.35367726965722</v>
       </c>
       <c r="L2" t="n">
-        <v>19822.2</v>
+        <v>21623.2</v>
       </c>
       <c r="M2" t="n">
-        <v>13061.05</v>
+        <v>13811.3</v>
       </c>
       <c r="N2" t="n">
-        <v>14956.65</v>
+        <v>14606.775</v>
       </c>
       <c r="O2" t="n">
-        <v>1.517657462455163</v>
+        <v>1.565616560352755</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.1594981511994646</v>
+        <v>-0.1576888472634543</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.1460251576936206</v>
+        <v>-0.1437849890590189</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.01347299350584405</v>
+        <v>-0.01390385820443543</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.01730334883661422</v>
+        <v>-0.01528267719281176</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.01989230789429874</v>
+        <v>-0.01925430553964688</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -775,12 +775,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>9949</t>
+          <t>8077</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>琉園</t>
+          <t>洛碁</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -789,49 +789,49 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>24.20000076293945</v>
+        <v>41.90000152587891</v>
       </c>
       <c r="G3" t="n">
-        <v>24.15249986648559</v>
+        <v>42.19250011444092</v>
       </c>
       <c r="H3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>37.0222422717444</v>
+        <v>37.8730425894468</v>
       </c>
       <c r="J3" t="n">
-        <v>35.51843972477845</v>
+        <v>32.28180388953243</v>
       </c>
       <c r="K3" t="n">
-        <v>49.0701968892679</v>
+        <v>46.29629042946247</v>
       </c>
       <c r="L3" t="n">
-        <v>313221.4</v>
+        <v>11007.6</v>
       </c>
       <c r="M3" t="n">
-        <v>100371.15</v>
+        <v>5005.75</v>
       </c>
       <c r="N3" t="n">
-        <v>68723.925</v>
+        <v>5396.575</v>
       </c>
       <c r="O3" t="n">
-        <v>3.12063177516647</v>
+        <v>2.198991160165809</v>
       </c>
       <c r="P3" t="n">
-        <v>0.06025973967355824</v>
+        <v>-0.585726300059747</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.04523973808438519</v>
+        <v>-0.574526090537591</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01502000158917306</v>
+        <v>-0.01120020952215606</v>
       </c>
       <c r="S3" t="n">
-        <v>0.02478584877907909</v>
+        <v>-0.08416789545260239</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.01830952087834201</v>
+        <v>-0.04777423133271252</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -921,63 +921,63 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4157</t>
+          <t>5546</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>太景*-KY</t>
+          <t>永固-KY</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>8.800000190734863</v>
+        <v>13.80000019073486</v>
       </c>
       <c r="G4" t="n">
-        <v>8.847500038146972</v>
+        <v>14.07500014305115</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>45.88195007481825</v>
+        <v>42.70883351137496</v>
       </c>
       <c r="J4" t="n">
-        <v>44.22801811964723</v>
+        <v>38.63788712607815</v>
       </c>
       <c r="K4" t="n">
-        <v>48.91984747275139</v>
+        <v>46.35730371292854</v>
       </c>
       <c r="L4" t="n">
-        <v>2790616.2</v>
+        <v>82832.60000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>1239215.2</v>
+        <v>40308.15</v>
       </c>
       <c r="N4" t="n">
-        <v>988984.4</v>
+        <v>47057.9</v>
       </c>
       <c r="O4" t="n">
-        <v>2.251922184298579</v>
+        <v>2.054983917644447</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01063903643603581</v>
+        <v>-0.2438624149944424</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.002662917596586213</v>
+        <v>-0.1983473752716165</v>
       </c>
       <c r="R4" t="n">
-        <v>0.01330195403262202</v>
+        <v>-0.04551503972282586</v>
       </c>
       <c r="S4" t="n">
-        <v>0.02334489605210566</v>
+        <v>-0.07491008119146778</v>
       </c>
       <c r="T4" t="n">
-        <v>0.02528440525433917</v>
+        <v>-0.06191469252091927</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1015,44 +1015,44 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>-8.553000000000001</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>-6.553</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>-9.576999999999998</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>-2.577</v>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -1067,63 +1067,63 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>6180</t>
+          <t>3033</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>橘子</t>
+          <t>威健</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>40.25</v>
+        <v>43.15000152587891</v>
       </c>
       <c r="G5" t="n">
-        <v>40.58000030517578</v>
+        <v>42.15500011444092</v>
       </c>
       <c r="H5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>37.95650170428486</v>
+        <v>47.55386617349842</v>
       </c>
       <c r="J5" t="n">
-        <v>33.89417324229827</v>
+        <v>47.24485086217334</v>
       </c>
       <c r="K5" t="n">
-        <v>44.77519895086012</v>
+        <v>47.45038387112216</v>
       </c>
       <c r="L5" t="n">
-        <v>581405.2</v>
+        <v>5261864.8</v>
       </c>
       <c r="M5" t="n">
-        <v>319424.2</v>
+        <v>2856723.95</v>
       </c>
       <c r="N5" t="n">
-        <v>312603.35</v>
+        <v>3237337.55</v>
       </c>
       <c r="O5" t="n">
-        <v>1.82016641193748</v>
+        <v>1.841922738107054</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.4184905277985891</v>
+        <v>-0.2484250376425763</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.3565345540607071</v>
+        <v>-0.5671590912521359</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.06195597373788198</v>
+        <v>0.3187340536095596</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1074515145809138</v>
+        <v>0.3180529035703213</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1355446885056974</v>
+        <v>0.3455922505488328</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1161,44 +1161,44 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>686.234</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>-78</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>-37.863</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>570.3710000000001</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>-557.251</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>-82.94800000000001</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>-624.587</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>-1264.786</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>-3464.844</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>-105.635</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>-1557.675</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>-5128.154</v>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -1213,12 +1213,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3629</t>
+          <t>2756</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>地心引力</t>
+          <t>聯發國際</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1227,49 +1227,49 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>14.39999961853027</v>
+        <v>60.70000076293945</v>
       </c>
       <c r="G6" t="n">
-        <v>16.60750021934509</v>
+        <v>61.93500003814697</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>45.93221909738547</v>
+        <v>42.17892554510296</v>
       </c>
       <c r="J6" t="n">
-        <v>37.98464350080399</v>
+        <v>41.90686376264285</v>
       </c>
       <c r="K6" t="n">
-        <v>40.69411263497764</v>
+        <v>44.46911393041243</v>
       </c>
       <c r="L6" t="n">
-        <v>8600</v>
+        <v>49800</v>
       </c>
       <c r="M6" t="n">
-        <v>4737.45</v>
+        <v>29736.9</v>
       </c>
       <c r="N6" t="n">
-        <v>6077</v>
+        <v>27373</v>
       </c>
       <c r="O6" t="n">
-        <v>1.815322589156614</v>
+        <v>1.674687005034149</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.761897729225705</v>
+        <v>-0.3302655065608775</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.5005199616121038</v>
+        <v>-0.07825990741563801</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.2613777676136012</v>
+        <v>-0.2520055991452395</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2694023288470383</v>
+        <v>-0.2858287860356707</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3297071310246915</v>
+        <v>-0.2749370929964949</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -1359,63 +1359,63 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>8092</t>
+          <t>4441</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>建暐</t>
+          <t>振大環球</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>12.39999961853027</v>
+        <v>167.5</v>
       </c>
       <c r="G7" t="n">
-        <v>12.58999996185303</v>
+        <v>169.95</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>42.95529461990483</v>
+        <v>33.75866108133361</v>
       </c>
       <c r="J7" t="n">
-        <v>37.70219607234667</v>
+        <v>30.8650528222336</v>
       </c>
       <c r="K7" t="n">
-        <v>44.4684599726675</v>
+        <v>38.25183045311576</v>
       </c>
       <c r="L7" t="n">
-        <v>161806.4</v>
+        <v>130522.2</v>
       </c>
       <c r="M7" t="n">
-        <v>91420.10000000001</v>
+        <v>78542.25</v>
       </c>
       <c r="N7" t="n">
-        <v>63717.55</v>
+        <v>68255</v>
       </c>
       <c r="O7" t="n">
-        <v>1.769921494288455</v>
+        <v>1.66180877171204</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.1026699552085706</v>
+        <v>-2.182926186906542</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.1266865359666954</v>
+        <v>-2.259526719949627</v>
       </c>
       <c r="R7" t="n">
-        <v>0.02401658075812479</v>
+        <v>0.07660053304308523</v>
       </c>
       <c r="S7" t="n">
-        <v>0.03660220404784362</v>
+        <v>0.06070525482918709</v>
       </c>
       <c r="T7" t="n">
-        <v>0.03009621950198432</v>
+        <v>0.01250319386707144</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>32.3</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1462,327 +1462,35 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>32.3</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>20.575</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-39.425</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>81.41099999999999</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>-65</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>16.41099999999999</v>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>70</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>4207</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>環泰</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>19.29999923706055</v>
-      </c>
-      <c r="G8" t="n">
-        <v>19.40500001907349</v>
-      </c>
-      <c r="H8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>47.39128230658497</v>
-      </c>
-      <c r="J8" t="n">
-        <v>46.45232509400192</v>
-      </c>
-      <c r="K8" t="n">
-        <v>39.77931278697724</v>
-      </c>
-      <c r="L8" t="n">
-        <v>191769</v>
-      </c>
-      <c r="M8" t="n">
-        <v>120190.85</v>
-      </c>
-      <c r="N8" t="n">
-        <v>102506.6</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.595537430677959</v>
-      </c>
-      <c r="P8" t="n">
-        <v>-0.1701468357126075</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>-0.1914313294493503</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.02128449373674288</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.02260570862095346</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0.03077567291693994</v>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>70</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>3349</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>寶德</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>18.85000038146973</v>
-      </c>
-      <c r="G9" t="n">
-        <v>19.36500015258789</v>
-      </c>
-      <c r="H9" t="b">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>37.60482290654189</v>
-      </c>
-      <c r="J9" t="n">
-        <v>33.2783706383258</v>
-      </c>
-      <c r="K9" t="n">
-        <v>33.87763849764255</v>
-      </c>
-      <c r="L9" t="n">
-        <v>287030</v>
-      </c>
-      <c r="M9" t="n">
-        <v>188168</v>
-      </c>
-      <c r="N9" t="n">
-        <v>202141.075</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.52539220271247</v>
-      </c>
-      <c r="P9" t="n">
-        <v>-0.7475991553599606</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>-0.8252576112665266</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.07765845590656606</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.06184930347564954</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0.04373980999189941</v>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN7"/>
+  <dimension ref="A1:AN6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -629,67 +629,67 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1796</t>
+          <t>4441</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>金穎生技</t>
+          <t>振大環球</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>29.25</v>
+        <v>167.5</v>
       </c>
       <c r="G2" t="n">
-        <v>29.48999977111816</v>
+        <v>169.95</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>39.47942089110586</v>
+        <v>33.75866108445424</v>
       </c>
       <c r="J2" t="n">
-        <v>35.81243842959032</v>
+        <v>30.86505288023947</v>
       </c>
       <c r="K2" t="n">
-        <v>45.35367726965722</v>
+        <v>41.38027085209842</v>
       </c>
       <c r="L2" t="n">
-        <v>21623.2</v>
+        <v>130200</v>
       </c>
       <c r="M2" t="n">
-        <v>13811.3</v>
+        <v>78461.7</v>
       </c>
       <c r="N2" t="n">
-        <v>14606.775</v>
+        <v>68214.72500000001</v>
       </c>
       <c r="O2" t="n">
-        <v>1.565616560352755</v>
+        <v>1.65940834827693</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.1576888472634543</v>
+        <v>-2.136359940827276</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.1437849890590189</v>
+        <v>-2.191385542642779</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.01390385820443543</v>
+        <v>0.05502560181550287</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.01528267719281176</v>
+        <v>0.03744572256751733</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.01925430553964688</v>
+        <v>-0.01256829876603049</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -709,12 +709,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>-32</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -732,31 +732,31 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>-32</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>59.197</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>-51</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>8.196999999999996</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>37.411</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>-65</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>-27.589</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
@@ -771,16 +771,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>8077</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>洛碁</t>
+          <t>金穎生技</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -789,53 +789,53 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>41.90000152587891</v>
+        <v>29.25</v>
       </c>
       <c r="G3" t="n">
-        <v>42.19250011444092</v>
+        <v>29.48999977111816</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>37.8730425894468</v>
+        <v>39.47942089930626</v>
       </c>
       <c r="J3" t="n">
-        <v>32.28180388953243</v>
+        <v>35.81243858094359</v>
       </c>
       <c r="K3" t="n">
-        <v>46.29629042946247</v>
+        <v>46.86370360252005</v>
       </c>
       <c r="L3" t="n">
-        <v>11007.6</v>
+        <v>21622.2</v>
       </c>
       <c r="M3" t="n">
-        <v>5005.75</v>
+        <v>13811.05</v>
       </c>
       <c r="N3" t="n">
-        <v>5396.575</v>
+        <v>14606.65</v>
       </c>
       <c r="O3" t="n">
-        <v>2.198991160165809</v>
+        <v>1.565572494488109</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.585726300059747</v>
+        <v>-0.1500176840698302</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.574526090537591</v>
+        <v>-0.1325624126971252</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.01120020952215606</v>
+        <v>-0.017455271372705</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.08416789545260239</v>
+        <v>-0.01911104888706883</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.04777423133271252</v>
+        <v>-0.02338051258999799</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -921,63 +921,63 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>5546</t>
+          <t>8077</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>永固-KY</t>
+          <t>洛碁</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>13.80000019073486</v>
+        <v>41.90000152587891</v>
       </c>
       <c r="G4" t="n">
-        <v>14.07500014305115</v>
+        <v>42.19250011444092</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>42.70883351137496</v>
+        <v>37.87304259725784</v>
       </c>
       <c r="J4" t="n">
-        <v>38.63788712607815</v>
+        <v>32.28180403388223</v>
       </c>
       <c r="K4" t="n">
-        <v>46.35730371292854</v>
+        <v>47.47084564183372</v>
       </c>
       <c r="L4" t="n">
-        <v>82832.60000000001</v>
+        <v>11006</v>
       </c>
       <c r="M4" t="n">
-        <v>40308.15</v>
+        <v>5005.35</v>
       </c>
       <c r="N4" t="n">
-        <v>47057.9</v>
+        <v>5396.375</v>
       </c>
       <c r="O4" t="n">
-        <v>2.054983917644447</v>
+        <v>2.198847233460198</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2438624149944424</v>
+        <v>-0.5743975905526142</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.1983473752716165</v>
+        <v>-0.5579492955768954</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.04551503972282586</v>
+        <v>-0.01644829497571876</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.07491008119146778</v>
+        <v>-0.08982567286832777</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.06191469252091927</v>
+        <v>-0.05387265868709601</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1015,40 +1015,40 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>-8.553000000000001</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>-6.553</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-9.576999999999998</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>-2.577</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3033</t>
+          <t>5546</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>威健</t>
+          <t>永固-KY</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1081,120 +1081,120 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>43.15000152587891</v>
+        <v>13.80000019073486</v>
       </c>
       <c r="G5" t="n">
-        <v>42.15500011444092</v>
+        <v>14.07500014305115</v>
       </c>
       <c r="H5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>42.70883351657083</v>
+      </c>
+      <c r="J5" t="n">
+        <v>38.63788722222824</v>
+      </c>
+      <c r="K5" t="n">
+        <v>46.38029677095577</v>
+      </c>
+      <c r="L5" t="n">
+        <v>82644.2</v>
+      </c>
+      <c r="M5" t="n">
+        <v>40261.05</v>
+      </c>
+      <c r="N5" t="n">
+        <v>47034.35</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.052708511079567</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-0.2468458507111073</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-0.2027106092549085</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-0.04413524145619879</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-0.07342285158700054</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-0.06031196490636384</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>-7</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
         <v>1</v>
       </c>
-      <c r="I5" t="n">
-        <v>47.55386617349842</v>
-      </c>
-      <c r="J5" t="n">
-        <v>47.24485086217334</v>
-      </c>
-      <c r="K5" t="n">
-        <v>47.45038387112216</v>
-      </c>
-      <c r="L5" t="n">
-        <v>5261864.8</v>
-      </c>
-      <c r="M5" t="n">
-        <v>2856723.95</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3237337.55</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.841922738107054</v>
-      </c>
-      <c r="P5" t="n">
-        <v>-0.2484250376425763</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>-0.5671590912521359</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.3187340536095596</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.3180529035703213</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.3455922505488328</v>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB5" t="n">
-        <v>686.234</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>-78</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>-37.863</v>
-      </c>
       <c r="AE5" t="n">
-        <v>570.3710000000001</v>
+        <v>-6</v>
       </c>
       <c r="AF5" t="n">
-        <v>-557.251</v>
+        <v>-10</v>
       </c>
       <c r="AG5" t="n">
-        <v>-82.94800000000001</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-624.587</v>
+        <v>4</v>
       </c>
       <c r="AI5" t="n">
-        <v>-1264.786</v>
+        <v>-6</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-3464.844</v>
+        <v>-19.577</v>
       </c>
       <c r="AK5" t="n">
-        <v>-105.635</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>-1557.675</v>
+        <v>8</v>
       </c>
       <c r="AM5" t="n">
-        <v>-5128.154</v>
+        <v>-11.577</v>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
@@ -1236,13 +1236,13 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>42.17892554510296</v>
+        <v>42.17892554892757</v>
       </c>
       <c r="J6" t="n">
-        <v>41.90686376264285</v>
+        <v>41.90686383231443</v>
       </c>
       <c r="K6" t="n">
-        <v>44.46911393041243</v>
+        <v>44.39541729198687</v>
       </c>
       <c r="L6" t="n">
         <v>49800</v>
@@ -1257,19 +1257,19 @@
         <v>1.674687005034149</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.3302655065608775</v>
+        <v>-0.3294219677733494</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.07825990741563801</v>
+        <v>-0.07702616835672794</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.2520055991452395</v>
+        <v>-0.2523957994166215</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2858287860356707</v>
+        <v>-0.2862493766375571</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2749370929964949</v>
+        <v>-0.2753903575262918</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1343,152 +1343,6 @@
         <v>0</v>
       </c>
       <c r="AN6" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>70</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>4441</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>振大環球</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>167.5</v>
-      </c>
-      <c r="G7" t="n">
-        <v>169.95</v>
-      </c>
-      <c r="H7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>33.75866108133361</v>
-      </c>
-      <c r="J7" t="n">
-        <v>30.8650528222336</v>
-      </c>
-      <c r="K7" t="n">
-        <v>38.25183045311576</v>
-      </c>
-      <c r="L7" t="n">
-        <v>130522.2</v>
-      </c>
-      <c r="M7" t="n">
-        <v>78542.25</v>
-      </c>
-      <c r="N7" t="n">
-        <v>68255</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.66180877171204</v>
-      </c>
-      <c r="P7" t="n">
-        <v>-2.182926186906542</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>-2.259526719949627</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.07660053304308523</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.06070525482918709</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.01250319386707144</v>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB7" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>20.575</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>-60</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>-39.425</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>81.41099999999999</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>-65</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>16.41099999999999</v>
-      </c>
-      <c r="AN7" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN6"/>
+  <dimension ref="A1:AN5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,16 +625,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4441</t>
+          <t>8101</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>振大環球</t>
+          <t>華冠</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -643,124 +643,124 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>167.5</v>
+        <v>9.989999771118164</v>
       </c>
       <c r="G2" t="n">
-        <v>169.95</v>
+        <v>10.61800003051758</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>33.75866108445424</v>
+        <v>44.5179162845414</v>
       </c>
       <c r="J2" t="n">
-        <v>30.86505288023947</v>
+        <v>38.08292730587635</v>
       </c>
       <c r="K2" t="n">
-        <v>41.38027085209842</v>
+        <v>39.0223325597096</v>
       </c>
       <c r="L2" t="n">
-        <v>130200</v>
+        <v>23878.6</v>
       </c>
       <c r="M2" t="n">
-        <v>78461.7</v>
+        <v>12339.45</v>
       </c>
       <c r="N2" t="n">
-        <v>68214.72500000001</v>
+        <v>10844.525</v>
       </c>
       <c r="O2" t="n">
-        <v>1.65940834827693</v>
+        <v>1.935142976388737</v>
       </c>
       <c r="P2" t="n">
-        <v>-2.136359940827276</v>
+        <v>-0.5267011334873022</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.191385542642779</v>
+        <v>-0.492762926856408</v>
       </c>
       <c r="R2" t="n">
-        <v>0.05502560181550287</v>
+        <v>-0.03393820663089414</v>
       </c>
       <c r="S2" t="n">
-        <v>0.03744572256751733</v>
+        <v>-0.05872963046900448</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.01256829876603049</v>
+        <v>-0.08632723849587298</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
       <c r="AB2" t="n">
-        <v>-32</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>0.225</v>
       </c>
       <c r="AE2" t="n">
-        <v>-32</v>
+        <v>0.225</v>
       </c>
       <c r="AF2" t="n">
-        <v>59.197</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>-51</v>
+        <v>0.225</v>
       </c>
       <c r="AI2" t="n">
-        <v>8.196999999999996</v>
+        <v>0.225</v>
       </c>
       <c r="AJ2" t="n">
-        <v>37.411</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>-65</v>
+        <v>0.225</v>
       </c>
       <c r="AM2" t="n">
-        <v>-27.589</v>
+        <v>0.225</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -775,63 +775,63 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1796</t>
+          <t>5546</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>金穎生技</t>
+          <t>永固-KY</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>29.25</v>
+        <v>13.5</v>
       </c>
       <c r="G3" t="n">
-        <v>29.48999977111816</v>
+        <v>13.9475001335144</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>39.47942089930626</v>
+        <v>41.85751711203831</v>
       </c>
       <c r="J3" t="n">
-        <v>35.81243858094359</v>
+        <v>40.50224306363673</v>
       </c>
       <c r="K3" t="n">
-        <v>46.86370360252005</v>
+        <v>42.99692235796033</v>
       </c>
       <c r="L3" t="n">
-        <v>21622.2</v>
+        <v>81410.39999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>13811.05</v>
+        <v>41512.65</v>
       </c>
       <c r="N3" t="n">
-        <v>14606.65</v>
+        <v>45760.15</v>
       </c>
       <c r="O3" t="n">
-        <v>1.565572494488109</v>
+        <v>1.96109860488309</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.1500176840698302</v>
+        <v>-0.2561133633186969</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1325624126971252</v>
+        <v>-0.22154354605194</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.017455271372705</v>
+        <v>-0.03456981726675698</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.01911104888706883</v>
+        <v>-0.04076192992136846</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.02338051258999799</v>
+        <v>-0.04413524145619879</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -869,44 +869,44 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>-29.577</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>-27.577</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>8077</t>
+          <t>2949</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>洛碁</t>
+          <t>欣新網</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,49 +935,49 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>41.90000152587891</v>
+        <v>63</v>
       </c>
       <c r="G4" t="n">
-        <v>42.19250011444092</v>
+        <v>64.93000030517578</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>37.87304259725784</v>
+        <v>49.39467841375637</v>
       </c>
       <c r="J4" t="n">
-        <v>32.28180403388223</v>
+        <v>48.13637815436499</v>
       </c>
       <c r="K4" t="n">
-        <v>47.47084564183372</v>
+        <v>44.76120766028657</v>
       </c>
       <c r="L4" t="n">
-        <v>11006</v>
+        <v>3207.6</v>
       </c>
       <c r="M4" t="n">
-        <v>5005.35</v>
+        <v>1869.55</v>
       </c>
       <c r="N4" t="n">
-        <v>5396.375</v>
+        <v>1528.325</v>
       </c>
       <c r="O4" t="n">
-        <v>2.198847233460198</v>
+        <v>1.715706988312696</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.5743975905526142</v>
+        <v>0.4654122769230185</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.5579492955768954</v>
+        <v>0.4935349868946228</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.01644829497571876</v>
+        <v>-0.02812270997160438</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.08982567286832777</v>
+        <v>0.1952049210983932</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.05387265868709601</v>
+        <v>0.04936167651063383</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -1067,63 +1067,63 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5546</t>
+          <t>3095</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>永固-KY</t>
+          <t>及成</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>13.80000019073486</v>
+        <v>33.15000152587891</v>
       </c>
       <c r="G5" t="n">
-        <v>14.07500014305115</v>
+        <v>33.33000011444092</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>42.70883351657083</v>
+        <v>48.86744513060617</v>
       </c>
       <c r="J5" t="n">
-        <v>38.63788722222824</v>
+        <v>42.90666478267164</v>
       </c>
       <c r="K5" t="n">
-        <v>46.38029677095577</v>
+        <v>45.6382719694646</v>
       </c>
       <c r="L5" t="n">
-        <v>82644.2</v>
+        <v>24519.2</v>
       </c>
       <c r="M5" t="n">
-        <v>40261.05</v>
+        <v>15184.95</v>
       </c>
       <c r="N5" t="n">
-        <v>47034.35</v>
+        <v>10362.275</v>
       </c>
       <c r="O5" t="n">
-        <v>2.052708511079567</v>
+        <v>1.614704032611237</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2468458507111073</v>
+        <v>-0.6192384899686161</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2027106092549085</v>
+        <v>-0.7122686417247662</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.04413524145619879</v>
+        <v>0.09303015175615015</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.07342285158700054</v>
+        <v>0.06950864730452699</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.06031196490636384</v>
+        <v>0.06741203349259672</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1161,190 +1161,44 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-19.577</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
         <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>-11.577</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>70</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2756</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>聯發國際</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>60.70000076293945</v>
-      </c>
-      <c r="G6" t="n">
-        <v>61.93500003814697</v>
-      </c>
-      <c r="H6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>42.17892554892757</v>
-      </c>
-      <c r="J6" t="n">
-        <v>41.90686383231443</v>
-      </c>
-      <c r="K6" t="n">
-        <v>44.39541729198687</v>
-      </c>
-      <c r="L6" t="n">
-        <v>49800</v>
-      </c>
-      <c r="M6" t="n">
-        <v>29736.9</v>
-      </c>
-      <c r="N6" t="n">
-        <v>27373</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.674687005034149</v>
-      </c>
-      <c r="P6" t="n">
-        <v>-0.3294219677733494</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>-0.07702616835672794</v>
-      </c>
-      <c r="R6" t="n">
-        <v>-0.2523957994166215</v>
-      </c>
-      <c r="S6" t="n">
-        <v>-0.2862493766375571</v>
-      </c>
-      <c r="T6" t="n">
-        <v>-0.2753903575262918</v>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN5"/>
+  <dimension ref="A1:AN7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,16 +625,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8101</t>
+          <t>7786</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>華冠</t>
+          <t>東方風能</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -643,53 +643,53 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>9.989999771118164</v>
+        <v>118.5</v>
       </c>
       <c r="G2" t="n">
-        <v>10.61800003051758</v>
+        <v>118</v>
       </c>
       <c r="H2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>44.5179162845414</v>
+        <v>45.39859974792159</v>
       </c>
       <c r="J2" t="n">
-        <v>38.08292730587635</v>
+        <v>41.34018519024317</v>
       </c>
       <c r="K2" t="n">
-        <v>39.0223325597096</v>
+        <v>49.9899076183347</v>
       </c>
       <c r="L2" t="n">
-        <v>23878.6</v>
+        <v>470520</v>
       </c>
       <c r="M2" t="n">
-        <v>12339.45</v>
+        <v>192570.85</v>
       </c>
       <c r="N2" t="n">
-        <v>10844.525</v>
+        <v>169000.025</v>
       </c>
       <c r="O2" t="n">
-        <v>1.935142976388737</v>
+        <v>2.443360456683865</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.5267011334873022</v>
+        <v>-0.02364030686372587</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.492762926856408</v>
+        <v>-0.5178935319629553</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.03393820663089414</v>
+        <v>0.4942532250992294</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.05872963046900448</v>
+        <v>0.5974079065195825</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.08632723849587298</v>
+        <v>0.4668063137057158</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -723,44 +723,44 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>8.122999999999999</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.225</v>
+        <v>-1</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.225</v>
+        <v>7.122999999999999</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>497.199</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.225</v>
+        <v>-61</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.225</v>
+        <v>436.199</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>842.5840000000001</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.225</v>
+        <v>-72</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.225</v>
+        <v>770.5840000000001</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
@@ -789,50 +789,50 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>13.5</v>
+        <v>13.80000019073486</v>
       </c>
       <c r="G3" t="n">
-        <v>13.9475001335144</v>
+        <v>13.90000014305115</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>41.85751711203831</v>
+        <v>47.51285674650875</v>
       </c>
       <c r="J3" t="n">
-        <v>40.50224306363673</v>
+        <v>42.83911431529047</v>
       </c>
       <c r="K3" t="n">
-        <v>42.99692235796033</v>
+        <v>46.96213707071186</v>
       </c>
       <c r="L3" t="n">
-        <v>81410.39999999999</v>
+        <v>84336</v>
       </c>
       <c r="M3" t="n">
-        <v>41512.65</v>
+        <v>43194.05</v>
       </c>
       <c r="N3" t="n">
-        <v>45760.15</v>
+        <v>46200.85</v>
       </c>
       <c r="O3" t="n">
-        <v>1.96109860488309</v>
+        <v>1.952491141719751</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.2561133633186969</v>
+        <v>-0.2311828367181867</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.22154354605194</v>
+        <v>-0.2234714041851893</v>
       </c>
       <c r="R3" t="n">
+        <v>-0.007711432532997414</v>
+      </c>
+      <c r="S3" t="n">
         <v>-0.03456981726675698</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>-0.04076192992136846</v>
       </c>
-      <c r="T3" t="n">
-        <v>-0.04413524145619879</v>
-      </c>
       <c r="U3" t="inlineStr">
         <is>
           <t>是</t>
@@ -869,44 +869,44 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>-9</v>
+        <v>-16</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AE3" t="n">
-        <v>-11</v>
+        <v>-17</v>
       </c>
       <c r="AF3" t="n">
-        <v>-9</v>
+        <v>-18</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI3" t="n">
-        <v>-7</v>
+        <v>-17</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-29.577</v>
+        <v>-49.577</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>-27.577</v>
+        <v>-48.577</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
@@ -917,67 +917,67 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2949</t>
+          <t>6955</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>欣新網</t>
+          <t>邦睿生技-創</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>63</v>
+        <v>90.30000305175781</v>
       </c>
       <c r="G4" t="n">
-        <v>64.93000030517578</v>
+        <v>93.50499992370605</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>49.39467841375637</v>
+        <v>41.67015320428199</v>
       </c>
       <c r="J4" t="n">
-        <v>48.13637815436499</v>
+        <v>39.32049072060046</v>
       </c>
       <c r="K4" t="n">
-        <v>44.76120766028657</v>
+        <v>30.25417448107962</v>
       </c>
       <c r="L4" t="n">
-        <v>3207.6</v>
+        <v>12046</v>
       </c>
       <c r="M4" t="n">
-        <v>1869.55</v>
+        <v>7749.95</v>
       </c>
       <c r="N4" t="n">
-        <v>1528.325</v>
+        <v>8630.325000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>1.715706988312696</v>
+        <v>1.554332608597475</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4654122769230185</v>
+        <v>-1.558733410561686</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4935349868946228</v>
+        <v>-1.436942437793764</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.02812270997160438</v>
+        <v>-0.1217909727679221</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1952049210983932</v>
+        <v>-0.03904053024920184</v>
       </c>
       <c r="T4" t="n">
-        <v>0.04936167651063383</v>
+        <v>-0.07674657196678059</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1015,44 +1015,44 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>6.07</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>6.122</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>14.14</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>20.262</v>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
@@ -1063,142 +1063,434 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>80</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2109</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>華豐</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>14.30000019073486</v>
+      </c>
+      <c r="G5" t="n">
+        <v>14.43500008583069</v>
+      </c>
+      <c r="H5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>46.68642252346051</v>
+      </c>
+      <c r="J5" t="n">
+        <v>45.13245592187096</v>
+      </c>
+      <c r="K5" t="n">
+        <v>42.23068777112609</v>
+      </c>
+      <c r="L5" t="n">
+        <v>266702.6</v>
+      </c>
+      <c r="M5" t="n">
+        <v>177515.9</v>
+      </c>
+      <c r="N5" t="n">
+        <v>135981.85</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.502415276603392</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-0.09810337157270865</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-0.09990646295698585</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.0018030913842772</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.0006236023291803783</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.0001493669354226956</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>174.817</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>173.817</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>102.937</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>104.937</v>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>70</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>3095</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>及成</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>5353</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>台林</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="F5" t="n">
-        <v>33.15000152587891</v>
-      </c>
-      <c r="G5" t="n">
-        <v>33.33000011444092</v>
-      </c>
-      <c r="H5" t="b">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>48.86744513060617</v>
-      </c>
-      <c r="J5" t="n">
-        <v>42.90666478267164</v>
-      </c>
-      <c r="K5" t="n">
-        <v>45.6382719694646</v>
-      </c>
-      <c r="L5" t="n">
-        <v>24519.2</v>
-      </c>
-      <c r="M5" t="n">
-        <v>15184.95</v>
-      </c>
-      <c r="N5" t="n">
-        <v>10362.275</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.614704032611237</v>
-      </c>
-      <c r="P5" t="n">
-        <v>-0.6192384899686161</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>-0.7122686417247662</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.09303015175615015</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.06950864730452699</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.06741203349259672</v>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
+      <c r="F6" t="n">
+        <v>27.89999961853027</v>
+      </c>
+      <c r="G6" t="n">
+        <v>28.35750007629395</v>
+      </c>
+      <c r="H6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>31.49721543941131</v>
+      </c>
+      <c r="J6" t="n">
+        <v>31.49495926902908</v>
+      </c>
+      <c r="K6" t="n">
+        <v>46.10599871905448</v>
+      </c>
+      <c r="L6" t="n">
+        <v>116043.4</v>
+      </c>
+      <c r="M6" t="n">
+        <v>69074.3</v>
+      </c>
+      <c r="N6" t="n">
+        <v>51158.9</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.679979384517831</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-0.04889195947079017</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.07421152958372353</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-0.1231034890545137</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-0.1324476682071835</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-0.1276236724279375</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>70</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>3494</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>誠研</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>7.010000228881836</v>
+      </c>
+      <c r="G7" t="n">
+        <v>7.082000088691712</v>
+      </c>
+      <c r="H7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>47.87552520599389</v>
+      </c>
+      <c r="J7" t="n">
+        <v>45.71409254993063</v>
+      </c>
+      <c r="K7" t="n">
+        <v>39.5216475669895</v>
+      </c>
+      <c r="L7" t="n">
+        <v>91974.2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>58341.7</v>
+      </c>
+      <c r="N7" t="n">
+        <v>63876.35</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.576474459948887</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-0.02323763295189973</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-0.01780276538168292</v>
+      </c>
+      <c r="R7" t="n">
+        <v>-0.005434867570216814</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-0.004189722568558443</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-0.002631707567612983</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>-15.653</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>-11.653</v>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN7"/>
+  <dimension ref="A1:AN3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,67 +625,67 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>7786</t>
+          <t>6846</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>東方風能</t>
+          <t>綠茵</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>118.5</v>
+        <v>57.90000152587891</v>
       </c>
       <c r="G2" t="n">
-        <v>118</v>
+        <v>58.08999996185302</v>
       </c>
       <c r="H2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>45.39859974792159</v>
+        <v>44.07253950624264</v>
       </c>
       <c r="J2" t="n">
-        <v>41.34018519024317</v>
+        <v>38.31003492681601</v>
       </c>
       <c r="K2" t="n">
-        <v>49.9899076183347</v>
+        <v>46.76015535942507</v>
       </c>
       <c r="L2" t="n">
-        <v>470520</v>
+        <v>14837.6</v>
       </c>
       <c r="M2" t="n">
-        <v>192570.85</v>
+        <v>7867.45</v>
       </c>
       <c r="N2" t="n">
-        <v>169000.025</v>
+        <v>7271.95</v>
       </c>
       <c r="O2" t="n">
-        <v>2.443360456683865</v>
+        <v>1.885947797571005</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.02364030686372587</v>
+        <v>-0.2213770443767231</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.5178935319629553</v>
+        <v>-0.2394901149307183</v>
       </c>
       <c r="R2" t="n">
-        <v>0.4942532250992294</v>
+        <v>0.01811307055399516</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5974079065195825</v>
+        <v>0.008056894453980307</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4668063137057158</v>
+        <v>-0.04583880816104052</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -723,44 +723,44 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>8.122999999999999</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>7.122999999999999</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>497.199</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>-61</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>436.199</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>842.5840000000001</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>-72</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>770.5840000000001</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -771,16 +771,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>5546</t>
+          <t>2642</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>永固-KY</t>
+          <t>宅配通</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -789,73 +789,73 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>13.80000019073486</v>
+        <v>20</v>
       </c>
       <c r="G3" t="n">
-        <v>13.90000014305115</v>
+        <v>20.27499990463257</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>47.51285674650875</v>
+        <v>46.45712576163717</v>
       </c>
       <c r="J3" t="n">
-        <v>42.83911431529047</v>
+        <v>40.96155817428451</v>
       </c>
       <c r="K3" t="n">
-        <v>46.96213707071186</v>
+        <v>36.34104207231446</v>
       </c>
       <c r="L3" t="n">
-        <v>84336</v>
+        <v>74170.2</v>
       </c>
       <c r="M3" t="n">
-        <v>43194.05</v>
+        <v>42432.35</v>
       </c>
       <c r="N3" t="n">
-        <v>46200.85</v>
+        <v>40710.75</v>
       </c>
       <c r="O3" t="n">
-        <v>1.952491141719751</v>
+        <v>1.747963523113851</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.2311828367181867</v>
+        <v>-0.06353845546477999</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2234714041851893</v>
+        <v>-0.03803155798686207</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.007711432532997414</v>
+        <v>-0.02550689747791791</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.03456981726675698</v>
+        <v>-0.01701274842385041</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.04076192992136846</v>
+        <v>-0.01175925837098443</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -869,628 +869,44 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>-16</v>
+        <v>-13</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>-17</v>
+        <v>-13</v>
       </c>
       <c r="AF3" t="n">
-        <v>-18</v>
+        <v>-12</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1</v>
+        <v>-8</v>
       </c>
       <c r="AI3" t="n">
-        <v>-17</v>
+        <v>-20</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-49.577</v>
+        <v>13.52</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AM3" t="n">
-        <v>-48.577</v>
+        <v>16.52</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>80</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>6955</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>邦睿生技-創</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>90.30000305175781</v>
-      </c>
-      <c r="G4" t="n">
-        <v>93.50499992370605</v>
-      </c>
-      <c r="H4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>41.67015320428199</v>
-      </c>
-      <c r="J4" t="n">
-        <v>39.32049072060046</v>
-      </c>
-      <c r="K4" t="n">
-        <v>30.25417448107962</v>
-      </c>
-      <c r="L4" t="n">
-        <v>12046</v>
-      </c>
-      <c r="M4" t="n">
-        <v>7749.95</v>
-      </c>
-      <c r="N4" t="n">
-        <v>8630.325000000001</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.554332608597475</v>
-      </c>
-      <c r="P4" t="n">
-        <v>-1.558733410561686</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>-1.436942437793764</v>
-      </c>
-      <c r="R4" t="n">
-        <v>-0.1217909727679221</v>
-      </c>
-      <c r="S4" t="n">
-        <v>-0.03904053024920184</v>
-      </c>
-      <c r="T4" t="n">
-        <v>-0.07674657196678059</v>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>6.07</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>6.122</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>14.14</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>20.262</v>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>80</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2109</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>華豐</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>14.30000019073486</v>
-      </c>
-      <c r="G5" t="n">
-        <v>14.43500008583069</v>
-      </c>
-      <c r="H5" t="b">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>46.68642252346051</v>
-      </c>
-      <c r="J5" t="n">
-        <v>45.13245592187096</v>
-      </c>
-      <c r="K5" t="n">
-        <v>42.23068777112609</v>
-      </c>
-      <c r="L5" t="n">
-        <v>266702.6</v>
-      </c>
-      <c r="M5" t="n">
-        <v>177515.9</v>
-      </c>
-      <c r="N5" t="n">
-        <v>135981.85</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.502415276603392</v>
-      </c>
-      <c r="P5" t="n">
-        <v>-0.09810337157270865</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>-0.09990646295698585</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.0018030913842772</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.0006236023291803783</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.0001493669354226956</v>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>174.817</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>173.817</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>102.937</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>104.937</v>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>70</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>5353</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>台林</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>27.89999961853027</v>
-      </c>
-      <c r="G6" t="n">
-        <v>28.35750007629395</v>
-      </c>
-      <c r="H6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>31.49721543941131</v>
-      </c>
-      <c r="J6" t="n">
-        <v>31.49495926902908</v>
-      </c>
-      <c r="K6" t="n">
-        <v>46.10599871905448</v>
-      </c>
-      <c r="L6" t="n">
-        <v>116043.4</v>
-      </c>
-      <c r="M6" t="n">
-        <v>69074.3</v>
-      </c>
-      <c r="N6" t="n">
-        <v>51158.9</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.679979384517831</v>
-      </c>
-      <c r="P6" t="n">
-        <v>-0.04889195947079017</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.07421152958372353</v>
-      </c>
-      <c r="R6" t="n">
-        <v>-0.1231034890545137</v>
-      </c>
-      <c r="S6" t="n">
-        <v>-0.1324476682071835</v>
-      </c>
-      <c r="T6" t="n">
-        <v>-0.1276236724279375</v>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>符合</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>70</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>3494</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>誠研</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>7.010000228881836</v>
-      </c>
-      <c r="G7" t="n">
-        <v>7.082000088691712</v>
-      </c>
-      <c r="H7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>47.87552520599389</v>
-      </c>
-      <c r="J7" t="n">
-        <v>45.71409254993063</v>
-      </c>
-      <c r="K7" t="n">
-        <v>39.5216475669895</v>
-      </c>
-      <c r="L7" t="n">
-        <v>91974.2</v>
-      </c>
-      <c r="M7" t="n">
-        <v>58341.7</v>
-      </c>
-      <c r="N7" t="n">
-        <v>63876.35</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.576474459948887</v>
-      </c>
-      <c r="P7" t="n">
-        <v>-0.02323763295189973</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>-0.01780276538168292</v>
-      </c>
-      <c r="R7" t="n">
-        <v>-0.005434867570216814</v>
-      </c>
-      <c r="S7" t="n">
-        <v>-0.004189722568558443</v>
-      </c>
-      <c r="T7" t="n">
-        <v>-0.002631707567612983</v>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>-6</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>-15.653</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>-11.653</v>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -652,40 +652,40 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>44.07253950624264</v>
+        <v>44.07253950744339</v>
       </c>
       <c r="J2" t="n">
-        <v>38.31003492681601</v>
+        <v>38.31003494922997</v>
       </c>
       <c r="K2" t="n">
-        <v>46.76015535942507</v>
+        <v>47.13584056222838</v>
       </c>
       <c r="L2" t="n">
-        <v>14837.6</v>
+        <v>14800</v>
       </c>
       <c r="M2" t="n">
-        <v>7867.45</v>
+        <v>7858.05</v>
       </c>
       <c r="N2" t="n">
-        <v>7271.95</v>
+        <v>7267.25</v>
       </c>
       <c r="O2" t="n">
-        <v>1.885947797571005</v>
+        <v>1.883418914361705</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.2213770443767231</v>
+        <v>-0.218251872856186</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.2394901149307183</v>
+        <v>-0.2349171909378948</v>
       </c>
       <c r="R2" t="n">
-        <v>0.01811307055399516</v>
+        <v>0.01666531808170887</v>
       </c>
       <c r="S2" t="n">
-        <v>0.008056894453980307</v>
+        <v>0.006496123137707782</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.04583880816104052</v>
+        <v>-0.0475211384808325</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -798,40 +798,40 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>46.45712576163717</v>
+        <v>46.45712576507932</v>
       </c>
       <c r="J3" t="n">
-        <v>40.96155817428451</v>
+        <v>40.96155823853795</v>
       </c>
       <c r="K3" t="n">
-        <v>36.34104207231446</v>
+        <v>37.23701979582768</v>
       </c>
       <c r="L3" t="n">
-        <v>74170.2</v>
+        <v>73870.39999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>42432.35</v>
+        <v>42357.4</v>
       </c>
       <c r="N3" t="n">
-        <v>40710.75</v>
+        <v>40673.275</v>
       </c>
       <c r="O3" t="n">
-        <v>1.747963523113851</v>
+        <v>1.743978620028613</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.06353845546477999</v>
+        <v>-0.06275716258464925</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.03803155798686207</v>
+        <v>-0.03688832698865847</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.02550689747791791</v>
+        <v>-0.02586883559599078</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.01701274842385041</v>
+        <v>-0.01740294125291661</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.01175925837098443</v>
+        <v>-0.01217984095092825</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -629,12 +629,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>6846</t>
+          <t>3687</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>綠茵</t>
+          <t>歐買尬</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -643,49 +643,49 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>57.90000152587891</v>
+        <v>61</v>
       </c>
       <c r="G2" t="n">
-        <v>58.08999996185302</v>
+        <v>60.85499973297119</v>
       </c>
       <c r="H2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>44.07253950744339</v>
+        <v>47.38785604092004</v>
       </c>
       <c r="J2" t="n">
-        <v>38.31003494922997</v>
+        <v>46.24501915595864</v>
       </c>
       <c r="K2" t="n">
-        <v>47.13584056222838</v>
+        <v>46.56703870303648</v>
       </c>
       <c r="L2" t="n">
-        <v>14800</v>
+        <v>89296.39999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>7858.05</v>
+        <v>48007.85</v>
       </c>
       <c r="N2" t="n">
-        <v>7267.25</v>
+        <v>45037.95</v>
       </c>
       <c r="O2" t="n">
-        <v>1.883418914361705</v>
+        <v>1.860037473038263</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.218251872856186</v>
+        <v>-0.2640192843381115</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.2349171909378948</v>
+        <v>-0.4879436140151682</v>
       </c>
       <c r="R2" t="n">
-        <v>0.01666531808170887</v>
+        <v>0.2239243296770567</v>
       </c>
       <c r="S2" t="n">
-        <v>0.006496123137707782</v>
+        <v>0.2693380955844606</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0475211384808325</v>
+        <v>0.3271788678723432</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
@@ -775,63 +775,63 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2642</t>
+          <t>6846</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>宅配通</t>
+          <t>綠茵</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>20</v>
+        <v>57.90000152587891</v>
       </c>
       <c r="G3" t="n">
-        <v>20.27499990463257</v>
+        <v>58.075</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>46.45712576507932</v>
+        <v>44.38171843627736</v>
       </c>
       <c r="J3" t="n">
-        <v>40.96155823853795</v>
+        <v>40.33392944491244</v>
       </c>
       <c r="K3" t="n">
-        <v>37.23701979582768</v>
+        <v>47.13584056222838</v>
       </c>
       <c r="L3" t="n">
-        <v>73870.39999999999</v>
+        <v>13800</v>
       </c>
       <c r="M3" t="n">
-        <v>42357.4</v>
+        <v>7708.05</v>
       </c>
       <c r="N3" t="n">
-        <v>40673.275</v>
+        <v>6892.25</v>
       </c>
       <c r="O3" t="n">
-        <v>1.743978620028613</v>
+        <v>1.790336077217973</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.06275716258464925</v>
+        <v>-0.2045331357646134</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.03688832698865847</v>
+        <v>-0.2288403799032385</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.02586883559599078</v>
+        <v>0.02430724413862514</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.01740294125291661</v>
+        <v>0.01666531808170887</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.01217984095092825</v>
+        <v>0.006496123137707782</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>-13</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -878,35 +878,35 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>-13</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>13.52</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>16.52</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -629,12 +629,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3687</t>
+          <t>6482</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>歐買尬</t>
+          <t>弘煜科</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -643,49 +643,49 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>61</v>
+        <v>23.25</v>
       </c>
       <c r="G2" t="n">
-        <v>60.85499973297119</v>
+        <v>23.40750026702881</v>
       </c>
       <c r="H2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>47.38785604092004</v>
+        <v>49.36702431932073</v>
       </c>
       <c r="J2" t="n">
-        <v>46.24501915595864</v>
+        <v>48.40844270083407</v>
       </c>
       <c r="K2" t="n">
-        <v>46.56703870303648</v>
+        <v>39.26527200014372</v>
       </c>
       <c r="L2" t="n">
-        <v>89296.39999999999</v>
+        <v>28956.2</v>
       </c>
       <c r="M2" t="n">
-        <v>48007.85</v>
+        <v>15086.95</v>
       </c>
       <c r="N2" t="n">
-        <v>45037.95</v>
+        <v>14218</v>
       </c>
       <c r="O2" t="n">
-        <v>1.860037473038263</v>
+        <v>1.919287861363629</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.2640192843381115</v>
+        <v>-0.3143572550791234</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.4879436140151682</v>
+        <v>-0.4427444978855387</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2239243296770567</v>
+        <v>0.1283872428064153</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2693380955844606</v>
+        <v>0.156976256777193</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3271788678723432</v>
+        <v>0.1505483289439123</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -775,63 +775,63 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>6846</t>
+          <t>4169</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>綠茵</t>
+          <t>泰宗</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>57.90000152587891</v>
+        <v>148</v>
       </c>
       <c r="G3" t="n">
-        <v>58.075</v>
+        <v>148.425</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>44.38171843627736</v>
+        <v>49.87620973024552</v>
       </c>
       <c r="J3" t="n">
-        <v>40.33392944491244</v>
+        <v>44.38662364962497</v>
       </c>
       <c r="K3" t="n">
-        <v>47.13584056222838</v>
+        <v>44.09280814181052</v>
       </c>
       <c r="L3" t="n">
-        <v>13800</v>
+        <v>204855.4</v>
       </c>
       <c r="M3" t="n">
-        <v>7708.05</v>
+        <v>107798.1</v>
       </c>
       <c r="N3" t="n">
-        <v>6892.25</v>
+        <v>106145.775</v>
       </c>
       <c r="O3" t="n">
-        <v>1.790336077217973</v>
+        <v>1.900361880218668</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.2045331357646134</v>
+        <v>-1.049259230948536</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2288403799032385</v>
+        <v>-1.829441795899141</v>
       </c>
       <c r="R3" t="n">
-        <v>0.02430724413862514</v>
+        <v>0.7801825649506053</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01666531808170887</v>
+        <v>0.938891264765624</v>
       </c>
       <c r="T3" t="n">
-        <v>0.006496123137707782</v>
+        <v>0.8375708745938866</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>-36.572</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -878,10 +878,10 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>-36.572</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>-137.989</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -890,10 +890,10 @@
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>-137.989</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>-51.58400000000001</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
@@ -902,11 +902,11 @@
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>-51.58400000000001</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -652,40 +652,40 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>49.36702431932073</v>
+        <v>49.36702432119827</v>
       </c>
       <c r="J2" t="n">
-        <v>48.40844270083407</v>
+        <v>48.4084427352555</v>
       </c>
       <c r="K2" t="n">
-        <v>39.26527200014372</v>
+        <v>40.11604917123692</v>
       </c>
       <c r="L2" t="n">
-        <v>28956.2</v>
+        <v>28953.4</v>
       </c>
       <c r="M2" t="n">
-        <v>15086.95</v>
+        <v>15086.25</v>
       </c>
       <c r="N2" t="n">
-        <v>14218</v>
+        <v>14217.65</v>
       </c>
       <c r="O2" t="n">
-        <v>1.919287861363629</v>
+        <v>1.919191316596238</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.3143572550791234</v>
+        <v>-0.3088743816711421</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.4427444978855387</v>
+        <v>-0.4347253822520767</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1283872428064153</v>
+        <v>0.1258510005809346</v>
       </c>
       <c r="S2" t="n">
-        <v>0.156976256777193</v>
+        <v>0.1542424820404525</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1505483289439123</v>
+        <v>0.1476021786612437</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -798,40 +798,40 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>49.87620973024552</v>
+        <v>49.87620973350651</v>
       </c>
       <c r="J3" t="n">
-        <v>44.38662364962497</v>
+        <v>44.38662370940963</v>
       </c>
       <c r="K3" t="n">
-        <v>44.09280814181052</v>
+        <v>44.41696657780764</v>
       </c>
       <c r="L3" t="n">
-        <v>204855.4</v>
+        <v>204605.2</v>
       </c>
       <c r="M3" t="n">
-        <v>107798.1</v>
+        <v>107735.55</v>
       </c>
       <c r="N3" t="n">
-        <v>106145.775</v>
+        <v>106114.5</v>
       </c>
       <c r="O3" t="n">
-        <v>1.900361880218668</v>
+        <v>1.89914285488866</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.049259230948536</v>
+        <v>-0.8636849451537785</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.829441795899141</v>
+        <v>-1.558025415170944</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7801825649506053</v>
+        <v>0.6943404700171651</v>
       </c>
       <c r="S3" t="n">
-        <v>0.938891264765624</v>
+        <v>0.8463634501427191</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8375708745938866</v>
+        <v>0.7378549603518336</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>-36.572</v>
+        <v>-44</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -878,10 +878,10 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>-36.572</v>
+        <v>-44</v>
       </c>
       <c r="AF3" t="n">
-        <v>-137.989</v>
+        <v>-142.989</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -890,10 +890,10 @@
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>-137.989</v>
+        <v>-142.989</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-51.58400000000001</v>
+        <v>-89.584</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
@@ -902,7 +902,7 @@
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>-51.58400000000001</v>
+        <v>-89.584</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN3"/>
+  <dimension ref="A1:AN5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -625,67 +625,67 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>6482</t>
+          <t>2348</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>弘煜科</t>
+          <t>海悅</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>23.25</v>
+        <v>70.59999847412109</v>
       </c>
       <c r="G2" t="n">
-        <v>23.40750026702881</v>
+        <v>70.45</v>
       </c>
       <c r="H2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>49.36702432119827</v>
+        <v>40.23226588699299</v>
       </c>
       <c r="J2" t="n">
-        <v>48.4084427352555</v>
+        <v>31.37747480130425</v>
       </c>
       <c r="K2" t="n">
-        <v>40.11604917123692</v>
+        <v>49.99775536378127</v>
       </c>
       <c r="L2" t="n">
-        <v>28953.4</v>
+        <v>542705.6</v>
       </c>
       <c r="M2" t="n">
-        <v>15086.25</v>
+        <v>312477.25</v>
       </c>
       <c r="N2" t="n">
-        <v>14217.65</v>
+        <v>347823.375</v>
       </c>
       <c r="O2" t="n">
-        <v>1.919191316596238</v>
+        <v>1.736784357901255</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.3088743816711421</v>
+        <v>-0.1337944044616393</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.4347253822520767</v>
+        <v>-0.2478221140614151</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1258510005809346</v>
+        <v>0.1140277095997758</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1542424820404525</v>
+        <v>0.1323193011689409</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1476021786612437</v>
+        <v>-0.1000901241403852</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -723,44 +723,44 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>-19.533</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>-0.823</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>-20.356</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>233.674</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>-20.239</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>213.435</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>420.284</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>-45.121</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>375.1630000000001</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -771,142 +771,434 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>80</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>8482</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>商億-KY</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>47.79999923706055</v>
+      </c>
+      <c r="G3" t="n">
+        <v>48.6774995803833</v>
+      </c>
+      <c r="H3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>37.5918080510838</v>
+      </c>
+      <c r="J3" t="n">
+        <v>35.94379593452688</v>
+      </c>
+      <c r="K3" t="n">
+        <v>48.30740701011262</v>
+      </c>
+      <c r="L3" t="n">
+        <v>10432</v>
+      </c>
+      <c r="M3" t="n">
+        <v>6463.5</v>
+      </c>
+      <c r="N3" t="n">
+        <v>6572.275</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.613986230370542</v>
+      </c>
+      <c r="P3" t="n">
+        <v>-0.1857989205389075</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-0.02390141103280045</v>
+      </c>
+      <c r="R3" t="n">
+        <v>-0.161897509506107</v>
+      </c>
+      <c r="S3" t="n">
+        <v>-0.1726730718467197</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-0.3334824094014055</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>7.974</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>6.974</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>7.974</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>7.974</v>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>70</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>4169</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>泰宗</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>6938</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>藍新資訊</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>83</v>
+      </c>
+      <c r="G4" t="n">
+        <v>85.24000091552735</v>
+      </c>
+      <c r="H4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>45.6020816585558</v>
+      </c>
+      <c r="J4" t="n">
+        <v>31.56492618792935</v>
+      </c>
+      <c r="K4" t="n">
+        <v>43.0366676379663</v>
+      </c>
+      <c r="L4" t="n">
+        <v>254061.6</v>
+      </c>
+      <c r="M4" t="n">
+        <v>79458.25</v>
+      </c>
+      <c r="N4" t="n">
+        <v>42461.25</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3.197422545802355</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-3.561837068483584</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-3.470961166276477</v>
+      </c>
+      <c r="R4" t="n">
+        <v>-0.0908759022071064</v>
+      </c>
+      <c r="S4" t="n">
+        <v>-0.5041888046871303</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-0.7556497771126316</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>70</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>4108</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>懷特</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v>148</v>
-      </c>
-      <c r="G3" t="n">
-        <v>148.425</v>
-      </c>
-      <c r="H3" t="b">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>49.87620973350651</v>
-      </c>
-      <c r="J3" t="n">
-        <v>44.38662370940963</v>
-      </c>
-      <c r="K3" t="n">
-        <v>44.41696657780764</v>
-      </c>
-      <c r="L3" t="n">
-        <v>204605.2</v>
-      </c>
-      <c r="M3" t="n">
-        <v>107735.55</v>
-      </c>
-      <c r="N3" t="n">
-        <v>106114.5</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.89914285488866</v>
-      </c>
-      <c r="P3" t="n">
-        <v>-0.8636849451537785</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>-1.558025415170944</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.6943404700171651</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.8463634501427191</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0.7378549603518336</v>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB3" t="n">
-        <v>-44</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>-44</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>-142.989</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>-142.989</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>-89.584</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>-89.584</v>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
+      <c r="F5" t="n">
+        <v>11.39999961853027</v>
+      </c>
+      <c r="G5" t="n">
+        <v>11.40500011444092</v>
+      </c>
+      <c r="H5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>35.15400332540009</v>
+      </c>
+      <c r="J5" t="n">
+        <v>33.43055598986453</v>
+      </c>
+      <c r="K5" t="n">
+        <v>48.96499194013519</v>
+      </c>
+      <c r="L5" t="n">
+        <v>428584.8</v>
+      </c>
+      <c r="M5" t="n">
+        <v>229036.8</v>
+      </c>
+      <c r="N5" t="n">
+        <v>274953.3</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.871248637773493</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.03870048138544391</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.01870035757286394</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.02000012381257996</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.0329948236547776</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.04058657501504438</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>-7</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-501.73</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-499.73</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>-670.307</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>-666.307</v>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>

--- a/output/strict_candidates.xlsx
+++ b/output/strict_candidates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN5"/>
+  <dimension ref="A1:AN6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -629,67 +629,67 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2348</t>
+          <t>6938</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>海悅</t>
+          <t>藍新資訊</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>70.59999847412109</v>
+        <v>79.19999694824219</v>
       </c>
       <c r="G2" t="n">
-        <v>70.45</v>
+        <v>84.48500061035156</v>
       </c>
       <c r="H2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>40.23226588699299</v>
+        <v>45.75718467089248</v>
       </c>
       <c r="J2" t="n">
-        <v>31.37747480130425</v>
+        <v>36.29567906391159</v>
       </c>
       <c r="K2" t="n">
-        <v>49.99775536378127</v>
+        <v>33.57053045904507</v>
       </c>
       <c r="L2" t="n">
-        <v>542705.6</v>
+        <v>294224.2</v>
       </c>
       <c r="M2" t="n">
-        <v>312477.25</v>
+        <v>91460.75</v>
       </c>
       <c r="N2" t="n">
-        <v>347823.375</v>
+        <v>48463.75</v>
       </c>
       <c r="O2" t="n">
-        <v>1.736784357901255</v>
+        <v>3.216944973663566</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.1337944044616393</v>
+        <v>-3.538604012375302</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.2478221140614151</v>
+        <v>-3.510049836700945</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1140277095997758</v>
+        <v>-0.02855417567435703</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1323193011689409</v>
+        <v>-0.0807819844639277</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1000901241403852</v>
+        <v>-0.4933107326160768</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -709,12 +709,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -723,44 +723,44 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>-19.533</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.823</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-20.356</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>233.674</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>-20.239</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>213.435</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>420.284</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>-45.121</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>375.1630000000001</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -775,12 +775,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>8482</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>商億-KY</t>
+          <t>志聯</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -789,49 +789,49 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>47.79999923706055</v>
+        <v>12.75</v>
       </c>
       <c r="G3" t="n">
-        <v>48.6774995803833</v>
+        <v>12.96499991416931</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>37.5918080510838</v>
+        <v>41.18018397688295</v>
       </c>
       <c r="J3" t="n">
-        <v>35.94379593452688</v>
+        <v>34.1255843417722</v>
       </c>
       <c r="K3" t="n">
-        <v>48.30740701011262</v>
+        <v>45.69438915568647</v>
       </c>
       <c r="L3" t="n">
-        <v>10432</v>
+        <v>70600.39999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>6463.5</v>
+        <v>32570.05</v>
       </c>
       <c r="N3" t="n">
-        <v>6572.275</v>
+        <v>22849.625</v>
       </c>
       <c r="O3" t="n">
-        <v>1.613986230370542</v>
+        <v>2.167647885096891</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.1857989205389075</v>
+        <v>-0.07140866261526213</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.02390141103280045</v>
+        <v>-0.07325528285188249</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.161897509506107</v>
+        <v>0.001846620236620355</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1726730718467197</v>
+        <v>0.01078982579367845</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3334824094014055</v>
+        <v>-0.02568096258250885</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -869,44 +869,44 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE3" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="AF3" t="n">
-        <v>7.974</v>
+        <v>16.096</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AI3" t="n">
-        <v>6.974</v>
+        <v>17.096</v>
       </c>
       <c r="AJ3" t="n">
-        <v>7.974</v>
+        <v>4.624000000000002</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AM3" t="n">
-        <v>7.974</v>
+        <v>9.624000000000002</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -917,67 +917,67 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>6938</t>
+          <t>1702</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>藍新資訊</t>
+          <t>南僑</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>83</v>
+        <v>33.04999923706055</v>
       </c>
       <c r="G4" t="n">
-        <v>85.24000091552735</v>
+        <v>33.26000003814697</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>45.6020816585558</v>
+        <v>43.97314699118908</v>
       </c>
       <c r="J4" t="n">
-        <v>31.56492618792935</v>
+        <v>42.25450171208714</v>
       </c>
       <c r="K4" t="n">
-        <v>43.0366676379663</v>
+        <v>45.86800532806714</v>
       </c>
       <c r="L4" t="n">
-        <v>254061.6</v>
+        <v>567237.2</v>
       </c>
       <c r="M4" t="n">
-        <v>79458.25</v>
+        <v>284009.35</v>
       </c>
       <c r="N4" t="n">
-        <v>42461.25</v>
+        <v>211756.65</v>
       </c>
       <c r="O4" t="n">
-        <v>3.197422545802355</v>
+        <v>1.997248330028571</v>
       </c>
       <c r="P4" t="n">
-        <v>-3.561837068483584</v>
+        <v>0.04231428564583695</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.470961166276477</v>
+        <v>0.100695262732506</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.0908759022071064</v>
+        <v>-0.05838097708666901</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5041888046871303</v>
+        <v>-0.05319513849769696</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7556497771126316</v>
+        <v>-0.03196761081141095</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1024,35 +1024,35 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1212.477</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1232.477</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1909.658</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>67.389</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1977.047</v>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -1063,142 +1063,288 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>80</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2348</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>海悅</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>69.80000305175781</v>
+      </c>
+      <c r="G5" t="n">
+        <v>70.41500015258789</v>
+      </c>
+      <c r="H5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>32.65488207063071</v>
+      </c>
+      <c r="J5" t="n">
+        <v>31.80327720634187</v>
+      </c>
+      <c r="K5" t="n">
+        <v>46.34133908076465</v>
+      </c>
+      <c r="L5" t="n">
+        <v>559675.6</v>
+      </c>
+      <c r="M5" t="n">
+        <v>312017.25</v>
+      </c>
+      <c r="N5" t="n">
+        <v>347527.775</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.793732878550785</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-0.1969203493523821</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-0.2487989339662471</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.05187858461386494</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.1184337792024969</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.1370676599240008</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>-40</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-1.279</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>-41.279</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>100.574</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-20.519</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>80.05500000000004</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>434.284</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>-42.914</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>391.3700000000001</v>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>符合</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>70</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>4108</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>懷特</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>5306</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>桂盟</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="F5" t="n">
-        <v>11.39999961853027</v>
-      </c>
-      <c r="G5" t="n">
-        <v>11.40500011444092</v>
-      </c>
-      <c r="H5" t="b">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>35.15400332540009</v>
-      </c>
-      <c r="J5" t="n">
-        <v>33.43055598986453</v>
-      </c>
-      <c r="K5" t="n">
-        <v>48.96499194013519</v>
-      </c>
-      <c r="L5" t="n">
-        <v>428584.8</v>
-      </c>
-      <c r="M5" t="n">
-        <v>229036.8</v>
-      </c>
-      <c r="N5" t="n">
-        <v>274953.3</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.871248637773493</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.03870048138544391</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.01870035757286394</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.02000012381257996</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.0329948236547776</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.04058657501504438</v>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="AB5" t="n">
-        <v>-7</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>-501.73</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>-499.73</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>-670.307</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL5" t="n">
+      <c r="F6" t="n">
+        <v>88.30000305175781</v>
+      </c>
+      <c r="G6" t="n">
+        <v>88.06000061035157</v>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>38.37581563855765</v>
+      </c>
+      <c r="J6" t="n">
+        <v>30.22850556835055</v>
+      </c>
+      <c r="K6" t="n">
+        <v>48.6576112912044</v>
+      </c>
+      <c r="L6" t="n">
+        <v>282428.2</v>
+      </c>
+      <c r="M6" t="n">
+        <v>155918.3</v>
+      </c>
+      <c r="N6" t="n">
+        <v>122152.675</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.811385834760897</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-0.7345209060671181</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-0.7963782110556326</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.06185730498851449</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-0.0294501384728727</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-0.1812186186015048</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>-9</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
         <v>4</v>
       </c>
-      <c r="AM5" t="n">
-        <v>-666.307</v>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
+      <c r="AE6" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-175.746</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-150.746</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>-271.218</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-153</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>-364.218</v>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
